--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,430 +34,394 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
   </si>
 </sst>
 </file>
@@ -819,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -844,16 +808,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>803</v>
+        <v>764</v>
       </c>
       <c r="C2">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="D2">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -864,16 +828,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>804</v>
+        <v>767</v>
       </c>
       <c r="C3">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="D3">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -884,16 +848,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>803</v>
+        <v>764</v>
       </c>
       <c r="C4">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="D4">
-        <v>1264</v>
+        <v>1293</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -904,16 +868,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>804</v>
+        <v>764</v>
       </c>
       <c r="C5">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="D5">
-        <v>1265</v>
+        <v>1293</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -924,16 +888,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>807</v>
+        <v>754</v>
       </c>
       <c r="C6">
-        <v>440</v>
+        <v>514</v>
       </c>
       <c r="D6">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -944,16 +908,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>804</v>
+        <v>752</v>
       </c>
       <c r="C7">
-        <v>441</v>
+        <v>513</v>
       </c>
       <c r="D7">
-        <v>1245</v>
+        <v>1265</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -964,16 +928,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>802</v>
+        <v>753</v>
       </c>
       <c r="C8">
-        <v>439</v>
+        <v>513</v>
       </c>
       <c r="D8">
-        <v>1241</v>
+        <v>1266</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -984,16 +948,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>804</v>
+        <v>752</v>
       </c>
       <c r="C9">
-        <v>440</v>
+        <v>514</v>
       </c>
       <c r="D9">
-        <v>1244</v>
+        <v>1266</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1004,16 +968,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>795</v>
+        <v>745</v>
       </c>
       <c r="C10">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="D10">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1024,16 +988,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>795</v>
+        <v>746</v>
       </c>
       <c r="C11">
-        <v>440</v>
+        <v>512</v>
       </c>
       <c r="D11">
-        <v>1235</v>
+        <v>1258</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1044,16 +1008,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>794</v>
+        <v>746</v>
       </c>
       <c r="C12">
-        <v>439</v>
+        <v>513</v>
       </c>
       <c r="D12">
-        <v>1233</v>
+        <v>1259</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1064,16 +1028,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>794</v>
+        <v>745</v>
       </c>
       <c r="C13">
-        <v>439</v>
+        <v>514</v>
       </c>
       <c r="D13">
-        <v>1233</v>
+        <v>1259</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1084,16 +1048,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>795</v>
+        <v>738</v>
       </c>
       <c r="C14">
-        <v>440</v>
+        <v>519</v>
       </c>
       <c r="D14">
-        <v>1235</v>
+        <v>1257</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1104,16 +1068,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>793</v>
+        <v>737</v>
       </c>
       <c r="C15">
-        <v>439</v>
+        <v>520</v>
       </c>
       <c r="D15">
-        <v>1232</v>
+        <v>1257</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1124,16 +1088,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>793</v>
+        <v>739</v>
       </c>
       <c r="C16">
-        <v>439</v>
+        <v>508</v>
       </c>
       <c r="D16">
-        <v>1232</v>
+        <v>1247</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1144,16 +1108,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>798</v>
+        <v>742</v>
       </c>
       <c r="C17">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="D17">
-        <v>1237</v>
+        <v>1222</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1164,16 +1128,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>821</v>
+        <v>743</v>
       </c>
       <c r="C18">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="D18">
-        <v>1261</v>
+        <v>1223</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1184,16 +1148,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>819</v>
+        <v>742</v>
       </c>
       <c r="C19">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="D19">
-        <v>1258</v>
+        <v>1223</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1204,16 +1168,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>821</v>
+        <v>744</v>
       </c>
       <c r="C20">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="D20">
-        <v>1260</v>
+        <v>1225</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1224,16 +1188,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>824</v>
+        <v>746</v>
       </c>
       <c r="C21">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="D21">
-        <v>1263</v>
+        <v>1228</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1244,16 +1208,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>849</v>
+        <v>750</v>
       </c>
       <c r="C22">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="D22">
-        <v>1310</v>
+        <v>1234</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1264,16 +1228,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>853</v>
+        <v>750</v>
       </c>
       <c r="C23">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="D23">
-        <v>1315</v>
+        <v>1237</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1284,16 +1248,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>853</v>
+        <v>750</v>
       </c>
       <c r="C24">
-        <v>466</v>
+        <v>525</v>
       </c>
       <c r="D24">
-        <v>1319</v>
+        <v>1275</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1304,16 +1268,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>868</v>
+        <v>753</v>
       </c>
       <c r="C25">
-        <v>466</v>
+        <v>525</v>
       </c>
       <c r="D25">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1324,16 +1288,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>1003</v>
+        <v>831</v>
       </c>
       <c r="C26">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="D26">
-        <v>1486</v>
+        <v>1351</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1344,16 +1308,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>1002</v>
+        <v>834</v>
       </c>
       <c r="C27">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="D27">
-        <v>1482</v>
+        <v>1300</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1364,16 +1328,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>1000</v>
+        <v>831</v>
       </c>
       <c r="C28">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="D28">
-        <v>1481</v>
+        <v>1295</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1384,16 +1348,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>996</v>
+        <v>827</v>
       </c>
       <c r="C29">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="D29">
-        <v>1476</v>
+        <v>1288</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1404,16 +1368,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>1007</v>
+        <v>853</v>
       </c>
       <c r="C30">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="D30">
-        <v>1489</v>
+        <v>1323</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1424,16 +1388,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>1003</v>
+        <v>855</v>
       </c>
       <c r="C31">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D31">
-        <v>1486</v>
+        <v>1326</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1444,16 +1408,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>1013</v>
+        <v>863</v>
       </c>
       <c r="C32">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D32">
-        <v>1503</v>
+        <v>1346</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1464,16 +1428,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>1015</v>
+        <v>850</v>
       </c>
       <c r="C33">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D33">
-        <v>1505</v>
+        <v>1333</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1484,16 +1448,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>846</v>
+        <v>802</v>
       </c>
       <c r="C34">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D34">
-        <v>1347</v>
+        <v>1318</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1504,16 +1468,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="C35">
-        <v>503</v>
+        <v>657</v>
       </c>
       <c r="D35">
-        <v>1334</v>
+        <v>1479</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1524,16 +1488,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>627</v>
+        <v>818</v>
       </c>
       <c r="C36">
-        <v>500</v>
+        <v>656</v>
       </c>
       <c r="D36">
-        <v>1127</v>
+        <v>1474</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1544,16 +1508,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>615</v>
+        <v>806</v>
       </c>
       <c r="C37">
-        <v>499</v>
+        <v>652</v>
       </c>
       <c r="D37">
-        <v>1114</v>
+        <v>1458</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1564,16 +1528,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>153</v>
+        <v>434</v>
       </c>
       <c r="C38">
-        <v>283</v>
+        <v>381</v>
       </c>
       <c r="D38">
-        <v>436</v>
+        <v>815</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1584,16 +1548,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>141</v>
+        <v>409</v>
       </c>
       <c r="C39">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="D39">
-        <v>416</v>
+        <v>766</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1604,16 +1568,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>141</v>
+        <v>408</v>
       </c>
       <c r="C40">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="D40">
-        <v>415</v>
+        <v>778</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1624,16 +1588,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="C41">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="D41">
-        <v>382</v>
+        <v>705</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1644,16 +1608,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>61</v>
+        <v>345</v>
       </c>
       <c r="C42">
-        <v>232</v>
+        <v>327</v>
       </c>
       <c r="D42">
-        <v>293</v>
+        <v>672</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1664,16 +1628,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="C43">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="D43">
-        <v>290</v>
+        <v>642</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1684,16 +1648,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="C44">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="D44">
-        <v>288</v>
+        <v>617</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1704,16 +1668,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="C45">
-        <v>228</v>
+        <v>314</v>
       </c>
       <c r="D45">
-        <v>287</v>
+        <v>629</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1724,16 +1688,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>50</v>
+        <v>368</v>
       </c>
       <c r="C46">
-        <v>207</v>
+        <v>402</v>
       </c>
       <c r="D46">
-        <v>257</v>
+        <v>770</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1744,16 +1708,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>50</v>
+        <v>366</v>
       </c>
       <c r="C47">
-        <v>206</v>
+        <v>400</v>
       </c>
       <c r="D47">
-        <v>256</v>
+        <v>766</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1764,16 +1728,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>51</v>
+        <v>368</v>
       </c>
       <c r="C48">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="D48">
-        <v>257</v>
+        <v>732</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1784,16 +1748,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>49</v>
+        <v>422</v>
       </c>
       <c r="C49">
-        <v>243</v>
+        <v>439</v>
       </c>
       <c r="D49">
-        <v>292</v>
+        <v>861</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1804,16 +1768,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>49</v>
+        <v>579</v>
       </c>
       <c r="C50">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="D50">
-        <v>318</v>
+        <v>911</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1824,16 +1788,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>47</v>
+        <v>584</v>
       </c>
       <c r="C51">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="D51">
-        <v>316</v>
+        <v>916</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1844,16 +1808,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>48</v>
+        <v>637</v>
       </c>
       <c r="C52">
-        <v>270</v>
+        <v>332</v>
       </c>
       <c r="D52">
-        <v>318</v>
+        <v>969</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1864,16 +1828,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="C53">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="D53">
-        <v>319</v>
+        <v>970</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1884,16 +1848,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>47</v>
+        <v>679</v>
       </c>
       <c r="C54">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D54">
-        <v>306</v>
+        <v>949</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1904,16 +1868,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>47</v>
+        <v>477</v>
       </c>
       <c r="C55">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D55">
-        <v>305</v>
+        <v>742</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1924,16 +1888,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="C56">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D56">
-        <v>306</v>
+        <v>645</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1944,16 +1908,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>51</v>
+        <v>286</v>
       </c>
       <c r="C57">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D57">
-        <v>311</v>
+        <v>551</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1964,16 +1928,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="C58">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D58">
-        <v>396</v>
+        <v>526</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -1984,16 +1948,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="C59">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D59">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2004,16 +1968,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>135</v>
+        <v>490</v>
       </c>
       <c r="C60">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D60">
-        <v>411</v>
+        <v>771</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2024,16 +1988,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>141</v>
+        <v>470</v>
       </c>
       <c r="C61">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="D61">
-        <v>398</v>
+        <v>752</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2044,16 +2008,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="C62">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="D62">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2064,16 +2028,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C63">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D63">
-        <v>444</v>
+        <v>492</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2084,16 +2048,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C64">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="D64">
-        <v>382</v>
+        <v>494</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2104,16 +2068,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C65">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="D65">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2124,16 +2088,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>797</v>
+        <v>302</v>
       </c>
       <c r="C66">
-        <v>517</v>
+        <v>441</v>
       </c>
       <c r="D66">
-        <v>1314</v>
+        <v>743</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2144,16 +2108,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>825</v>
+        <v>303</v>
       </c>
       <c r="C67">
-        <v>526</v>
+        <v>449</v>
       </c>
       <c r="D67">
-        <v>1351</v>
+        <v>752</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2164,16 +2128,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>833</v>
+        <v>304</v>
       </c>
       <c r="C68">
-        <v>524</v>
+        <v>450</v>
       </c>
       <c r="D68">
-        <v>1357</v>
+        <v>754</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2184,16 +2148,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>922</v>
+        <v>350</v>
       </c>
       <c r="C69">
-        <v>525</v>
+        <v>456</v>
       </c>
       <c r="D69">
-        <v>1447</v>
+        <v>806</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2204,16 +2168,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>965</v>
+        <v>852</v>
       </c>
       <c r="C70">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="D70">
-        <v>1573</v>
+        <v>1479</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2224,16 +2188,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>979</v>
+        <v>776</v>
       </c>
       <c r="C71">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="D71">
-        <v>1592</v>
+        <v>1404</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2244,16 +2208,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>979</v>
+        <v>769</v>
       </c>
       <c r="C72">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D72">
-        <v>1590</v>
+        <v>1389</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2264,16 +2228,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>916</v>
+        <v>770</v>
       </c>
       <c r="C73">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="D73">
-        <v>1539</v>
+        <v>1385</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2284,16 +2248,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>1093</v>
+        <v>752</v>
       </c>
       <c r="C74">
-        <v>651</v>
+        <v>601</v>
       </c>
       <c r="D74">
-        <v>1744</v>
+        <v>1353</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2304,16 +2268,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>1108</v>
+        <v>751</v>
       </c>
       <c r="C75">
-        <v>654</v>
+        <v>600</v>
       </c>
       <c r="D75">
-        <v>1762</v>
+        <v>1351</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2324,16 +2288,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>1107</v>
+        <v>750</v>
       </c>
       <c r="C76">
-        <v>655</v>
+        <v>603</v>
       </c>
       <c r="D76">
-        <v>1762</v>
+        <v>1353</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2344,16 +2308,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>1113</v>
+        <v>760</v>
       </c>
       <c r="C77">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="D77">
-        <v>1760</v>
+        <v>1370</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2364,16 +2328,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>1157</v>
+        <v>863</v>
       </c>
       <c r="C78">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D78">
-        <v>1782</v>
+        <v>1487</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2384,16 +2348,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>1154</v>
+        <v>879</v>
       </c>
       <c r="C79">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="D79">
-        <v>1771</v>
+        <v>1510</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2404,16 +2368,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>1153</v>
+        <v>881</v>
       </c>
       <c r="C80">
-        <v>609</v>
+        <v>705</v>
       </c>
       <c r="D80">
-        <v>1762</v>
+        <v>1586</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2424,16 +2388,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>1022</v>
+        <v>886</v>
       </c>
       <c r="C81">
-        <v>607</v>
+        <v>708</v>
       </c>
       <c r="D81">
-        <v>1629</v>
+        <v>1594</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2444,16 +2408,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>1082</v>
+        <v>901</v>
       </c>
       <c r="C82">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D82">
-        <v>1688</v>
+        <v>1516</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2464,16 +2428,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>1085</v>
+        <v>906</v>
       </c>
       <c r="C83">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="D83">
-        <v>1690</v>
+        <v>1518</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2484,16 +2448,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>1018</v>
+        <v>905</v>
       </c>
       <c r="C84">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D84">
-        <v>1625</v>
+        <v>1515</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2504,16 +2468,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>1017</v>
+        <v>904</v>
       </c>
       <c r="C85">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D85">
-        <v>1621</v>
+        <v>1514</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2524,16 +2488,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>947</v>
+        <v>854</v>
       </c>
       <c r="C86">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="D86">
-        <v>1554</v>
+        <v>1471</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2544,16 +2508,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>948</v>
+        <v>841</v>
       </c>
       <c r="C87">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D87">
-        <v>1560</v>
+        <v>1458</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2564,16 +2528,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>952</v>
+        <v>778</v>
       </c>
       <c r="C88">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="D88">
-        <v>1572</v>
+        <v>1367</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2584,16 +2548,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>932</v>
+        <v>774</v>
       </c>
       <c r="C89">
-        <v>632</v>
+        <v>589</v>
       </c>
       <c r="D89">
-        <v>1564</v>
+        <v>1363</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2604,16 +2568,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>855</v>
+        <v>689</v>
       </c>
       <c r="C90">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="D90">
-        <v>1449</v>
+        <v>1266</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2624,16 +2588,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>850</v>
+        <v>686</v>
       </c>
       <c r="C91">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D91">
-        <v>1440</v>
+        <v>1264</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2644,16 +2608,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>843</v>
+        <v>685</v>
       </c>
       <c r="C92">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="D92">
-        <v>1432</v>
+        <v>1263</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2664,16 +2628,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>843</v>
+        <v>694</v>
       </c>
       <c r="C93">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="D93">
-        <v>1435</v>
+        <v>1272</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2684,16 +2648,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C94">
-        <v>560</v>
+        <v>463</v>
       </c>
       <c r="D94">
-        <v>1373</v>
+        <v>1267</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2704,16 +2668,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C95">
-        <v>556</v>
+        <v>447</v>
       </c>
       <c r="D95">
-        <v>1366</v>
+        <v>1255</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2724,16 +2688,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C96">
-        <v>555</v>
+        <v>447</v>
       </c>
       <c r="D96">
-        <v>1361</v>
+        <v>1259</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2744,16 +2708,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
         <v>810</v>
       </c>
       <c r="C97">
-        <v>552</v>
+        <v>448</v>
       </c>
       <c r="D97">
-        <v>1362</v>
+        <v>1258</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2764,16 +2728,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>867</v>
+        <v>776</v>
       </c>
       <c r="C98">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D98">
-        <v>1303</v>
+        <v>1204</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2784,16 +2748,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>867</v>
+        <v>772</v>
       </c>
       <c r="C99">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D99">
-        <v>1301</v>
+        <v>1199</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2804,16 +2768,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>866</v>
+        <v>768</v>
       </c>
       <c r="C100">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D100">
-        <v>1301</v>
+        <v>1196</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2824,16 +2788,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>863</v>
+        <v>768</v>
       </c>
       <c r="C101">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D101">
-        <v>1296</v>
+        <v>1195</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2844,16 +2808,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>867</v>
+        <v>706</v>
       </c>
       <c r="C102">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D102">
-        <v>1283</v>
+        <v>1129</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2864,16 +2828,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>864</v>
+        <v>688</v>
       </c>
       <c r="C103">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D103">
-        <v>1280</v>
+        <v>1099</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2884,16 +2848,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>864</v>
+        <v>688</v>
       </c>
       <c r="C104">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="D104">
-        <v>1279</v>
+        <v>1091</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2904,16 +2868,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>866</v>
+        <v>687</v>
       </c>
       <c r="C105">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="D105">
-        <v>1279</v>
+        <v>1089</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2924,16 +2888,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>853</v>
+        <v>681</v>
       </c>
       <c r="C106">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D106">
-        <v>1261</v>
+        <v>1096</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2944,16 +2908,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>853</v>
+        <v>680</v>
       </c>
       <c r="C107">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D107">
-        <v>1259</v>
+        <v>1097</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2964,16 +2928,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>854</v>
+        <v>680</v>
       </c>
       <c r="C108">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D108">
-        <v>1262</v>
+        <v>1096</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -2984,16 +2948,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>854</v>
+        <v>678</v>
       </c>
       <c r="C109">
         <v>418</v>
       </c>
       <c r="D109">
-        <v>1272</v>
+        <v>1096</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3004,16 +2968,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>855</v>
+        <v>204</v>
       </c>
       <c r="C110">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="D110">
-        <v>1271</v>
+        <v>544</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3024,16 +2988,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>855</v>
+        <v>183</v>
       </c>
       <c r="C111">
-        <v>417</v>
+        <v>336</v>
       </c>
       <c r="D111">
-        <v>1272</v>
+        <v>519</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3044,16 +3008,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>854</v>
+        <v>183</v>
       </c>
       <c r="C112">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="D112">
-        <v>1263</v>
+        <v>518</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3064,16 +3028,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>861</v>
+        <v>213</v>
       </c>
       <c r="C113">
-        <v>418</v>
+        <v>336</v>
       </c>
       <c r="D113">
-        <v>1279</v>
+        <v>549</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3084,16 +3048,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>884</v>
+        <v>660</v>
       </c>
       <c r="C114">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="D114">
-        <v>1297</v>
+        <v>1049</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3104,16 +3068,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>884</v>
+        <v>673</v>
       </c>
       <c r="C115">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D115">
-        <v>1289</v>
+        <v>1072</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3124,16 +3088,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>885</v>
+        <v>674</v>
       </c>
       <c r="C116">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D116">
-        <v>1290</v>
+        <v>1074</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3144,16 +3108,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>884</v>
+        <v>680</v>
       </c>
       <c r="C117">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D117">
-        <v>1288</v>
+        <v>1081</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3164,16 +3128,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>924</v>
+        <v>655</v>
       </c>
       <c r="C118">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="D118">
-        <v>1343</v>
+        <v>1096</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3184,16 +3148,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>931</v>
+        <v>664</v>
       </c>
       <c r="C119">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="D119">
-        <v>1344</v>
+        <v>1105</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3204,16 +3168,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>958</v>
+        <v>668</v>
       </c>
       <c r="C120">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D120">
-        <v>1384</v>
+        <v>1101</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3224,16 +3188,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>960</v>
+        <v>652</v>
       </c>
       <c r="C121">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D121">
-        <v>1394</v>
+        <v>1085</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3244,16 +3208,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>1029</v>
+        <v>681</v>
       </c>
       <c r="C122">
-        <v>536</v>
+        <v>447</v>
       </c>
       <c r="D122">
-        <v>1565</v>
+        <v>1128</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3264,16 +3228,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>1001</v>
+        <v>678</v>
       </c>
       <c r="C123">
-        <v>541</v>
+        <v>451</v>
       </c>
       <c r="D123">
-        <v>1542</v>
+        <v>1129</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3284,16 +3248,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>1002</v>
+        <v>679</v>
       </c>
       <c r="C124">
-        <v>533</v>
+        <v>452</v>
       </c>
       <c r="D124">
-        <v>1535</v>
+        <v>1131</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3304,16 +3268,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>991</v>
+        <v>677</v>
       </c>
       <c r="C125">
-        <v>537</v>
+        <v>453</v>
       </c>
       <c r="D125">
-        <v>1528</v>
+        <v>1130</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3324,16 +3288,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>964</v>
+        <v>679</v>
       </c>
       <c r="C126">
-        <v>572</v>
+        <v>443</v>
       </c>
       <c r="D126">
-        <v>1536</v>
+        <v>1122</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3344,16 +3308,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>939</v>
+        <v>683</v>
       </c>
       <c r="C127">
-        <v>565</v>
+        <v>444</v>
       </c>
       <c r="D127">
-        <v>1504</v>
+        <v>1127</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3364,16 +3328,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>932</v>
+        <v>685</v>
       </c>
       <c r="C128">
-        <v>565</v>
+        <v>444</v>
       </c>
       <c r="D128">
-        <v>1497</v>
+        <v>1129</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3384,16 +3348,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>931</v>
+        <v>681</v>
       </c>
       <c r="C129">
-        <v>559</v>
+        <v>446</v>
       </c>
       <c r="D129">
-        <v>1490</v>
+        <v>1127</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3404,16 +3368,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>899</v>
+        <v>535</v>
       </c>
       <c r="C130">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D130">
-        <v>1354</v>
+        <v>980</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3424,262 +3388,22 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>936</v>
+        <v>545</v>
       </c>
       <c r="C131">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="D131">
-        <v>1385</v>
+        <v>980</v>
       </c>
       <c r="E131">
         <v>34</v>
       </c>
       <c r="F131" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132" s="2">
-        <v>46269.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>787</v>
-      </c>
-      <c r="C132">
-        <v>452</v>
-      </c>
-      <c r="D132">
-        <v>1239</v>
-      </c>
-      <c r="E132">
-        <v>35</v>
-      </c>
-      <c r="F132" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>766</v>
-      </c>
-      <c r="C133">
-        <v>451</v>
-      </c>
-      <c r="D133">
-        <v>1217</v>
-      </c>
-      <c r="E133">
-        <v>36</v>
-      </c>
-      <c r="F133" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B134">
-        <v>245</v>
-      </c>
-      <c r="C134">
-        <v>298</v>
-      </c>
-      <c r="D134">
-        <v>543</v>
-      </c>
-      <c r="E134">
-        <v>37</v>
-      </c>
-      <c r="F134" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>228</v>
-      </c>
-      <c r="C135">
-        <v>289</v>
-      </c>
-      <c r="D135">
-        <v>517</v>
-      </c>
-      <c r="E135">
-        <v>38</v>
-      </c>
-      <c r="F135" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>222</v>
-      </c>
-      <c r="C136">
-        <v>289</v>
-      </c>
-      <c r="D136">
-        <v>511</v>
-      </c>
-      <c r="E136">
-        <v>39</v>
-      </c>
-      <c r="F136" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B137">
-        <v>221</v>
-      </c>
-      <c r="C137">
-        <v>289</v>
-      </c>
-      <c r="D137">
-        <v>510</v>
-      </c>
-      <c r="E137">
-        <v>40</v>
-      </c>
-      <c r="F137" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>173</v>
-      </c>
-      <c r="C138">
-        <v>247</v>
-      </c>
-      <c r="D138">
-        <v>420</v>
-      </c>
-      <c r="E138">
-        <v>41</v>
-      </c>
-      <c r="F138" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>162</v>
-      </c>
-      <c r="C139">
-        <v>243</v>
-      </c>
-      <c r="D139">
-        <v>405</v>
-      </c>
-      <c r="E139">
-        <v>42</v>
-      </c>
-      <c r="F139" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B140">
-        <v>162</v>
-      </c>
-      <c r="C140">
-        <v>243</v>
-      </c>
-      <c r="D140">
-        <v>405</v>
-      </c>
-      <c r="E140">
-        <v>43</v>
-      </c>
-      <c r="F140" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>69</v>
-      </c>
-      <c r="C141">
-        <v>244</v>
-      </c>
-      <c r="D141">
-        <v>313</v>
-      </c>
-      <c r="E141">
-        <v>44</v>
-      </c>
-      <c r="F141" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>101</v>
-      </c>
-      <c r="C142">
-        <v>250</v>
-      </c>
-      <c r="D142">
-        <v>351</v>
-      </c>
-      <c r="E142">
-        <v>45</v>
-      </c>
-      <c r="F142" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>248</v>
-      </c>
-      <c r="D143">
-        <v>248</v>
-      </c>
-      <c r="E143">
-        <v>46</v>
-      </c>
-      <c r="F143" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,691 +34,697 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1105,16 +1111,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>689</v>
+        <v>284</v>
       </c>
       <c r="D2">
-        <v>1082</v>
+        <v>314</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1125,16 +1131,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>387</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>690</v>
+        <v>256</v>
       </c>
       <c r="D3">
-        <v>1077</v>
+        <v>285</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1145,16 +1151,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>386</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>690</v>
+        <v>256</v>
       </c>
       <c r="D4">
-        <v>1076</v>
+        <v>283</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1165,16 +1171,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>386</v>
+        <v>28</v>
       </c>
       <c r="C5">
-        <v>690</v>
+        <v>256</v>
       </c>
       <c r="D5">
-        <v>1076</v>
+        <v>284</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1185,16 +1191,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="C6">
-        <v>420</v>
+        <v>256</v>
       </c>
       <c r="D6">
-        <v>590</v>
+        <v>285</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1205,16 +1211,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="C7">
-        <v>385</v>
+        <v>256</v>
       </c>
       <c r="D7">
-        <v>546</v>
+        <v>284</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1225,16 +1231,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="C8">
-        <v>385</v>
+        <v>256</v>
       </c>
       <c r="D8">
-        <v>544</v>
+        <v>284</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1245,16 +1251,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="C9">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="D9">
-        <v>543</v>
+        <v>284</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1265,16 +1271,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>423</v>
+        <v>283</v>
       </c>
       <c r="D10">
-        <v>642</v>
+        <v>312</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1285,16 +1291,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="C11">
-        <v>426</v>
+        <v>284</v>
       </c>
       <c r="D11">
-        <v>648</v>
+        <v>312</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1305,16 +1311,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>221</v>
+        <v>28</v>
       </c>
       <c r="C12">
-        <v>424</v>
+        <v>284</v>
       </c>
       <c r="D12">
-        <v>645</v>
+        <v>312</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1325,16 +1331,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>232</v>
+        <v>28</v>
       </c>
       <c r="C13">
-        <v>426</v>
+        <v>285</v>
       </c>
       <c r="D13">
-        <v>658</v>
+        <v>313</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1345,16 +1351,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="C14">
-        <v>425</v>
+        <v>288</v>
       </c>
       <c r="D14">
-        <v>750</v>
+        <v>317</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1365,16 +1371,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>324</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>426</v>
+        <v>288</v>
       </c>
       <c r="D15">
-        <v>750</v>
+        <v>317</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1385,16 +1391,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>324</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>425</v>
+        <v>288</v>
       </c>
       <c r="D16">
-        <v>749</v>
+        <v>317</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1405,16 +1411,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="C17">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="D17">
-        <v>768</v>
+        <v>293</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1425,16 +1431,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>524</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>423</v>
+        <v>263</v>
       </c>
       <c r="D18">
-        <v>947</v>
+        <v>291</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1445,16 +1451,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>526</v>
+        <v>29</v>
       </c>
       <c r="C19">
-        <v>424</v>
+        <v>263</v>
       </c>
       <c r="D19">
-        <v>950</v>
+        <v>292</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1465,16 +1471,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>525</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>423</v>
+        <v>263</v>
       </c>
       <c r="D20">
-        <v>948</v>
+        <v>292</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1485,16 +1491,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>533</v>
+        <v>40</v>
       </c>
       <c r="C21">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="D21">
-        <v>958</v>
+        <v>304</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1505,16 +1511,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>705</v>
+        <v>73</v>
       </c>
       <c r="C22">
-        <v>449</v>
+        <v>311</v>
       </c>
       <c r="D22">
-        <v>1154</v>
+        <v>384</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1525,16 +1531,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>726</v>
+        <v>79</v>
       </c>
       <c r="C23">
-        <v>461</v>
+        <v>313</v>
       </c>
       <c r="D23">
-        <v>1187</v>
+        <v>392</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1545,16 +1551,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>723</v>
+        <v>81</v>
       </c>
       <c r="C24">
-        <v>556</v>
+        <v>314</v>
       </c>
       <c r="D24">
-        <v>1279</v>
+        <v>395</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1565,16 +1571,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>737</v>
+        <v>99</v>
       </c>
       <c r="C25">
-        <v>551</v>
+        <v>328</v>
       </c>
       <c r="D25">
-        <v>1288</v>
+        <v>427</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1585,16 +1591,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>773</v>
+        <v>145</v>
       </c>
       <c r="C26">
-        <v>663</v>
+        <v>598</v>
       </c>
       <c r="D26">
-        <v>1436</v>
+        <v>743</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1605,16 +1611,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>777</v>
+        <v>162</v>
       </c>
       <c r="C27">
-        <v>667</v>
+        <v>612</v>
       </c>
       <c r="D27">
-        <v>1444</v>
+        <v>774</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1625,16 +1631,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>772</v>
+        <v>150</v>
       </c>
       <c r="C28">
-        <v>666</v>
+        <v>606</v>
       </c>
       <c r="D28">
-        <v>1438</v>
+        <v>756</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1645,16 +1651,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>761</v>
+        <v>150</v>
       </c>
       <c r="C29">
-        <v>666</v>
+        <v>623</v>
       </c>
       <c r="D29">
-        <v>1427</v>
+        <v>773</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1665,16 +1671,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>805</v>
+        <v>296</v>
       </c>
       <c r="C30">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D30">
-        <v>1470</v>
+        <v>963</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1685,16 +1691,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>829</v>
+        <v>296</v>
       </c>
       <c r="C31">
-        <v>648</v>
+        <v>623</v>
       </c>
       <c r="D31">
-        <v>1477</v>
+        <v>919</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1705,16 +1711,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>869</v>
+        <v>297</v>
       </c>
       <c r="C32">
-        <v>682</v>
+        <v>627</v>
       </c>
       <c r="D32">
-        <v>1551</v>
+        <v>924</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1725,16 +1731,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>932</v>
+        <v>294</v>
       </c>
       <c r="C33">
-        <v>707</v>
+        <v>630</v>
       </c>
       <c r="D33">
-        <v>1639</v>
+        <v>924</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1745,16 +1751,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>325</v>
+        <v>105</v>
       </c>
       <c r="C34">
-        <v>567</v>
+        <v>314</v>
       </c>
       <c r="D34">
-        <v>892</v>
+        <v>419</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1765,16 +1771,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>313</v>
+        <v>101</v>
       </c>
       <c r="C35">
-        <v>559</v>
+        <v>240</v>
       </c>
       <c r="D35">
-        <v>872</v>
+        <v>341</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1785,16 +1791,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C36">
-        <v>522</v>
+        <v>231</v>
       </c>
       <c r="D36">
-        <v>624</v>
+        <v>328</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1805,16 +1811,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C37">
-        <v>519</v>
+        <v>232</v>
       </c>
       <c r="D37">
-        <v>596</v>
+        <v>338</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1825,16 +1831,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C38">
-        <v>332</v>
+        <v>201</v>
       </c>
       <c r="D38">
-        <v>393</v>
+        <v>293</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1845,16 +1851,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="D39">
-        <v>366</v>
+        <v>243</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1865,16 +1871,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C40">
-        <v>305</v>
+        <v>200</v>
       </c>
       <c r="D40">
-        <v>364</v>
+        <v>300</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1885,16 +1891,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="D41">
-        <v>362</v>
+        <v>258</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1905,16 +1911,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C42">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="D42">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1925,16 +1931,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C43">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="D43">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1945,16 +1951,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="D44">
-        <v>364</v>
+        <v>250</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1965,16 +1971,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D45">
-        <v>371</v>
+        <v>231</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1985,16 +1991,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="D46">
-        <v>379</v>
+        <v>205</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2005,16 +2011,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C47">
-        <v>246</v>
+        <v>185</v>
       </c>
       <c r="D47">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2025,16 +2031,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C48">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="D48">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2045,16 +2051,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C49">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="D49">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2065,16 +2071,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="D50">
-        <v>281</v>
+        <v>208</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2085,16 +2091,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C51">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="D51">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2105,16 +2111,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C52">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="D52">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2125,16 +2131,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C53">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D53">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2145,16 +2151,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="D54">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2165,16 +2171,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D55">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2185,16 +2191,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C56">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="D56">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2205,16 +2211,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C57">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D57">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2225,16 +2231,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="C58">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D58">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2245,16 +2251,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C59">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="D59">
-        <v>292</v>
+        <v>219</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2265,16 +2271,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C60">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="D60">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2285,16 +2291,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C61">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="D61">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2305,16 +2311,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C62">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="D62">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2325,16 +2331,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C63">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="D63">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2345,16 +2351,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C64">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D64">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2365,16 +2371,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C65">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="D65">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2385,16 +2391,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C66">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D66">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2405,16 +2411,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C67">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D67">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2425,16 +2431,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C68">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D68">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2445,16 +2451,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="C69">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D69">
-        <v>431</v>
+        <v>372</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2465,16 +2471,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>770</v>
+        <v>639</v>
       </c>
       <c r="C70">
-        <v>673</v>
+        <v>735</v>
       </c>
       <c r="D70">
-        <v>1443</v>
+        <v>1374</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2485,16 +2491,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>777</v>
+        <v>659</v>
       </c>
       <c r="C71">
-        <v>695</v>
+        <v>767</v>
       </c>
       <c r="D71">
-        <v>1472</v>
+        <v>1426</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2505,16 +2511,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>836</v>
+        <v>659</v>
       </c>
       <c r="C72">
-        <v>739</v>
+        <v>764</v>
       </c>
       <c r="D72">
-        <v>1575</v>
+        <v>1423</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2525,16 +2531,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>848</v>
+        <v>665</v>
       </c>
       <c r="C73">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="D73">
-        <v>1585</v>
+        <v>1429</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2545,16 +2551,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>840</v>
+        <v>663</v>
       </c>
       <c r="C74">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="D74">
-        <v>1583</v>
+        <v>1436</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2565,16 +2571,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>868</v>
+        <v>663</v>
       </c>
       <c r="C75">
-        <v>727</v>
+        <v>776</v>
       </c>
       <c r="D75">
-        <v>1595</v>
+        <v>1439</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2585,16 +2591,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>851</v>
+        <v>663</v>
       </c>
       <c r="C76">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="D76">
-        <v>1604</v>
+        <v>1439</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2605,16 +2611,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>852</v>
+        <v>674</v>
       </c>
       <c r="C77">
-        <v>743</v>
+        <v>779</v>
       </c>
       <c r="D77">
-        <v>1595</v>
+        <v>1453</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2625,16 +2631,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>850</v>
+        <v>687</v>
       </c>
       <c r="C78">
-        <v>715</v>
+        <v>769</v>
       </c>
       <c r="D78">
-        <v>1565</v>
+        <v>1456</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2645,16 +2651,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>853</v>
+        <v>693</v>
       </c>
       <c r="C79">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="D79">
-        <v>1566</v>
+        <v>1462</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2665,16 +2671,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>852</v>
+        <v>702</v>
       </c>
       <c r="C80">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="D80">
-        <v>1565</v>
+        <v>1471</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2685,16 +2691,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>858</v>
+        <v>733</v>
       </c>
       <c r="C81">
-        <v>715</v>
+        <v>770</v>
       </c>
       <c r="D81">
-        <v>1573</v>
+        <v>1503</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2705,16 +2711,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>833</v>
+        <v>734</v>
       </c>
       <c r="C82">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="D82">
-        <v>1562</v>
+        <v>1495</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2725,16 +2731,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>828</v>
+        <v>736</v>
       </c>
       <c r="C83">
-        <v>730</v>
+        <v>761</v>
       </c>
       <c r="D83">
-        <v>1558</v>
+        <v>1497</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2745,16 +2751,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>829</v>
+        <v>728</v>
       </c>
       <c r="C84">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="D84">
-        <v>1559</v>
+        <v>1490</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2765,16 +2771,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>829</v>
+        <v>729</v>
       </c>
       <c r="C85">
-        <v>730</v>
+        <v>759</v>
       </c>
       <c r="D85">
-        <v>1559</v>
+        <v>1488</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2785,16 +2791,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>796</v>
+        <v>606</v>
       </c>
       <c r="C86">
-        <v>719</v>
+        <v>758</v>
       </c>
       <c r="D86">
-        <v>1515</v>
+        <v>1364</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2805,16 +2811,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>786</v>
+        <v>604</v>
       </c>
       <c r="C87">
-        <v>718</v>
+        <v>757</v>
       </c>
       <c r="D87">
-        <v>1504</v>
+        <v>1361</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2825,16 +2831,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>787</v>
+        <v>603</v>
       </c>
       <c r="C88">
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="D88">
-        <v>1504</v>
+        <v>1361</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2845,16 +2851,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>780</v>
+        <v>594</v>
       </c>
       <c r="C89">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="D89">
-        <v>1498</v>
+        <v>1346</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2865,16 +2871,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>548</v>
+        <v>157</v>
       </c>
       <c r="C90">
-        <v>807</v>
+        <v>392</v>
       </c>
       <c r="D90">
-        <v>1355</v>
+        <v>549</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2885,16 +2891,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>549</v>
+        <v>136</v>
       </c>
       <c r="C91">
-        <v>812</v>
+        <v>364</v>
       </c>
       <c r="D91">
-        <v>1361</v>
+        <v>500</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2905,16 +2911,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>547</v>
+        <v>135</v>
       </c>
       <c r="C92">
-        <v>810</v>
+        <v>364</v>
       </c>
       <c r="D92">
-        <v>1357</v>
+        <v>499</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2925,16 +2931,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>539</v>
+        <v>135</v>
       </c>
       <c r="C93">
-        <v>808</v>
+        <v>362</v>
       </c>
       <c r="D93">
-        <v>1347</v>
+        <v>497</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2945,16 +2951,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="C94">
-        <v>800</v>
+        <v>301</v>
       </c>
       <c r="D94">
-        <v>1265</v>
+        <v>386</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2965,16 +2971,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="C95">
-        <v>810</v>
+        <v>292</v>
       </c>
       <c r="D95">
-        <v>1266</v>
+        <v>375</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2985,16 +2991,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="C96">
-        <v>902</v>
+        <v>304</v>
       </c>
       <c r="D96">
-        <v>1380</v>
+        <v>387</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3005,16 +3011,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="C97">
-        <v>902</v>
+        <v>305</v>
       </c>
       <c r="D97">
-        <v>1376</v>
+        <v>383</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3025,16 +3031,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="C98">
-        <v>430</v>
+        <v>275</v>
       </c>
       <c r="D98">
-        <v>637</v>
+        <v>352</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3045,16 +3051,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="C99">
-        <v>383</v>
+        <v>274</v>
       </c>
       <c r="D99">
-        <v>563</v>
+        <v>350</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3065,16 +3071,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C100">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D100">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3085,16 +3091,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="C101">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D101">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3105,16 +3111,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="C102">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="D102">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3125,16 +3131,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C103">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="D103">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3145,16 +3151,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C104">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="D104">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3165,16 +3171,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C105">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="D105">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3185,16 +3191,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C106">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="D106">
-        <v>394</v>
+        <v>330</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3205,16 +3211,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C107">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="D107">
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3225,16 +3231,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C108">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="D108">
-        <v>393</v>
+        <v>328</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3245,16 +3251,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C109">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="D109">
-        <v>395</v>
+        <v>328</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3265,16 +3271,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C110">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="D110">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3285,16 +3291,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C111">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D111">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3305,16 +3311,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C112">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="D112">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3325,16 +3331,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C113">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="D113">
-        <v>397</v>
+        <v>332</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3345,16 +3351,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C114">
-        <v>389</v>
+        <v>283</v>
       </c>
       <c r="D114">
-        <v>504</v>
+        <v>359</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3365,16 +3371,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C115">
-        <v>391</v>
+        <v>285</v>
       </c>
       <c r="D115">
-        <v>507</v>
+        <v>360</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3385,16 +3391,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C116">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="D116">
-        <v>507</v>
+        <v>360</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3405,16 +3411,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="C117">
-        <v>391</v>
+        <v>285</v>
       </c>
       <c r="D117">
-        <v>510</v>
+        <v>366</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3425,16 +3431,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="C118">
-        <v>419</v>
+        <v>292</v>
       </c>
       <c r="D118">
-        <v>548</v>
+        <v>468</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3445,16 +3451,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C119">
-        <v>422</v>
+        <v>291</v>
       </c>
       <c r="D119">
-        <v>553</v>
+        <v>404</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3465,16 +3471,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C120">
-        <v>413</v>
+        <v>291</v>
       </c>
       <c r="D120">
-        <v>543</v>
+        <v>410</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3485,16 +3491,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C121">
-        <v>414</v>
+        <v>306</v>
       </c>
       <c r="D121">
-        <v>545</v>
+        <v>467</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3505,16 +3511,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>154</v>
+        <v>627</v>
       </c>
       <c r="C122">
-        <v>412</v>
+        <v>695</v>
       </c>
       <c r="D122">
-        <v>566</v>
+        <v>1322</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3525,16 +3531,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>153</v>
+        <v>652</v>
       </c>
       <c r="C123">
-        <v>409</v>
+        <v>722</v>
       </c>
       <c r="D123">
-        <v>562</v>
+        <v>1374</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3545,16 +3551,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>151</v>
+        <v>647</v>
       </c>
       <c r="C124">
-        <v>410</v>
+        <v>722</v>
       </c>
       <c r="D124">
-        <v>561</v>
+        <v>1369</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3565,16 +3571,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>148</v>
+        <v>654</v>
       </c>
       <c r="C125">
-        <v>409</v>
+        <v>727</v>
       </c>
       <c r="D125">
-        <v>557</v>
+        <v>1381</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3585,16 +3591,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>115</v>
+        <v>668</v>
       </c>
       <c r="C126">
-        <v>299</v>
+        <v>722</v>
       </c>
       <c r="D126">
-        <v>414</v>
+        <v>1390</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3605,16 +3611,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>112</v>
+        <v>659</v>
       </c>
       <c r="C127">
-        <v>293</v>
+        <v>725</v>
       </c>
       <c r="D127">
-        <v>405</v>
+        <v>1384</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3625,16 +3631,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>112</v>
+        <v>644</v>
       </c>
       <c r="C128">
-        <v>300</v>
+        <v>727</v>
       </c>
       <c r="D128">
-        <v>412</v>
+        <v>1371</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3645,16 +3651,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>108</v>
+        <v>643</v>
       </c>
       <c r="C129">
-        <v>300</v>
+        <v>722</v>
       </c>
       <c r="D129">
-        <v>408</v>
+        <v>1365</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3665,16 +3671,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="C130">
-        <v>275</v>
+        <v>708</v>
       </c>
       <c r="D130">
-        <v>355</v>
+        <v>1165</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3685,16 +3691,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>75</v>
+        <v>449</v>
       </c>
       <c r="C131">
-        <v>273</v>
+        <v>704</v>
       </c>
       <c r="D131">
-        <v>348</v>
+        <v>1153</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3705,16 +3711,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>73</v>
+        <v>450</v>
       </c>
       <c r="C132">
-        <v>273</v>
+        <v>705</v>
       </c>
       <c r="D132">
-        <v>346</v>
+        <v>1155</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3725,16 +3731,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>72</v>
+        <v>442</v>
       </c>
       <c r="C133">
-        <v>271</v>
+        <v>705</v>
       </c>
       <c r="D133">
-        <v>343</v>
+        <v>1147</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3745,16 +3751,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="C134">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="D134">
-        <v>319</v>
+        <v>481</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3765,16 +3771,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="C135">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D135">
-        <v>316</v>
+        <v>407</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3785,16 +3791,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="C136">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D136">
-        <v>305</v>
+        <v>407</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3805,16 +3811,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="C137">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D137">
-        <v>306</v>
+        <v>404</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3825,16 +3831,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C138">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D138">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3845,16 +3851,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C139">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="D139">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3865,16 +3871,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C140">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D140">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3885,16 +3891,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C141">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="D141">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3905,16 +3911,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C142">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D142">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3925,16 +3931,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="C143">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D143">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3945,16 +3951,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="C144">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D144">
-        <v>343</v>
+        <v>388</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3965,16 +3971,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C145">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D145">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3985,16 +3991,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C146">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D146">
-        <v>339</v>
+        <v>277</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4005,16 +4011,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C147">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D147">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4025,16 +4031,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C148">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="D148">
-        <v>339</v>
+        <v>269</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4045,16 +4051,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C149">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="D149">
-        <v>340</v>
+        <v>271</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4065,16 +4071,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C150">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D150">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4085,16 +4091,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C151">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D151">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4105,16 +4111,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="C152">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D152">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4125,16 +4131,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="C153">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D153">
-        <v>362</v>
+        <v>307</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4145,16 +4151,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="C154">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="D154">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4165,16 +4171,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="C155">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D155">
-        <v>354</v>
+        <v>307</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4185,16 +4191,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C156">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D156">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4205,16 +4211,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C157">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D157">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4225,16 +4231,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C158">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="D158">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4245,16 +4251,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C159">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="D159">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4265,16 +4271,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C160">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="D160">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4285,16 +4291,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C161">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="D161">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4305,16 +4311,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="C162">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="D162">
-        <v>390</v>
+        <v>276</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4325,16 +4331,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="C163">
+        <v>222</v>
+      </c>
+      <c r="D163">
         <v>298</v>
-      </c>
-      <c r="D163">
-        <v>397</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4345,16 +4351,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C164">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="D164">
-        <v>399</v>
+        <v>312</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4365,16 +4371,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="C165">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D165">
-        <v>410</v>
+        <v>489</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4385,16 +4391,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>224</v>
+        <v>641</v>
       </c>
       <c r="C166">
-        <v>443</v>
+        <v>534</v>
       </c>
       <c r="D166">
-        <v>667</v>
+        <v>1175</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4405,16 +4411,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>226</v>
+        <v>724</v>
       </c>
       <c r="C167">
-        <v>457</v>
+        <v>566</v>
       </c>
       <c r="D167">
-        <v>683</v>
+        <v>1290</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4425,16 +4431,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>223</v>
+        <v>823</v>
       </c>
       <c r="C168">
-        <v>459</v>
+        <v>576</v>
       </c>
       <c r="D168">
-        <v>682</v>
+        <v>1399</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4445,16 +4451,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>253</v>
+        <v>853</v>
       </c>
       <c r="C169">
-        <v>464</v>
+        <v>749</v>
       </c>
       <c r="D169">
-        <v>717</v>
+        <v>1602</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4465,16 +4471,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>467</v>
+        <v>1197</v>
       </c>
       <c r="C170">
-        <v>678</v>
+        <v>890</v>
       </c>
       <c r="D170">
-        <v>1145</v>
+        <v>2087</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4485,16 +4491,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>470</v>
+        <v>1225</v>
       </c>
       <c r="C171">
-        <v>696</v>
+        <v>856</v>
       </c>
       <c r="D171">
-        <v>1166</v>
+        <v>2081</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4505,16 +4511,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>471</v>
+        <v>1226</v>
       </c>
       <c r="C172">
-        <v>694</v>
+        <v>856</v>
       </c>
       <c r="D172">
-        <v>1165</v>
+        <v>2082</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4525,16 +4531,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>471</v>
+        <v>1230</v>
       </c>
       <c r="C173">
-        <v>695</v>
+        <v>853</v>
       </c>
       <c r="D173">
-        <v>1166</v>
+        <v>2083</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4545,16 +4551,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>445</v>
+        <v>1227</v>
       </c>
       <c r="C174">
-        <v>636</v>
+        <v>747</v>
       </c>
       <c r="D174">
-        <v>1081</v>
+        <v>1974</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4565,16 +4571,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>444</v>
+        <v>1226</v>
       </c>
       <c r="C175">
-        <v>632</v>
+        <v>746</v>
       </c>
       <c r="D175">
-        <v>1076</v>
+        <v>1972</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4585,16 +4591,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>443</v>
+        <v>1131</v>
       </c>
       <c r="C176">
-        <v>633</v>
+        <v>746</v>
       </c>
       <c r="D176">
-        <v>1076</v>
+        <v>1877</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4605,16 +4611,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>441</v>
+        <v>1114</v>
       </c>
       <c r="C177">
-        <v>631</v>
+        <v>745</v>
       </c>
       <c r="D177">
-        <v>1072</v>
+        <v>1859</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4625,16 +4631,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>334</v>
+        <v>780</v>
       </c>
       <c r="C178">
-        <v>631</v>
+        <v>675</v>
       </c>
       <c r="D178">
-        <v>965</v>
+        <v>1455</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4645,16 +4651,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>332</v>
+        <v>775</v>
       </c>
       <c r="C179">
-        <v>630</v>
+        <v>678</v>
       </c>
       <c r="D179">
-        <v>962</v>
+        <v>1453</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4665,16 +4671,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>332</v>
+        <v>668</v>
       </c>
       <c r="C180">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D180">
-        <v>963</v>
+        <v>1304</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4685,16 +4691,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>337</v>
+        <v>648</v>
       </c>
       <c r="C181">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D181">
-        <v>965</v>
+        <v>1275</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4705,16 +4711,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="C182">
-        <v>566</v>
+        <v>498</v>
       </c>
       <c r="D182">
-        <v>914</v>
+        <v>694</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4725,16 +4731,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="C183">
-        <v>561</v>
+        <v>487</v>
       </c>
       <c r="D183">
-        <v>911</v>
+        <v>662</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4745,16 +4751,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="C184">
-        <v>564</v>
+        <v>487</v>
       </c>
       <c r="D184">
-        <v>917</v>
+        <v>652</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4765,16 +4771,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>350</v>
+        <v>167</v>
       </c>
       <c r="C185">
-        <v>560</v>
+        <v>483</v>
       </c>
       <c r="D185">
-        <v>910</v>
+        <v>650</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4785,16 +4791,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>294</v>
+        <v>102</v>
       </c>
       <c r="C186">
-        <v>580</v>
+        <v>327</v>
       </c>
       <c r="D186">
-        <v>874</v>
+        <v>429</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4805,16 +4811,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>287</v>
+        <v>91</v>
       </c>
       <c r="C187">
-        <v>577</v>
+        <v>303</v>
       </c>
       <c r="D187">
-        <v>864</v>
+        <v>394</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4825,16 +4831,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>289</v>
+        <v>86</v>
       </c>
       <c r="C188">
-        <v>579</v>
+        <v>313</v>
       </c>
       <c r="D188">
-        <v>868</v>
+        <v>399</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4845,16 +4851,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>293</v>
+        <v>87</v>
       </c>
       <c r="C189">
-        <v>575</v>
+        <v>312</v>
       </c>
       <c r="D189">
-        <v>868</v>
+        <v>399</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4865,16 +4871,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>208</v>
+        <v>52</v>
       </c>
       <c r="C190">
-        <v>563</v>
+        <v>285</v>
       </c>
       <c r="D190">
-        <v>771</v>
+        <v>337</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4885,16 +4891,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="C191">
-        <v>560</v>
+        <v>281</v>
       </c>
       <c r="D191">
-        <v>768</v>
+        <v>320</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4905,16 +4911,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="C192">
-        <v>562</v>
+        <v>282</v>
       </c>
       <c r="D192">
-        <v>765</v>
+        <v>321</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4925,16 +4931,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="C193">
-        <v>564</v>
+        <v>277</v>
       </c>
       <c r="D193">
-        <v>788</v>
+        <v>315</v>
       </c>
       <c r="E193">
         <v>96</v>
@@ -4945,16 +4951,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>560</v>
+        <v>38</v>
       </c>
       <c r="C194">
-        <v>616</v>
+        <v>229</v>
       </c>
       <c r="D194">
-        <v>1176</v>
+        <v>267</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -4965,16 +4971,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>566</v>
+        <v>40</v>
       </c>
       <c r="C195">
-        <v>616</v>
+        <v>231</v>
       </c>
       <c r="D195">
-        <v>1182</v>
+        <v>271</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -4985,16 +4991,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>566</v>
+        <v>39</v>
       </c>
       <c r="C196">
-        <v>617</v>
+        <v>230</v>
       </c>
       <c r="D196">
-        <v>1183</v>
+        <v>269</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -5005,16 +5011,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>582</v>
+        <v>38</v>
       </c>
       <c r="C197">
-        <v>617</v>
+        <v>229</v>
       </c>
       <c r="D197">
-        <v>1199</v>
+        <v>267</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -5025,16 +5031,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>655</v>
+        <v>38</v>
       </c>
       <c r="C198">
-        <v>518</v>
+        <v>227</v>
       </c>
       <c r="D198">
-        <v>1173</v>
+        <v>265</v>
       </c>
       <c r="E198">
         <v>5</v>
@@ -5045,16 +5051,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>655</v>
+        <v>39</v>
       </c>
       <c r="C199">
-        <v>503</v>
+        <v>227</v>
       </c>
       <c r="D199">
-        <v>1158</v>
+        <v>266</v>
       </c>
       <c r="E199">
         <v>6</v>
@@ -5065,16 +5071,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>655</v>
+        <v>39</v>
       </c>
       <c r="C200">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="D200">
-        <v>1157</v>
+        <v>266</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -5085,16 +5091,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>655</v>
+        <v>38</v>
       </c>
       <c r="C201">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="D201">
-        <v>1157</v>
+        <v>265</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5105,16 +5111,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C202">
-        <v>502</v>
+        <v>220</v>
       </c>
       <c r="D202">
-        <v>1108</v>
+        <v>259</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -5125,16 +5131,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>606</v>
+        <v>38</v>
       </c>
       <c r="C203">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D203">
-        <v>1108</v>
+        <v>257</v>
       </c>
       <c r="E203">
         <v>10</v>
@@ -5145,16 +5151,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C204">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D204">
-        <v>1108</v>
+        <v>258</v>
       </c>
       <c r="E204">
         <v>11</v>
@@ -5165,16 +5171,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C205">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D205">
-        <v>1108</v>
+        <v>258</v>
       </c>
       <c r="E205">
         <v>12</v>
@@ -5185,16 +5191,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="C206">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="D206">
-        <v>1109</v>
+        <v>262</v>
       </c>
       <c r="E206">
         <v>13</v>
@@ -5205,16 +5211,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>606</v>
+        <v>37</v>
       </c>
       <c r="C207">
-        <v>501</v>
+        <v>224</v>
       </c>
       <c r="D207">
-        <v>1107</v>
+        <v>261</v>
       </c>
       <c r="E207">
         <v>14</v>
@@ -5225,16 +5231,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="C208">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="D208">
-        <v>1109</v>
+        <v>262</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5245,16 +5251,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>606</v>
+        <v>38</v>
       </c>
       <c r="C209">
-        <v>501</v>
+        <v>224</v>
       </c>
       <c r="D209">
-        <v>1107</v>
+        <v>262</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5265,16 +5271,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>589</v>
+        <v>39</v>
       </c>
       <c r="C210">
-        <v>510</v>
+        <v>225</v>
       </c>
       <c r="D210">
-        <v>1099</v>
+        <v>264</v>
       </c>
       <c r="E210">
         <v>17</v>
@@ -5285,16 +5291,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>588</v>
+        <v>39</v>
       </c>
       <c r="C211">
-        <v>515</v>
+        <v>244</v>
       </c>
       <c r="D211">
-        <v>1103</v>
+        <v>283</v>
       </c>
       <c r="E211">
         <v>18</v>
@@ -5305,16 +5311,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>588</v>
+        <v>39</v>
       </c>
       <c r="C212">
-        <v>515</v>
+        <v>245</v>
       </c>
       <c r="D212">
-        <v>1103</v>
+        <v>284</v>
       </c>
       <c r="E212">
         <v>19</v>
@@ -5325,16 +5331,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>590</v>
+        <v>44</v>
       </c>
       <c r="C213">
-        <v>515</v>
+        <v>246</v>
       </c>
       <c r="D213">
-        <v>1105</v>
+        <v>290</v>
       </c>
       <c r="E213">
         <v>20</v>
@@ -5345,16 +5351,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>437</v>
+        <v>91</v>
       </c>
       <c r="C214">
-        <v>475</v>
+        <v>297</v>
       </c>
       <c r="D214">
-        <v>912</v>
+        <v>388</v>
       </c>
       <c r="E214">
         <v>21</v>
@@ -5365,16 +5371,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>435</v>
+        <v>94</v>
       </c>
       <c r="C215">
-        <v>471</v>
+        <v>297</v>
       </c>
       <c r="D215">
-        <v>906</v>
+        <v>391</v>
       </c>
       <c r="E215">
         <v>22</v>
@@ -5385,16 +5391,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="C216">
-        <v>471</v>
+        <v>298</v>
       </c>
       <c r="D216">
-        <v>903</v>
+        <v>394</v>
       </c>
       <c r="E216">
         <v>23</v>
@@ -5405,16 +5411,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>436</v>
+        <v>115</v>
       </c>
       <c r="C217">
-        <v>471</v>
+        <v>302</v>
       </c>
       <c r="D217">
-        <v>907</v>
+        <v>417</v>
       </c>
       <c r="E217">
         <v>24</v>
@@ -5425,16 +5431,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="C218">
-        <v>512</v>
+        <v>600</v>
       </c>
       <c r="D218">
-        <v>1120</v>
+        <v>765</v>
       </c>
       <c r="E218">
         <v>25</v>
@@ -5445,16 +5451,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>620</v>
+        <v>160</v>
       </c>
       <c r="C219">
-        <v>513</v>
+        <v>649</v>
       </c>
       <c r="D219">
-        <v>1133</v>
+        <v>809</v>
       </c>
       <c r="E219">
         <v>26</v>
@@ -5465,16 +5471,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>632</v>
+        <v>158</v>
       </c>
       <c r="C220">
-        <v>513</v>
+        <v>643</v>
       </c>
       <c r="D220">
-        <v>1145</v>
+        <v>801</v>
       </c>
       <c r="E220">
         <v>27</v>
@@ -5485,16 +5491,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>620</v>
+        <v>158</v>
       </c>
       <c r="C221">
-        <v>511</v>
+        <v>645</v>
       </c>
       <c r="D221">
-        <v>1131</v>
+        <v>803</v>
       </c>
       <c r="E221">
         <v>28</v>
@@ -5505,16 +5511,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C222">
-        <v>276</v>
+        <v>623</v>
       </c>
       <c r="D222">
-        <v>393</v>
+        <v>776</v>
       </c>
       <c r="E222">
         <v>29</v>
@@ -5525,16 +5531,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="C223">
-        <v>254</v>
+        <v>636</v>
       </c>
       <c r="D223">
-        <v>351</v>
+        <v>813</v>
       </c>
       <c r="E223">
         <v>30</v>
@@ -5545,16 +5551,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>89</v>
+        <v>279</v>
       </c>
       <c r="C224">
-        <v>254</v>
+        <v>638</v>
       </c>
       <c r="D224">
-        <v>343</v>
+        <v>917</v>
       </c>
       <c r="E224">
         <v>31</v>
@@ -5565,16 +5571,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>86</v>
+        <v>303</v>
       </c>
       <c r="C225">
-        <v>254</v>
+        <v>637</v>
       </c>
       <c r="D225">
-        <v>340</v>
+        <v>940</v>
       </c>
       <c r="E225">
         <v>32</v>
@@ -5585,16 +5591,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>74</v>
+        <v>377</v>
       </c>
       <c r="C226">
-        <v>246</v>
+        <v>461</v>
       </c>
       <c r="D226">
-        <v>320</v>
+        <v>838</v>
       </c>
       <c r="E226">
         <v>33</v>
@@ -5605,16 +5611,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>73</v>
+        <v>394</v>
       </c>
       <c r="C227">
-        <v>244</v>
+        <v>418</v>
       </c>
       <c r="D227">
-        <v>317</v>
+        <v>812</v>
       </c>
       <c r="E227">
         <v>34</v>
@@ -5625,16 +5631,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>72</v>
+        <v>398</v>
       </c>
       <c r="C228">
-        <v>244</v>
+        <v>420</v>
       </c>
       <c r="D228">
-        <v>316</v>
+        <v>818</v>
       </c>
       <c r="E228">
         <v>35</v>
@@ -5645,16 +5651,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>71</v>
+        <v>362</v>
       </c>
       <c r="C229">
-        <v>245</v>
+        <v>417</v>
       </c>
       <c r="D229">
-        <v>316</v>
+        <v>779</v>
       </c>
       <c r="E229">
         <v>36</v>
@@ -5665,22 +5671,62 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>88</v>
+        <v>390</v>
       </c>
       <c r="C230">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="D230">
-        <v>329</v>
+        <v>709</v>
       </c>
       <c r="E230">
         <v>37</v>
       </c>
       <c r="F230" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46295.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>400</v>
+      </c>
+      <c r="C231">
+        <v>310</v>
+      </c>
+      <c r="D231">
+        <v>710</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>401</v>
+      </c>
+      <c r="C232">
+        <v>313</v>
+      </c>
+      <c r="D232">
+        <v>714</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -428,6 +140,291 @@
   </si>
   <si>
     <t>08.10.202636</t>
+  </si>
+  <si>
+    <t>08.10.202637</t>
+  </si>
+  <si>
+    <t>08.10.202638</t>
+  </si>
+  <si>
+    <t>08.10.202639</t>
+  </si>
+  <si>
+    <t>08.10.202640</t>
+  </si>
+  <si>
+    <t>08.10.202641</t>
+  </si>
+  <si>
+    <t>08.10.202642</t>
+  </si>
+  <si>
+    <t>08.10.202643</t>
+  </si>
+  <si>
+    <t>08.10.202644</t>
+  </si>
+  <si>
+    <t>08.10.202645</t>
+  </si>
+  <si>
+    <t>08.10.202646</t>
+  </si>
+  <si>
+    <t>08.10.202647</t>
+  </si>
+  <si>
+    <t>08.10.202648</t>
+  </si>
+  <si>
+    <t>08.10.202649</t>
+  </si>
+  <si>
+    <t>08.10.202650</t>
+  </si>
+  <si>
+    <t>08.10.202651</t>
+  </si>
+  <si>
+    <t>08.10.202652</t>
+  </si>
+  <si>
+    <t>08.10.202653</t>
+  </si>
+  <si>
+    <t>08.10.202654</t>
+  </si>
+  <si>
+    <t>08.10.202655</t>
+  </si>
+  <si>
+    <t>08.10.202656</t>
+  </si>
+  <si>
+    <t>08.10.202657</t>
+  </si>
+  <si>
+    <t>08.10.202658</t>
+  </si>
+  <si>
+    <t>08.10.202659</t>
+  </si>
+  <si>
+    <t>08.10.202660</t>
+  </si>
+  <si>
+    <t>08.10.202661</t>
+  </si>
+  <si>
+    <t>08.10.202662</t>
+  </si>
+  <si>
+    <t>08.10.202663</t>
+  </si>
+  <si>
+    <t>08.10.202664</t>
+  </si>
+  <si>
+    <t>08.10.202665</t>
+  </si>
+  <si>
+    <t>08.10.202666</t>
+  </si>
+  <si>
+    <t>08.10.202667</t>
+  </si>
+  <si>
+    <t>08.10.202668</t>
+  </si>
+  <si>
+    <t>08.10.202669</t>
+  </si>
+  <si>
+    <t>08.10.202670</t>
+  </si>
+  <si>
+    <t>08.10.202671</t>
+  </si>
+  <si>
+    <t>08.10.202672</t>
+  </si>
+  <si>
+    <t>08.10.202673</t>
+  </si>
+  <si>
+    <t>08.10.202674</t>
+  </si>
+  <si>
+    <t>08.10.202675</t>
+  </si>
+  <si>
+    <t>08.10.202676</t>
+  </si>
+  <si>
+    <t>08.10.202677</t>
+  </si>
+  <si>
+    <t>08.10.202678</t>
+  </si>
+  <si>
+    <t>08.10.202679</t>
+  </si>
+  <si>
+    <t>08.10.202680</t>
+  </si>
+  <si>
+    <t>08.10.202681</t>
+  </si>
+  <si>
+    <t>08.10.202682</t>
+  </si>
+  <si>
+    <t>08.10.202683</t>
+  </si>
+  <si>
+    <t>08.10.202684</t>
+  </si>
+  <si>
+    <t>08.10.202685</t>
+  </si>
+  <si>
+    <t>08.10.202686</t>
+  </si>
+  <si>
+    <t>08.10.202687</t>
+  </si>
+  <si>
+    <t>08.10.202688</t>
+  </si>
+  <si>
+    <t>08.10.202689</t>
+  </si>
+  <si>
+    <t>08.10.202690</t>
+  </si>
+  <si>
+    <t>08.10.202691</t>
+  </si>
+  <si>
+    <t>08.10.202692</t>
+  </si>
+  <si>
+    <t>08.10.202693</t>
+  </si>
+  <si>
+    <t>08.10.202694</t>
+  </si>
+  <si>
+    <t>08.10.202695</t>
+  </si>
+  <si>
+    <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
   </si>
 </sst>
 </file>
@@ -789,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -814,16 +811,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="C2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D2">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -834,16 +831,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="C3">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="D3">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -854,16 +851,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="C4">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D4">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -874,16 +871,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="C5">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D5">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -894,16 +891,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>325</v>
+        <v>827</v>
       </c>
       <c r="C6">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="D6">
-        <v>550</v>
+        <v>1111</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -914,16 +911,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>305</v>
+        <v>837</v>
       </c>
       <c r="C7">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="D7">
-        <v>564</v>
+        <v>1123</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -934,16 +931,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>304</v>
+        <v>837</v>
       </c>
       <c r="C8">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="D8">
-        <v>562</v>
+        <v>1123</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -954,16 +951,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>313</v>
+        <v>835</v>
       </c>
       <c r="C9">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="D9">
-        <v>571</v>
+        <v>1120</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -974,16 +971,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>314</v>
+        <v>833</v>
       </c>
       <c r="C10">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="D10">
-        <v>573</v>
+        <v>1119</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -994,16 +991,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>299</v>
+        <v>842</v>
       </c>
       <c r="C11">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="D11">
-        <v>518</v>
+        <v>1128</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1014,16 +1011,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>297</v>
+        <v>837</v>
       </c>
       <c r="C12">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="D12">
-        <v>514</v>
+        <v>1122</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1034,16 +1031,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>298</v>
+        <v>837</v>
       </c>
       <c r="C13">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="D13">
-        <v>515</v>
+        <v>1121</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1054,16 +1051,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>298</v>
+        <v>838</v>
       </c>
       <c r="C14">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="D14">
-        <v>515</v>
+        <v>1123</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1074,16 +1071,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>298</v>
+        <v>836</v>
       </c>
       <c r="C15">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="D15">
-        <v>515</v>
+        <v>1120</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1094,16 +1091,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>298</v>
+        <v>842</v>
       </c>
       <c r="C16">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="D16">
-        <v>515</v>
+        <v>1126</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1114,16 +1111,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>299</v>
+        <v>847</v>
       </c>
       <c r="C17">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="D17">
-        <v>516</v>
+        <v>1131</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1134,16 +1131,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>299</v>
+        <v>870</v>
       </c>
       <c r="C18">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="D18">
-        <v>524</v>
+        <v>1151</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1154,16 +1151,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>302</v>
+        <v>870</v>
       </c>
       <c r="C19">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="D19">
-        <v>527</v>
+        <v>1150</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1174,16 +1171,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>300</v>
+        <v>870</v>
       </c>
       <c r="C20">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="D20">
-        <v>525</v>
+        <v>1165</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1194,16 +1191,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>315</v>
+        <v>871</v>
       </c>
       <c r="C21">
-        <v>236</v>
+        <v>299</v>
       </c>
       <c r="D21">
-        <v>551</v>
+        <v>1170</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1214,16 +1211,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>631</v>
+        <v>795</v>
       </c>
       <c r="C22">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="D22">
-        <v>1065</v>
+        <v>1242</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1234,16 +1231,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>639</v>
+        <v>799</v>
       </c>
       <c r="C23">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D23">
-        <v>1082</v>
+        <v>1255</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1254,16 +1251,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>652</v>
+        <v>819</v>
       </c>
       <c r="C24">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D24">
-        <v>1095</v>
+        <v>1272</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1274,16 +1271,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>673</v>
+        <v>810</v>
       </c>
       <c r="C25">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D25">
-        <v>1123</v>
+        <v>1267</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1294,16 +1291,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>869</v>
+        <v>783</v>
       </c>
       <c r="C26">
-        <v>579</v>
+        <v>643</v>
       </c>
       <c r="D26">
-        <v>1448</v>
+        <v>1426</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1314,16 +1311,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>909</v>
+        <v>778</v>
       </c>
       <c r="C27">
-        <v>582</v>
+        <v>656</v>
       </c>
       <c r="D27">
-        <v>1491</v>
+        <v>1434</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1334,16 +1331,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>890</v>
+        <v>775</v>
       </c>
       <c r="C28">
-        <v>582</v>
+        <v>638</v>
       </c>
       <c r="D28">
-        <v>1472</v>
+        <v>1413</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1354,16 +1351,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>860</v>
+        <v>778</v>
       </c>
       <c r="C29">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="D29">
-        <v>1443</v>
+        <v>1422</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1374,16 +1371,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>967</v>
+        <v>759</v>
       </c>
       <c r="C30">
-        <v>559</v>
+        <v>695</v>
       </c>
       <c r="D30">
-        <v>1526</v>
+        <v>1454</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1394,16 +1391,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>953</v>
+        <v>750</v>
       </c>
       <c r="C31">
-        <v>558</v>
+        <v>681</v>
       </c>
       <c r="D31">
-        <v>1511</v>
+        <v>1431</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1414,16 +1411,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>926</v>
+        <v>751</v>
       </c>
       <c r="C32">
-        <v>553</v>
+        <v>702</v>
       </c>
       <c r="D32">
-        <v>1479</v>
+        <v>1453</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1434,16 +1431,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>922</v>
+        <v>752</v>
       </c>
       <c r="C33">
-        <v>551</v>
+        <v>702</v>
       </c>
       <c r="D33">
-        <v>1473</v>
+        <v>1454</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1454,16 +1451,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>837</v>
+        <v>727</v>
       </c>
       <c r="C34">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="D34">
-        <v>1407</v>
+        <v>1385</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1474,16 +1471,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>831</v>
+        <v>887</v>
       </c>
       <c r="C35">
-        <v>570</v>
+        <v>681</v>
       </c>
       <c r="D35">
-        <v>1401</v>
+        <v>1568</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1494,16 +1491,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>832</v>
+        <v>888</v>
       </c>
       <c r="C36">
-        <v>573</v>
+        <v>682</v>
       </c>
       <c r="D36">
-        <v>1405</v>
+        <v>1570</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1514,16 +1511,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>819</v>
+        <v>859</v>
       </c>
       <c r="C37">
-        <v>573</v>
+        <v>678</v>
       </c>
       <c r="D37">
-        <v>1392</v>
+        <v>1537</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1534,16 +1531,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>457</v>
+        <v>317</v>
       </c>
       <c r="C38">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="D38">
-        <v>819</v>
+        <v>601</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1554,16 +1551,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>448</v>
+        <v>247</v>
       </c>
       <c r="C39">
-        <v>338</v>
+        <v>221</v>
       </c>
       <c r="D39">
-        <v>786</v>
+        <v>468</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1574,16 +1571,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>447</v>
+        <v>87</v>
       </c>
       <c r="C40">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="D40">
-        <v>786</v>
+        <v>283</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1594,16 +1591,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="C41">
-        <v>337</v>
+        <v>194</v>
       </c>
       <c r="D41">
-        <v>782</v>
+        <v>277</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1614,16 +1611,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="C42">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D42">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1634,16 +1631,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D43">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1654,16 +1651,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C44">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D44">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1674,16 +1671,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C45">
         <v>206</v>
       </c>
       <c r="D45">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1694,16 +1691,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C46">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D46">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1714,16 +1711,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C47">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D47">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1734,16 +1731,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C48">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="D48">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1754,16 +1751,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C49">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="D49">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1774,16 +1771,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C50">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D50">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1794,16 +1791,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C51">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D51">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1814,16 +1811,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C52">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D52">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1834,16 +1831,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C53">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D53">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1854,16 +1851,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C54">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D54">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1874,16 +1871,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C55">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D55">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1894,16 +1891,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C56">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D56">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1914,16 +1911,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C57">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D57">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1934,16 +1931,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C58">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D58">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -1954,16 +1951,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C59">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D59">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -1974,16 +1971,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="C60">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D60">
-        <v>316</v>
+        <v>253</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -1994,16 +1991,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="C61">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D61">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2014,16 +2011,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C62">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D62">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2034,16 +2031,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C63">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D63">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2054,16 +2051,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C64">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D64">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2074,16 +2071,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="C65">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D65">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2094,16 +2091,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>207</v>
+        <v>592</v>
       </c>
       <c r="C66">
-        <v>234</v>
+        <v>416</v>
       </c>
       <c r="D66">
-        <v>441</v>
+        <v>1008</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2114,16 +2111,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>180</v>
+        <v>605</v>
       </c>
       <c r="C67">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D67">
-        <v>423</v>
+        <v>1026</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2134,16 +2131,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>249</v>
+        <v>608</v>
       </c>
       <c r="C68">
-        <v>243</v>
+        <v>442</v>
       </c>
       <c r="D68">
-        <v>492</v>
+        <v>1050</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2154,16 +2151,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>292</v>
+        <v>625</v>
       </c>
       <c r="C69">
-        <v>252</v>
+        <v>463</v>
       </c>
       <c r="D69">
-        <v>544</v>
+        <v>1088</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2174,16 +2171,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>1029</v>
+        <v>1055</v>
       </c>
       <c r="C70">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="D70">
-        <v>1507</v>
+        <v>1518</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2194,16 +2191,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C71">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="D71">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2214,16 +2211,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>1054</v>
+        <v>1114</v>
       </c>
       <c r="C72">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="D72">
-        <v>1545</v>
+        <v>1646</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2234,16 +2231,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>1051</v>
+        <v>1117</v>
       </c>
       <c r="C73">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D73">
-        <v>1586</v>
+        <v>1650</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2254,16 +2251,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>1068</v>
+        <v>1131</v>
       </c>
       <c r="C74">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="D74">
-        <v>1628</v>
+        <v>1660</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2274,16 +2271,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>1064</v>
+        <v>1130</v>
       </c>
       <c r="C75">
-        <v>563</v>
+        <v>532</v>
       </c>
       <c r="D75">
-        <v>1627</v>
+        <v>1662</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2294,16 +2291,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>1064</v>
+        <v>1139</v>
       </c>
       <c r="C76">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="D76">
-        <v>1574</v>
+        <v>1666</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2314,16 +2311,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>1067</v>
+        <v>1151</v>
       </c>
       <c r="C77">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="D77">
-        <v>1576</v>
+        <v>1681</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2334,16 +2331,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>948</v>
+        <v>905</v>
       </c>
       <c r="C78">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="D78">
-        <v>1549</v>
+        <v>1538</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2354,16 +2351,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>946</v>
+        <v>893</v>
       </c>
       <c r="C79">
-        <v>601</v>
+        <v>639</v>
       </c>
       <c r="D79">
-        <v>1547</v>
+        <v>1532</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2374,16 +2371,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>945</v>
+        <v>890</v>
       </c>
       <c r="C80">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="D80">
-        <v>1546</v>
+        <v>1517</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2394,16 +2391,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>943</v>
+        <v>891</v>
       </c>
       <c r="C81">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="D81">
-        <v>1543</v>
+        <v>1517</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2414,16 +2411,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>905</v>
+        <v>853</v>
       </c>
       <c r="C82">
-        <v>607</v>
+        <v>642</v>
       </c>
       <c r="D82">
-        <v>1512</v>
+        <v>1495</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2434,16 +2431,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>904</v>
+        <v>850</v>
       </c>
       <c r="C83">
-        <v>608</v>
+        <v>649</v>
       </c>
       <c r="D83">
-        <v>1512</v>
+        <v>1499</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2454,16 +2451,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>903</v>
+        <v>850</v>
       </c>
       <c r="C84">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="D84">
-        <v>1513</v>
+        <v>1499</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2474,16 +2471,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>906</v>
+        <v>855</v>
       </c>
       <c r="C85">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="D85">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2494,16 +2491,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C86">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="D86">
-        <v>1436</v>
+        <v>1424</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2514,16 +2511,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C87">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="D87">
-        <v>1432</v>
+        <v>1420</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2534,16 +2531,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C88">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="D88">
-        <v>1432</v>
+        <v>1406</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2554,16 +2551,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="C89">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D89">
-        <v>1426</v>
+        <v>1404</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2574,16 +2571,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="C90">
-        <v>586</v>
+        <v>540</v>
       </c>
       <c r="D90">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2594,16 +2591,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>703</v>
+        <v>741</v>
       </c>
       <c r="C91">
-        <v>583</v>
+        <v>535</v>
       </c>
       <c r="D91">
-        <v>1286</v>
+        <v>1276</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2614,16 +2611,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>701</v>
+        <v>742</v>
       </c>
       <c r="C92">
-        <v>584</v>
+        <v>534</v>
       </c>
       <c r="D92">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2634,16 +2631,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="C93">
-        <v>583</v>
+        <v>533</v>
       </c>
       <c r="D93">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2654,16 +2651,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>333</v>
+        <v>804</v>
       </c>
       <c r="C94">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D94">
-        <v>744</v>
+        <v>1216</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2674,16 +2671,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>318</v>
+        <v>802</v>
       </c>
       <c r="C95">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D95">
-        <v>711</v>
+        <v>1201</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2694,16 +2691,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>319</v>
+        <v>800</v>
       </c>
       <c r="C96">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D96">
-        <v>719</v>
+        <v>1202</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2714,16 +2711,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>318</v>
+        <v>800</v>
       </c>
       <c r="C97">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D97">
-        <v>714</v>
+        <v>1202</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2734,16 +2731,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>336</v>
+        <v>778</v>
       </c>
       <c r="C98">
-        <v>227</v>
+        <v>381</v>
       </c>
       <c r="D98">
-        <v>563</v>
+        <v>1159</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2754,16 +2751,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>339</v>
+        <v>776</v>
       </c>
       <c r="C99">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="D99">
-        <v>553</v>
+        <v>1156</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2774,16 +2771,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>338</v>
+        <v>775</v>
       </c>
       <c r="C100">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="D100">
-        <v>553</v>
+        <v>1153</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2794,16 +2791,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>356</v>
+        <v>774</v>
       </c>
       <c r="C101">
-        <v>215</v>
+        <v>377</v>
       </c>
       <c r="D101">
-        <v>571</v>
+        <v>1151</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2814,16 +2811,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>827</v>
+        <v>686</v>
       </c>
       <c r="C102">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="D102">
-        <v>1111</v>
+        <v>995</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2834,16 +2831,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>837</v>
+        <v>674</v>
       </c>
       <c r="C103">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D103">
-        <v>1123</v>
+        <v>979</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2854,16 +2851,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>837</v>
+        <v>679</v>
       </c>
       <c r="C104">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D104">
-        <v>1123</v>
+        <v>984</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2874,16 +2871,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>835</v>
+        <v>678</v>
       </c>
       <c r="C105">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D105">
-        <v>1120</v>
+        <v>983</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2894,16 +2891,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>833</v>
+        <v>693</v>
       </c>
       <c r="C106">
-        <v>286</v>
+        <v>181</v>
       </c>
       <c r="D106">
-        <v>1119</v>
+        <v>874</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2914,16 +2911,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>842</v>
+        <v>695</v>
       </c>
       <c r="C107">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="D107">
-        <v>1128</v>
+        <v>871</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2934,16 +2931,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="C108">
-        <v>285</v>
+        <v>176</v>
       </c>
       <c r="D108">
-        <v>1122</v>
+        <v>874</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -2954,16 +2951,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>837</v>
+        <v>710</v>
       </c>
       <c r="C109">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="D109">
-        <v>1121</v>
+        <v>885</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -2974,16 +2971,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>838</v>
+        <v>546</v>
       </c>
       <c r="C110">
-        <v>285</v>
+        <v>173</v>
       </c>
       <c r="D110">
-        <v>1123</v>
+        <v>719</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -2994,16 +2991,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>836</v>
+        <v>613</v>
       </c>
       <c r="C111">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="D111">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3014,16 +3011,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>842</v>
+        <v>605</v>
       </c>
       <c r="C112">
-        <v>284</v>
+        <v>201</v>
       </c>
       <c r="D112">
-        <v>1126</v>
+        <v>806</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3034,16 +3031,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>847</v>
+        <v>626</v>
       </c>
       <c r="C113">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="D113">
-        <v>1131</v>
+        <v>843</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3054,16 +3051,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>870</v>
+        <v>836</v>
       </c>
       <c r="C114">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="D114">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3074,16 +3071,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>870</v>
+        <v>845</v>
       </c>
       <c r="C115">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="D115">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3094,16 +3091,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="C116">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D116">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3114,16 +3111,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="C117">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="D117">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3134,16 +3131,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>795</v>
+        <v>856</v>
       </c>
       <c r="C118">
-        <v>447</v>
+        <v>547</v>
       </c>
       <c r="D118">
-        <v>1242</v>
+        <v>1403</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3154,16 +3151,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>799</v>
+        <v>877</v>
       </c>
       <c r="C119">
-        <v>456</v>
+        <v>558</v>
       </c>
       <c r="D119">
-        <v>1255</v>
+        <v>1435</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3174,16 +3171,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>819</v>
+        <v>883</v>
       </c>
       <c r="C120">
-        <v>453</v>
+        <v>576</v>
       </c>
       <c r="D120">
-        <v>1272</v>
+        <v>1459</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3194,16 +3191,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>810</v>
+        <v>886</v>
       </c>
       <c r="C121">
-        <v>457</v>
+        <v>582</v>
       </c>
       <c r="D121">
-        <v>1267</v>
+        <v>1468</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3214,16 +3211,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>783</v>
+        <v>925</v>
       </c>
       <c r="C122">
-        <v>643</v>
+        <v>583</v>
       </c>
       <c r="D122">
-        <v>1426</v>
+        <v>1508</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3234,16 +3231,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>778</v>
+        <v>930</v>
       </c>
       <c r="C123">
-        <v>656</v>
+        <v>566</v>
       </c>
       <c r="D123">
-        <v>1434</v>
+        <v>1496</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3254,16 +3251,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>775</v>
+        <v>924</v>
       </c>
       <c r="C124">
-        <v>638</v>
+        <v>591</v>
       </c>
       <c r="D124">
-        <v>1413</v>
+        <v>1515</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3274,16 +3271,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>778</v>
+        <v>921</v>
       </c>
       <c r="C125">
-        <v>644</v>
+        <v>544</v>
       </c>
       <c r="D125">
-        <v>1422</v>
+        <v>1465</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3294,16 +3291,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>759</v>
+        <v>934</v>
       </c>
       <c r="C126">
-        <v>695</v>
+        <v>526</v>
       </c>
       <c r="D126">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3314,16 +3311,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>750</v>
+        <v>931</v>
       </c>
       <c r="C127">
-        <v>681</v>
+        <v>514</v>
       </c>
       <c r="D127">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3334,13 +3331,13 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>751</v>
+        <v>936</v>
       </c>
       <c r="C128">
-        <v>702</v>
+        <v>517</v>
       </c>
       <c r="D128">
         <v>1453</v>
@@ -3354,16 +3351,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>752</v>
+        <v>939</v>
       </c>
       <c r="C129">
-        <v>702</v>
+        <v>519</v>
       </c>
       <c r="D129">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3374,16 +3371,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>727</v>
+        <v>927</v>
       </c>
       <c r="C130">
-        <v>658</v>
+        <v>476</v>
       </c>
       <c r="D130">
-        <v>1385</v>
+        <v>1403</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3394,16 +3391,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>887</v>
+        <v>926</v>
       </c>
       <c r="C131">
-        <v>681</v>
+        <v>472</v>
       </c>
       <c r="D131">
-        <v>1568</v>
+        <v>1398</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3414,42 +3411,22 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>888</v>
+        <v>924</v>
       </c>
       <c r="C132">
-        <v>682</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1570</v>
+        <v>924</v>
       </c>
       <c r="E132">
         <v>35</v>
       </c>
       <c r="F132" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="2">
-        <v>46303.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>859</v>
-      </c>
-      <c r="C133">
-        <v>678</v>
-      </c>
-      <c r="D133">
-        <v>1537</v>
-      </c>
-      <c r="E133">
-        <v>36</v>
-      </c>
-      <c r="F133" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -425,6 +137,879 @@
   </si>
   <si>
     <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
   </si>
 </sst>
 </file>
@@ -786,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -811,16 +1396,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>336</v>
+        <v>778</v>
       </c>
       <c r="C2">
-        <v>227</v>
+        <v>381</v>
       </c>
       <c r="D2">
-        <v>563</v>
+        <v>1159</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -831,16 +1416,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>339</v>
+        <v>776</v>
       </c>
       <c r="C3">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="D3">
-        <v>553</v>
+        <v>1156</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -851,16 +1436,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>338</v>
+        <v>775</v>
       </c>
       <c r="C4">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="D4">
-        <v>553</v>
+        <v>1153</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -871,16 +1456,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>356</v>
+        <v>774</v>
       </c>
       <c r="C5">
-        <v>215</v>
+        <v>377</v>
       </c>
       <c r="D5">
-        <v>571</v>
+        <v>1151</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -891,16 +1476,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>827</v>
+        <v>686</v>
       </c>
       <c r="C6">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="D6">
-        <v>1111</v>
+        <v>995</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -911,16 +1496,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>837</v>
+        <v>674</v>
       </c>
       <c r="C7">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D7">
-        <v>1123</v>
+        <v>979</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -931,16 +1516,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>837</v>
+        <v>679</v>
       </c>
       <c r="C8">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D8">
-        <v>1123</v>
+        <v>984</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -951,16 +1536,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>835</v>
+        <v>678</v>
       </c>
       <c r="C9">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D9">
-        <v>1120</v>
+        <v>983</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -971,16 +1556,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>833</v>
+        <v>693</v>
       </c>
       <c r="C10">
-        <v>286</v>
+        <v>181</v>
       </c>
       <c r="D10">
-        <v>1119</v>
+        <v>874</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -991,16 +1576,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>842</v>
+        <v>695</v>
       </c>
       <c r="C11">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="D11">
-        <v>1128</v>
+        <v>871</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1011,16 +1596,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="C12">
-        <v>285</v>
+        <v>176</v>
       </c>
       <c r="D12">
-        <v>1122</v>
+        <v>874</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1031,16 +1616,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>837</v>
+        <v>710</v>
       </c>
       <c r="C13">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="D13">
-        <v>1121</v>
+        <v>885</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1051,16 +1636,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>838</v>
+        <v>546</v>
       </c>
       <c r="C14">
-        <v>285</v>
+        <v>173</v>
       </c>
       <c r="D14">
-        <v>1123</v>
+        <v>719</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1071,16 +1656,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>836</v>
+        <v>613</v>
       </c>
       <c r="C15">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="D15">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1091,16 +1676,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>842</v>
+        <v>605</v>
       </c>
       <c r="C16">
-        <v>284</v>
+        <v>201</v>
       </c>
       <c r="D16">
-        <v>1126</v>
+        <v>806</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1111,16 +1696,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>847</v>
+        <v>626</v>
       </c>
       <c r="C17">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="D17">
-        <v>1131</v>
+        <v>843</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1131,16 +1716,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>870</v>
+        <v>836</v>
       </c>
       <c r="C18">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="D18">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1151,16 +1736,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>870</v>
+        <v>845</v>
       </c>
       <c r="C19">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="D19">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1171,16 +1756,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="C20">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D20">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1191,16 +1776,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="C21">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="D21">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1211,16 +1796,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>795</v>
+        <v>856</v>
       </c>
       <c r="C22">
-        <v>447</v>
+        <v>547</v>
       </c>
       <c r="D22">
-        <v>1242</v>
+        <v>1403</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1231,16 +1816,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>799</v>
+        <v>877</v>
       </c>
       <c r="C23">
-        <v>456</v>
+        <v>558</v>
       </c>
       <c r="D23">
-        <v>1255</v>
+        <v>1435</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1251,16 +1836,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>819</v>
+        <v>883</v>
       </c>
       <c r="C24">
-        <v>453</v>
+        <v>576</v>
       </c>
       <c r="D24">
-        <v>1272</v>
+        <v>1459</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1271,16 +1856,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>810</v>
+        <v>886</v>
       </c>
       <c r="C25">
-        <v>457</v>
+        <v>582</v>
       </c>
       <c r="D25">
-        <v>1267</v>
+        <v>1468</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1291,16 +1876,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>783</v>
+        <v>925</v>
       </c>
       <c r="C26">
-        <v>643</v>
+        <v>583</v>
       </c>
       <c r="D26">
-        <v>1426</v>
+        <v>1508</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1311,16 +1896,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>778</v>
+        <v>930</v>
       </c>
       <c r="C27">
-        <v>656</v>
+        <v>566</v>
       </c>
       <c r="D27">
-        <v>1434</v>
+        <v>1496</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1331,16 +1916,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>775</v>
+        <v>924</v>
       </c>
       <c r="C28">
-        <v>638</v>
+        <v>591</v>
       </c>
       <c r="D28">
-        <v>1413</v>
+        <v>1515</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1351,16 +1936,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>778</v>
+        <v>921</v>
       </c>
       <c r="C29">
-        <v>644</v>
+        <v>544</v>
       </c>
       <c r="D29">
-        <v>1422</v>
+        <v>1465</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1371,16 +1956,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>759</v>
+        <v>934</v>
       </c>
       <c r="C30">
-        <v>695</v>
+        <v>526</v>
       </c>
       <c r="D30">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1391,16 +1976,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>750</v>
+        <v>931</v>
       </c>
       <c r="C31">
-        <v>681</v>
+        <v>514</v>
       </c>
       <c r="D31">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1411,13 +1996,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>751</v>
+        <v>936</v>
       </c>
       <c r="C32">
-        <v>702</v>
+        <v>517</v>
       </c>
       <c r="D32">
         <v>1453</v>
@@ -1431,16 +2016,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>752</v>
+        <v>939</v>
       </c>
       <c r="C33">
-        <v>702</v>
+        <v>519</v>
       </c>
       <c r="D33">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1451,16 +2036,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>727</v>
+        <v>927</v>
       </c>
       <c r="C34">
-        <v>658</v>
+        <v>476</v>
       </c>
       <c r="D34">
-        <v>1385</v>
+        <v>1403</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1471,16 +2056,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>887</v>
+        <v>926</v>
       </c>
       <c r="C35">
-        <v>681</v>
+        <v>472</v>
       </c>
       <c r="D35">
-        <v>1568</v>
+        <v>1398</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1491,16 +2076,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>888</v>
+        <v>924</v>
       </c>
       <c r="C36">
-        <v>682</v>
+        <v>472</v>
       </c>
       <c r="D36">
-        <v>1570</v>
+        <v>1396</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1511,16 +2096,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>859</v>
+        <v>913</v>
       </c>
       <c r="C37">
-        <v>678</v>
+        <v>472</v>
       </c>
       <c r="D37">
-        <v>1537</v>
+        <v>1385</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1531,16 +2116,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="C38">
-        <v>284</v>
+        <v>239</v>
       </c>
       <c r="D38">
-        <v>601</v>
+        <v>535</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1551,16 +2136,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="C39">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D39">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1571,16 +2156,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>87</v>
+        <v>280</v>
       </c>
       <c r="C40">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D40">
-        <v>283</v>
+        <v>512</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1591,16 +2176,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="C41">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="D41">
-        <v>277</v>
+        <v>509</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1611,16 +2196,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D42">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1631,16 +2216,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C43">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D43">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1651,16 +2236,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C44">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D44">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1671,16 +2256,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C45">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="D45">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1691,16 +2276,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C46">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D46">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1711,16 +2296,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C47">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D47">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1731,16 +2316,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C48">
         <v>204</v>
       </c>
       <c r="D48">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1751,16 +2336,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C49">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D49">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1771,16 +2356,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="C50">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D50">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1791,16 +2376,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C51">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="D51">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1811,16 +2396,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C52">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="D52">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1831,16 +2416,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C53">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D53">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1851,16 +2436,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C54">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D54">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1871,16 +2456,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C55">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D55">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1891,16 +2476,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C56">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D56">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1911,16 +2496,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C57">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D57">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1931,16 +2516,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C58">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D58">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -1951,16 +2536,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C59">
         <v>215</v>
       </c>
       <c r="D59">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -1971,16 +2556,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C60">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D60">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -1991,16 +2576,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="C61">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D61">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2011,16 +2596,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="C62">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D62">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2031,16 +2616,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C63">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D63">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2051,16 +2636,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="C64">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D64">
-        <v>311</v>
+        <v>437</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2071,16 +2656,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>160</v>
+        <v>318</v>
       </c>
       <c r="C65">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="D65">
-        <v>348</v>
+        <v>520</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2091,16 +2676,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>592</v>
+        <v>1116</v>
       </c>
       <c r="C66">
-        <v>416</v>
+        <v>482</v>
       </c>
       <c r="D66">
-        <v>1008</v>
+        <v>1598</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2111,16 +2696,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>605</v>
+        <v>1091</v>
       </c>
       <c r="C67">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="D67">
-        <v>1026</v>
+        <v>1589</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2131,16 +2716,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>608</v>
+        <v>1079</v>
       </c>
       <c r="C68">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="D68">
-        <v>1050</v>
+        <v>1577</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2151,16 +2736,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>625</v>
+        <v>1081</v>
       </c>
       <c r="C69">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="D69">
-        <v>1088</v>
+        <v>1590</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2171,16 +2756,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="C70">
-        <v>463</v>
+        <v>561</v>
       </c>
       <c r="D70">
-        <v>1518</v>
+        <v>1624</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2191,16 +2776,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C71">
-        <v>477</v>
+        <v>566</v>
       </c>
       <c r="D71">
-        <v>1537</v>
+        <v>1632</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2211,16 +2796,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>1114</v>
+        <v>995</v>
       </c>
       <c r="C72">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="D72">
-        <v>1646</v>
+        <v>1550</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2231,16 +2816,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>1117</v>
+        <v>994</v>
       </c>
       <c r="C73">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="D73">
-        <v>1650</v>
+        <v>1545</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2251,16 +2836,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>1131</v>
+        <v>923</v>
       </c>
       <c r="C74">
-        <v>529</v>
+        <v>665</v>
       </c>
       <c r="D74">
-        <v>1660</v>
+        <v>1588</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2271,16 +2856,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>1130</v>
+        <v>921</v>
       </c>
       <c r="C75">
-        <v>532</v>
+        <v>670</v>
       </c>
       <c r="D75">
-        <v>1662</v>
+        <v>1591</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2291,16 +2876,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>1139</v>
+        <v>925</v>
       </c>
       <c r="C76">
-        <v>527</v>
+        <v>671</v>
       </c>
       <c r="D76">
-        <v>1666</v>
+        <v>1596</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2311,16 +2896,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>1151</v>
+        <v>928</v>
       </c>
       <c r="C77">
-        <v>530</v>
+        <v>670</v>
       </c>
       <c r="D77">
-        <v>1681</v>
+        <v>1598</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2331,16 +2916,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="C78">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="D78">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2351,16 +2936,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>893</v>
+        <v>935</v>
       </c>
       <c r="C79">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="D79">
-        <v>1532</v>
+        <v>1596</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2371,16 +2956,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>890</v>
+        <v>932</v>
       </c>
       <c r="C80">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="D80">
-        <v>1517</v>
+        <v>1591</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2391,16 +2976,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>891</v>
+        <v>934</v>
       </c>
       <c r="C81">
-        <v>626</v>
+        <v>660</v>
       </c>
       <c r="D81">
-        <v>1517</v>
+        <v>1594</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2411,16 +2996,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>853</v>
+        <v>907</v>
       </c>
       <c r="C82">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D82">
-        <v>1495</v>
+        <v>1553</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2431,16 +3016,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>850</v>
+        <v>908</v>
       </c>
       <c r="C83">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D83">
-        <v>1499</v>
+        <v>1553</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2451,16 +3036,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>850</v>
+        <v>912</v>
       </c>
       <c r="C84">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D84">
-        <v>1499</v>
+        <v>1560</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2471,16 +3056,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>855</v>
+        <v>914</v>
       </c>
       <c r="C85">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D85">
-        <v>1506</v>
+        <v>1563</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2491,16 +3076,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>812</v>
+        <v>847</v>
       </c>
       <c r="C86">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="D86">
-        <v>1424</v>
+        <v>1485</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2511,16 +3096,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>809</v>
+        <v>846</v>
       </c>
       <c r="C87">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="D87">
-        <v>1420</v>
+        <v>1482</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2531,16 +3116,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>785</v>
+        <v>840</v>
       </c>
       <c r="C88">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="D88">
-        <v>1406</v>
+        <v>1478</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2551,16 +3136,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>783</v>
+        <v>832</v>
       </c>
       <c r="C89">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="D89">
-        <v>1404</v>
+        <v>1466</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2571,16 +3156,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C90">
-        <v>540</v>
+        <v>609</v>
       </c>
       <c r="D90">
-        <v>1284</v>
+        <v>1359</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2591,16 +3176,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C91">
-        <v>535</v>
+        <v>603</v>
       </c>
       <c r="D91">
-        <v>1276</v>
+        <v>1340</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2611,16 +3196,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="C92">
-        <v>534</v>
+        <v>604</v>
       </c>
       <c r="D92">
-        <v>1276</v>
+        <v>1332</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2631,16 +3216,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C93">
-        <v>533</v>
+        <v>604</v>
       </c>
       <c r="D93">
-        <v>1271</v>
+        <v>1335</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2651,16 +3236,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>804</v>
+        <v>876</v>
       </c>
       <c r="C94">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D94">
-        <v>1216</v>
+        <v>1290</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2671,16 +3256,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>802</v>
+        <v>853</v>
       </c>
       <c r="C95">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D95">
-        <v>1201</v>
+        <v>1259</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2691,16 +3276,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>800</v>
+        <v>913</v>
       </c>
       <c r="C96">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="D96">
-        <v>1202</v>
+        <v>1366</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2711,16 +3296,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>800</v>
+        <v>913</v>
       </c>
       <c r="C97">
-        <v>402</v>
+        <v>467</v>
       </c>
       <c r="D97">
-        <v>1202</v>
+        <v>1380</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2731,16 +3316,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>778</v>
+        <v>885</v>
       </c>
       <c r="C98">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="D98">
-        <v>1159</v>
+        <v>1334</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2751,16 +3336,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>776</v>
+        <v>812</v>
       </c>
       <c r="C99">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="D99">
-        <v>1156</v>
+        <v>1234</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2771,16 +3356,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="C100">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="D100">
-        <v>1153</v>
+        <v>1229</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2791,16 +3376,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>774</v>
+        <v>812</v>
       </c>
       <c r="C101">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="D101">
-        <v>1151</v>
+        <v>1209</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2811,16 +3396,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="C102">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="D102">
-        <v>995</v>
+        <v>1163</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2831,16 +3416,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>674</v>
+        <v>764</v>
       </c>
       <c r="C103">
-        <v>305</v>
+        <v>399</v>
       </c>
       <c r="D103">
-        <v>979</v>
+        <v>1163</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2851,16 +3436,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>679</v>
+        <v>763</v>
       </c>
       <c r="C104">
-        <v>305</v>
+        <v>399</v>
       </c>
       <c r="D104">
-        <v>984</v>
+        <v>1162</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2871,16 +3456,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>678</v>
+        <v>762</v>
       </c>
       <c r="C105">
-        <v>305</v>
+        <v>398</v>
       </c>
       <c r="D105">
-        <v>983</v>
+        <v>1160</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2891,16 +3476,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>693</v>
+        <v>758</v>
       </c>
       <c r="C106">
-        <v>181</v>
+        <v>395</v>
       </c>
       <c r="D106">
-        <v>874</v>
+        <v>1153</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2911,16 +3496,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>695</v>
+        <v>758</v>
       </c>
       <c r="C107">
-        <v>176</v>
+        <v>392</v>
       </c>
       <c r="D107">
-        <v>871</v>
+        <v>1150</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2931,16 +3516,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>698</v>
+        <v>757</v>
       </c>
       <c r="C108">
-        <v>176</v>
+        <v>393</v>
       </c>
       <c r="D108">
-        <v>874</v>
+        <v>1150</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -2951,16 +3536,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>710</v>
+        <v>753</v>
       </c>
       <c r="C109">
-        <v>175</v>
+        <v>392</v>
       </c>
       <c r="D109">
-        <v>885</v>
+        <v>1145</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -2971,16 +3556,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>546</v>
+        <v>757</v>
       </c>
       <c r="C110">
-        <v>173</v>
+        <v>391</v>
       </c>
       <c r="D110">
-        <v>719</v>
+        <v>1148</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -2991,16 +3576,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>613</v>
+        <v>757</v>
       </c>
       <c r="C111">
-        <v>196</v>
+        <v>391</v>
       </c>
       <c r="D111">
-        <v>809</v>
+        <v>1148</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3011,16 +3596,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>605</v>
+        <v>757</v>
       </c>
       <c r="C112">
-        <v>201</v>
+        <v>392</v>
       </c>
       <c r="D112">
-        <v>806</v>
+        <v>1149</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3031,16 +3616,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>626</v>
+        <v>757</v>
       </c>
       <c r="C113">
-        <v>217</v>
+        <v>392</v>
       </c>
       <c r="D113">
-        <v>843</v>
+        <v>1149</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3051,16 +3636,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>836</v>
+        <v>755</v>
       </c>
       <c r="C114">
-        <v>310</v>
+        <v>419</v>
       </c>
       <c r="D114">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3071,16 +3656,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>845</v>
+        <v>753</v>
       </c>
       <c r="C115">
-        <v>316</v>
+        <v>441</v>
       </c>
       <c r="D115">
-        <v>1161</v>
+        <v>1194</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3091,16 +3676,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>847</v>
+        <v>751</v>
       </c>
       <c r="C116">
-        <v>317</v>
+        <v>442</v>
       </c>
       <c r="D116">
-        <v>1164</v>
+        <v>1193</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3111,16 +3696,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>850</v>
+        <v>755</v>
       </c>
       <c r="C117">
-        <v>322</v>
+        <v>442</v>
       </c>
       <c r="D117">
-        <v>1172</v>
+        <v>1197</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3131,16 +3716,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>856</v>
+        <v>781</v>
       </c>
       <c r="C118">
-        <v>547</v>
+        <v>486</v>
       </c>
       <c r="D118">
-        <v>1403</v>
+        <v>1267</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3151,16 +3736,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>877</v>
+        <v>788</v>
       </c>
       <c r="C119">
-        <v>558</v>
+        <v>493</v>
       </c>
       <c r="D119">
-        <v>1435</v>
+        <v>1281</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3171,16 +3756,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>883</v>
+        <v>776</v>
       </c>
       <c r="C120">
-        <v>576</v>
+        <v>442</v>
       </c>
       <c r="D120">
-        <v>1459</v>
+        <v>1218</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3191,16 +3776,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>886</v>
+        <v>782</v>
       </c>
       <c r="C121">
-        <v>582</v>
+        <v>439</v>
       </c>
       <c r="D121">
-        <v>1468</v>
+        <v>1221</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3211,16 +3796,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>925</v>
+        <v>762</v>
       </c>
       <c r="C122">
-        <v>583</v>
+        <v>509</v>
       </c>
       <c r="D122">
-        <v>1508</v>
+        <v>1271</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3231,16 +3816,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="C123">
-        <v>566</v>
+        <v>524</v>
       </c>
       <c r="D123">
-        <v>1496</v>
+        <v>1285</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3251,16 +3836,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>924</v>
+        <v>623</v>
       </c>
       <c r="C124">
-        <v>591</v>
+        <v>518</v>
       </c>
       <c r="D124">
-        <v>1515</v>
+        <v>1141</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3271,16 +3856,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>921</v>
+        <v>615</v>
       </c>
       <c r="C125">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="D125">
-        <v>1465</v>
+        <v>1132</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3291,16 +3876,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>934</v>
+        <v>656</v>
       </c>
       <c r="C126">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="D126">
-        <v>1460</v>
+        <v>1133</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3311,16 +3896,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>931</v>
+        <v>654</v>
       </c>
       <c r="C127">
-        <v>514</v>
+        <v>476</v>
       </c>
       <c r="D127">
-        <v>1445</v>
+        <v>1130</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3331,16 +3916,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>936</v>
+        <v>634</v>
       </c>
       <c r="C128">
-        <v>517</v>
+        <v>477</v>
       </c>
       <c r="D128">
-        <v>1453</v>
+        <v>1111</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3351,16 +3936,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>939</v>
+        <v>772</v>
       </c>
       <c r="C129">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="D129">
-        <v>1458</v>
+        <v>1247</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3371,16 +3956,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>927</v>
+        <v>284</v>
       </c>
       <c r="C130">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="D130">
-        <v>1403</v>
+        <v>745</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3391,16 +3976,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>926</v>
+        <v>259</v>
       </c>
       <c r="C131">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="D131">
-        <v>1398</v>
+        <v>717</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3411,22 +3996,3922 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>924</v>
+        <v>255</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="D132">
-        <v>924</v>
+        <v>731</v>
       </c>
       <c r="E132">
         <v>35</v>
       </c>
       <c r="F132" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="2">
+        <v>46305.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>255</v>
+      </c>
+      <c r="C133">
+        <v>474</v>
+      </c>
+      <c r="D133">
+        <v>729</v>
+      </c>
+      <c r="E133">
+        <v>36</v>
+      </c>
+      <c r="F133" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="2">
+        <v>46305.375</v>
+      </c>
+      <c r="B134">
+        <v>71</v>
+      </c>
+      <c r="C134">
+        <v>229</v>
+      </c>
+      <c r="D134">
+        <v>300</v>
+      </c>
+      <c r="E134">
+        <v>37</v>
+      </c>
+      <c r="F134" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="2">
+        <v>46305.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>208</v>
+      </c>
+      <c r="C135">
+        <v>201</v>
+      </c>
+      <c r="D135">
+        <v>409</v>
+      </c>
+      <c r="E135">
+        <v>38</v>
+      </c>
+      <c r="F135" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="2">
+        <v>46305.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>214</v>
+      </c>
+      <c r="C136">
+        <v>202</v>
+      </c>
+      <c r="D136">
+        <v>416</v>
+      </c>
+      <c r="E136">
+        <v>39</v>
+      </c>
+      <c r="F136" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="2">
+        <v>46305.40625</v>
+      </c>
+      <c r="B137">
+        <v>212</v>
+      </c>
+      <c r="C137">
+        <v>200</v>
+      </c>
+      <c r="D137">
+        <v>412</v>
+      </c>
+      <c r="E137">
+        <v>40</v>
+      </c>
+      <c r="F137" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="2">
+        <v>46305.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>214</v>
+      </c>
+      <c r="C138">
+        <v>223</v>
+      </c>
+      <c r="D138">
+        <v>437</v>
+      </c>
+      <c r="E138">
+        <v>41</v>
+      </c>
+      <c r="F138" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="2">
+        <v>46305.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>164</v>
+      </c>
+      <c r="C139">
+        <v>223</v>
+      </c>
+      <c r="D139">
+        <v>387</v>
+      </c>
+      <c r="E139">
+        <v>42</v>
+      </c>
+      <c r="F139" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="2">
+        <v>46305.4375</v>
+      </c>
+      <c r="B140">
+        <v>49</v>
+      </c>
+      <c r="C140">
+        <v>224</v>
+      </c>
+      <c r="D140">
+        <v>273</v>
+      </c>
+      <c r="E140">
+        <v>43</v>
+      </c>
+      <c r="F140" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="2">
+        <v>46305.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>39</v>
+      </c>
+      <c r="C141">
+        <v>222</v>
+      </c>
+      <c r="D141">
+        <v>261</v>
+      </c>
+      <c r="E141">
+        <v>44</v>
+      </c>
+      <c r="F141" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="2">
+        <v>46305.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>42</v>
+      </c>
+      <c r="C142">
+        <v>220</v>
+      </c>
+      <c r="D142">
+        <v>262</v>
+      </c>
+      <c r="E142">
+        <v>45</v>
+      </c>
+      <c r="F142" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="2">
+        <v>46305.46875</v>
+      </c>
+      <c r="B143">
+        <v>40</v>
+      </c>
+      <c r="C143">
+        <v>203</v>
+      </c>
+      <c r="D143">
+        <v>243</v>
+      </c>
+      <c r="E143">
+        <v>46</v>
+      </c>
+      <c r="F143" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="2">
+        <v>46305.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>44</v>
+      </c>
+      <c r="C144">
+        <v>200</v>
+      </c>
+      <c r="D144">
+        <v>244</v>
+      </c>
+      <c r="E144">
+        <v>47</v>
+      </c>
+      <c r="F144" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="2">
+        <v>46305.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>178</v>
+      </c>
+      <c r="C145">
+        <v>253</v>
+      </c>
+      <c r="D145">
+        <v>431</v>
+      </c>
+      <c r="E145">
+        <v>48</v>
+      </c>
+      <c r="F145" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="2">
+        <v>46305.5</v>
+      </c>
+      <c r="B146">
+        <v>50</v>
+      </c>
+      <c r="C146">
+        <v>253</v>
+      </c>
+      <c r="D146">
+        <v>303</v>
+      </c>
+      <c r="E146">
+        <v>49</v>
+      </c>
+      <c r="F146" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="2">
+        <v>46305.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>49</v>
+      </c>
+      <c r="C147">
+        <v>205</v>
+      </c>
+      <c r="D147">
+        <v>254</v>
+      </c>
+      <c r="E147">
+        <v>50</v>
+      </c>
+      <c r="F147" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="2">
+        <v>46305.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>52</v>
+      </c>
+      <c r="C148">
+        <v>204</v>
+      </c>
+      <c r="D148">
+        <v>256</v>
+      </c>
+      <c r="E148">
+        <v>51</v>
+      </c>
+      <c r="F148" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="2">
+        <v>46305.53125</v>
+      </c>
+      <c r="B149">
+        <v>54</v>
+      </c>
+      <c r="C149">
+        <v>204</v>
+      </c>
+      <c r="D149">
+        <v>258</v>
+      </c>
+      <c r="E149">
+        <v>52</v>
+      </c>
+      <c r="F149" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="2">
+        <v>46305.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>48</v>
+      </c>
+      <c r="C150">
+        <v>210</v>
+      </c>
+      <c r="D150">
+        <v>258</v>
+      </c>
+      <c r="E150">
+        <v>53</v>
+      </c>
+      <c r="F150" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="2">
+        <v>46305.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>46</v>
+      </c>
+      <c r="C151">
+        <v>210</v>
+      </c>
+      <c r="D151">
+        <v>256</v>
+      </c>
+      <c r="E151">
+        <v>54</v>
+      </c>
+      <c r="F151" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="2">
+        <v>46305.5625</v>
+      </c>
+      <c r="B152">
+        <v>46</v>
+      </c>
+      <c r="C152">
+        <v>210</v>
+      </c>
+      <c r="D152">
+        <v>256</v>
+      </c>
+      <c r="E152">
+        <v>55</v>
+      </c>
+      <c r="F152" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="2">
+        <v>46305.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>46</v>
+      </c>
+      <c r="C153">
+        <v>210</v>
+      </c>
+      <c r="D153">
+        <v>256</v>
+      </c>
+      <c r="E153">
+        <v>56</v>
+      </c>
+      <c r="F153" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="2">
+        <v>46305.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>47</v>
+      </c>
+      <c r="C154">
+        <v>206</v>
+      </c>
+      <c r="D154">
+        <v>253</v>
+      </c>
+      <c r="E154">
+        <v>57</v>
+      </c>
+      <c r="F154" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="2">
+        <v>46305.59375</v>
+      </c>
+      <c r="B155">
+        <v>47</v>
+      </c>
+      <c r="C155">
+        <v>206</v>
+      </c>
+      <c r="D155">
+        <v>253</v>
+      </c>
+      <c r="E155">
+        <v>58</v>
+      </c>
+      <c r="F155" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="2">
+        <v>46305.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>47</v>
+      </c>
+      <c r="C156">
+        <v>206</v>
+      </c>
+      <c r="D156">
+        <v>253</v>
+      </c>
+      <c r="E156">
+        <v>59</v>
+      </c>
+      <c r="F156" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="2">
+        <v>46305.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>47</v>
+      </c>
+      <c r="C157">
+        <v>206</v>
+      </c>
+      <c r="D157">
+        <v>253</v>
+      </c>
+      <c r="E157">
+        <v>60</v>
+      </c>
+      <c r="F157" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="2">
+        <v>46305.625</v>
+      </c>
+      <c r="B158">
+        <v>42</v>
+      </c>
+      <c r="C158">
+        <v>217</v>
+      </c>
+      <c r="D158">
+        <v>259</v>
+      </c>
+      <c r="E158">
+        <v>61</v>
+      </c>
+      <c r="F158" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="2">
+        <v>46305.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>42</v>
+      </c>
+      <c r="C159">
+        <v>218</v>
+      </c>
+      <c r="D159">
+        <v>260</v>
+      </c>
+      <c r="E159">
+        <v>62</v>
+      </c>
+      <c r="F159" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="2">
+        <v>46305.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>42</v>
+      </c>
+      <c r="C160">
+        <v>218</v>
+      </c>
+      <c r="D160">
+        <v>260</v>
+      </c>
+      <c r="E160">
+        <v>63</v>
+      </c>
+      <c r="F160" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="2">
+        <v>46305.65625</v>
+      </c>
+      <c r="B161">
+        <v>82</v>
+      </c>
+      <c r="C161">
+        <v>221</v>
+      </c>
+      <c r="D161">
+        <v>303</v>
+      </c>
+      <c r="E161">
+        <v>64</v>
+      </c>
+      <c r="F161" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="2">
+        <v>46305.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>756</v>
+      </c>
+      <c r="C162">
+        <v>428</v>
+      </c>
+      <c r="D162">
+        <v>1184</v>
+      </c>
+      <c r="E162">
+        <v>65</v>
+      </c>
+      <c r="F162" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="2">
+        <v>46305.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>792</v>
+      </c>
+      <c r="C163">
+        <v>469</v>
+      </c>
+      <c r="D163">
+        <v>1261</v>
+      </c>
+      <c r="E163">
+        <v>66</v>
+      </c>
+      <c r="F163" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="2">
+        <v>46305.6875</v>
+      </c>
+      <c r="B164">
+        <v>790</v>
+      </c>
+      <c r="C164">
+        <v>465</v>
+      </c>
+      <c r="D164">
+        <v>1255</v>
+      </c>
+      <c r="E164">
+        <v>67</v>
+      </c>
+      <c r="F164" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="2">
+        <v>46305.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>801</v>
+      </c>
+      <c r="C165">
+        <v>471</v>
+      </c>
+      <c r="D165">
+        <v>1272</v>
+      </c>
+      <c r="E165">
+        <v>68</v>
+      </c>
+      <c r="F165" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="2">
+        <v>46305.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>736</v>
+      </c>
+      <c r="C166">
+        <v>608</v>
+      </c>
+      <c r="D166">
+        <v>1344</v>
+      </c>
+      <c r="E166">
+        <v>69</v>
+      </c>
+      <c r="F166" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="2">
+        <v>46305.71875</v>
+      </c>
+      <c r="B167">
+        <v>741</v>
+      </c>
+      <c r="C167">
+        <v>625</v>
+      </c>
+      <c r="D167">
+        <v>1366</v>
+      </c>
+      <c r="E167">
+        <v>70</v>
+      </c>
+      <c r="F167" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="2">
+        <v>46305.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>739</v>
+      </c>
+      <c r="C168">
+        <v>624</v>
+      </c>
+      <c r="D168">
+        <v>1363</v>
+      </c>
+      <c r="E168">
+        <v>71</v>
+      </c>
+      <c r="F168" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="2">
+        <v>46305.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>746</v>
+      </c>
+      <c r="C169">
+        <v>628</v>
+      </c>
+      <c r="D169">
+        <v>1374</v>
+      </c>
+      <c r="E169">
+        <v>72</v>
+      </c>
+      <c r="F169" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="2">
+        <v>46305.75</v>
+      </c>
+      <c r="B170">
+        <v>848</v>
+      </c>
+      <c r="C170">
+        <v>642</v>
+      </c>
+      <c r="D170">
+        <v>1490</v>
+      </c>
+      <c r="E170">
+        <v>73</v>
+      </c>
+      <c r="F170" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="2">
+        <v>46305.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>848</v>
+      </c>
+      <c r="C171">
+        <v>645</v>
+      </c>
+      <c r="D171">
+        <v>1493</v>
+      </c>
+      <c r="E171">
+        <v>74</v>
+      </c>
+      <c r="F171" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="2">
+        <v>46305.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>848</v>
+      </c>
+      <c r="C172">
+        <v>644</v>
+      </c>
+      <c r="D172">
+        <v>1492</v>
+      </c>
+      <c r="E172">
+        <v>75</v>
+      </c>
+      <c r="F172" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="2">
+        <v>46305.78125</v>
+      </c>
+      <c r="B173">
+        <v>840</v>
+      </c>
+      <c r="C173">
+        <v>643</v>
+      </c>
+      <c r="D173">
+        <v>1483</v>
+      </c>
+      <c r="E173">
+        <v>76</v>
+      </c>
+      <c r="F173" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="2">
+        <v>46305.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>869</v>
+      </c>
+      <c r="C174">
+        <v>652</v>
+      </c>
+      <c r="D174">
+        <v>1521</v>
+      </c>
+      <c r="E174">
+        <v>77</v>
+      </c>
+      <c r="F174" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="2">
+        <v>46305.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>867</v>
+      </c>
+      <c r="C175">
+        <v>654</v>
+      </c>
+      <c r="D175">
+        <v>1521</v>
+      </c>
+      <c r="E175">
+        <v>78</v>
+      </c>
+      <c r="F175" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="2">
+        <v>46305.8125</v>
+      </c>
+      <c r="B176">
+        <v>792</v>
+      </c>
+      <c r="C176">
+        <v>639</v>
+      </c>
+      <c r="D176">
+        <v>1431</v>
+      </c>
+      <c r="E176">
+        <v>79</v>
+      </c>
+      <c r="F176" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="2">
+        <v>46305.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>788</v>
+      </c>
+      <c r="C177">
+        <v>639</v>
+      </c>
+      <c r="D177">
+        <v>1427</v>
+      </c>
+      <c r="E177">
+        <v>80</v>
+      </c>
+      <c r="F177" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="2">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>800</v>
+      </c>
+      <c r="C178">
+        <v>613</v>
+      </c>
+      <c r="D178">
+        <v>1413</v>
+      </c>
+      <c r="E178">
+        <v>81</v>
+      </c>
+      <c r="F178" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="2">
+        <v>46305.84375</v>
+      </c>
+      <c r="B179">
+        <v>803</v>
+      </c>
+      <c r="C179">
+        <v>610</v>
+      </c>
+      <c r="D179">
+        <v>1413</v>
+      </c>
+      <c r="E179">
+        <v>82</v>
+      </c>
+      <c r="F179" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="2">
+        <v>46305.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>805</v>
+      </c>
+      <c r="C180">
+        <v>613</v>
+      </c>
+      <c r="D180">
+        <v>1418</v>
+      </c>
+      <c r="E180">
+        <v>83</v>
+      </c>
+      <c r="F180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="2">
+        <v>46305.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>803</v>
+      </c>
+      <c r="C181">
+        <v>608</v>
+      </c>
+      <c r="D181">
+        <v>1411</v>
+      </c>
+      <c r="E181">
+        <v>84</v>
+      </c>
+      <c r="F181" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="2">
+        <v>46305.875</v>
+      </c>
+      <c r="B182">
+        <v>734</v>
+      </c>
+      <c r="C182">
+        <v>617</v>
+      </c>
+      <c r="D182">
+        <v>1351</v>
+      </c>
+      <c r="E182">
+        <v>85</v>
+      </c>
+      <c r="F182" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="2">
+        <v>46305.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>734</v>
+      </c>
+      <c r="C183">
+        <v>605</v>
+      </c>
+      <c r="D183">
+        <v>1339</v>
+      </c>
+      <c r="E183">
+        <v>86</v>
+      </c>
+      <c r="F183" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="2">
+        <v>46305.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>737</v>
+      </c>
+      <c r="C184">
+        <v>606</v>
+      </c>
+      <c r="D184">
+        <v>1343</v>
+      </c>
+      <c r="E184">
+        <v>87</v>
+      </c>
+      <c r="F184" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="2">
+        <v>46305.90625</v>
+      </c>
+      <c r="B185">
+        <v>733</v>
+      </c>
+      <c r="C185">
+        <v>601</v>
+      </c>
+      <c r="D185">
+        <v>1334</v>
+      </c>
+      <c r="E185">
+        <v>88</v>
+      </c>
+      <c r="F185" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="2">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>671</v>
+      </c>
+      <c r="C186">
+        <v>602</v>
+      </c>
+      <c r="D186">
+        <v>1273</v>
+      </c>
+      <c r="E186">
+        <v>89</v>
+      </c>
+      <c r="F186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="2">
+        <v>46305.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>669</v>
+      </c>
+      <c r="C187">
+        <v>600</v>
+      </c>
+      <c r="D187">
+        <v>1269</v>
+      </c>
+      <c r="E187">
+        <v>90</v>
+      </c>
+      <c r="F187" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="2">
+        <v>46305.9375</v>
+      </c>
+      <c r="B188">
+        <v>661</v>
+      </c>
+      <c r="C188">
+        <v>608</v>
+      </c>
+      <c r="D188">
+        <v>1269</v>
+      </c>
+      <c r="E188">
+        <v>91</v>
+      </c>
+      <c r="F188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="2">
+        <v>46305.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>671</v>
+      </c>
+      <c r="C189">
+        <v>605</v>
+      </c>
+      <c r="D189">
+        <v>1276</v>
+      </c>
+      <c r="E189">
+        <v>92</v>
+      </c>
+      <c r="F189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="2">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>762</v>
+      </c>
+      <c r="C190">
+        <v>462</v>
+      </c>
+      <c r="D190">
+        <v>1224</v>
+      </c>
+      <c r="E190">
+        <v>93</v>
+      </c>
+      <c r="F190" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="2">
+        <v>46305.96875</v>
+      </c>
+      <c r="B191">
+        <v>759</v>
+      </c>
+      <c r="C191">
+        <v>440</v>
+      </c>
+      <c r="D191">
+        <v>1199</v>
+      </c>
+      <c r="E191">
+        <v>94</v>
+      </c>
+      <c r="F191" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="2">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>759</v>
+      </c>
+      <c r="C192">
+        <v>442</v>
+      </c>
+      <c r="D192">
+        <v>1201</v>
+      </c>
+      <c r="E192">
+        <v>95</v>
+      </c>
+      <c r="F192" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="2">
+        <v>46305.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>757</v>
+      </c>
+      <c r="C193">
+        <v>441</v>
+      </c>
+      <c r="D193">
+        <v>1198</v>
+      </c>
+      <c r="E193">
+        <v>96</v>
+      </c>
+      <c r="F193" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>682</v>
+      </c>
+      <c r="C194">
+        <v>451</v>
+      </c>
+      <c r="D194">
+        <v>1133</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>682</v>
+      </c>
+      <c r="C195">
+        <v>452</v>
+      </c>
+      <c r="D195">
+        <v>1134</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>681</v>
+      </c>
+      <c r="C196">
+        <v>453</v>
+      </c>
+      <c r="D196">
+        <v>1134</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>679</v>
+      </c>
+      <c r="C197">
+        <v>453</v>
+      </c>
+      <c r="D197">
+        <v>1132</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>589</v>
+      </c>
+      <c r="C198">
+        <v>444</v>
+      </c>
+      <c r="D198">
+        <v>1033</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>588</v>
+      </c>
+      <c r="C199">
+        <v>443</v>
+      </c>
+      <c r="D199">
+        <v>1031</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>588</v>
+      </c>
+      <c r="C200">
+        <v>443</v>
+      </c>
+      <c r="D200">
+        <v>1031</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>586</v>
+      </c>
+      <c r="C201">
+        <v>441</v>
+      </c>
+      <c r="D201">
+        <v>1027</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>365</v>
+      </c>
+      <c r="C202">
+        <v>443</v>
+      </c>
+      <c r="D202">
+        <v>808</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>354</v>
+      </c>
+      <c r="C203">
+        <v>442</v>
+      </c>
+      <c r="D203">
+        <v>796</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>355</v>
+      </c>
+      <c r="C204">
+        <v>444</v>
+      </c>
+      <c r="D204">
+        <v>799</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>353</v>
+      </c>
+      <c r="C205">
+        <v>441</v>
+      </c>
+      <c r="D205">
+        <v>794</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>55</v>
+      </c>
+      <c r="C206">
+        <v>283</v>
+      </c>
+      <c r="D206">
+        <v>338</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>49</v>
+      </c>
+      <c r="C207">
+        <v>276</v>
+      </c>
+      <c r="D207">
+        <v>325</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>50</v>
+      </c>
+      <c r="C208">
+        <v>276</v>
+      </c>
+      <c r="D208">
+        <v>326</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>49</v>
+      </c>
+      <c r="C209">
+        <v>276</v>
+      </c>
+      <c r="D209">
+        <v>325</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>51</v>
+      </c>
+      <c r="C210">
+        <v>329</v>
+      </c>
+      <c r="D210">
+        <v>380</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>51</v>
+      </c>
+      <c r="C211">
+        <v>339</v>
+      </c>
+      <c r="D211">
+        <v>390</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>51</v>
+      </c>
+      <c r="C212">
+        <v>340</v>
+      </c>
+      <c r="D212">
+        <v>391</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>70</v>
+      </c>
+      <c r="C213">
+        <v>341</v>
+      </c>
+      <c r="D213">
+        <v>411</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>208</v>
+      </c>
+      <c r="C214">
+        <v>383</v>
+      </c>
+      <c r="D214">
+        <v>591</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>212</v>
+      </c>
+      <c r="C215">
+        <v>391</v>
+      </c>
+      <c r="D215">
+        <v>603</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>202</v>
+      </c>
+      <c r="C216">
+        <v>392</v>
+      </c>
+      <c r="D216">
+        <v>594</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>209</v>
+      </c>
+      <c r="C217">
+        <v>395</v>
+      </c>
+      <c r="D217">
+        <v>604</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>379</v>
+      </c>
+      <c r="C218">
+        <v>493</v>
+      </c>
+      <c r="D218">
+        <v>872</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>465</v>
+      </c>
+      <c r="C219">
+        <v>498</v>
+      </c>
+      <c r="D219">
+        <v>963</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>567</v>
+      </c>
+      <c r="C220">
+        <v>499</v>
+      </c>
+      <c r="D220">
+        <v>1066</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>569</v>
+      </c>
+      <c r="C221">
+        <v>496</v>
+      </c>
+      <c r="D221">
+        <v>1065</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>650</v>
+      </c>
+      <c r="C222">
+        <v>494</v>
+      </c>
+      <c r="D222">
+        <v>1144</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>690</v>
+      </c>
+      <c r="C223">
+        <v>495</v>
+      </c>
+      <c r="D223">
+        <v>1185</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>687</v>
+      </c>
+      <c r="C224">
+        <v>496</v>
+      </c>
+      <c r="D224">
+        <v>1183</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>686</v>
+      </c>
+      <c r="C225">
+        <v>497</v>
+      </c>
+      <c r="D225">
+        <v>1183</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>413</v>
+      </c>
+      <c r="C226">
+        <v>256</v>
+      </c>
+      <c r="D226">
+        <v>669</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>404</v>
+      </c>
+      <c r="C227">
+        <v>244</v>
+      </c>
+      <c r="D227">
+        <v>648</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>138</v>
+      </c>
+      <c r="C228">
+        <v>224</v>
+      </c>
+      <c r="D228">
+        <v>362</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>122</v>
+      </c>
+      <c r="C229">
+        <v>233</v>
+      </c>
+      <c r="D229">
+        <v>355</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>79</v>
+      </c>
+      <c r="C230">
+        <v>202</v>
+      </c>
+      <c r="D230">
+        <v>281</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>75</v>
+      </c>
+      <c r="C231">
+        <v>200</v>
+      </c>
+      <c r="D231">
+        <v>275</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>76</v>
+      </c>
+      <c r="C232">
+        <v>200</v>
+      </c>
+      <c r="D232">
+        <v>276</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>76</v>
+      </c>
+      <c r="C233">
+        <v>200</v>
+      </c>
+      <c r="D233">
+        <v>276</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>50</v>
+      </c>
+      <c r="C234">
+        <v>202</v>
+      </c>
+      <c r="D234">
+        <v>252</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>44</v>
+      </c>
+      <c r="C235">
+        <v>202</v>
+      </c>
+      <c r="D235">
+        <v>246</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>47</v>
+      </c>
+      <c r="C236">
+        <v>185</v>
+      </c>
+      <c r="D236">
+        <v>232</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>47</v>
+      </c>
+      <c r="C237">
+        <v>184</v>
+      </c>
+      <c r="D237">
+        <v>231</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>40</v>
+      </c>
+      <c r="C238">
+        <v>195</v>
+      </c>
+      <c r="D238">
+        <v>235</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>39</v>
+      </c>
+      <c r="C239">
+        <v>194</v>
+      </c>
+      <c r="D239">
+        <v>233</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>38</v>
+      </c>
+      <c r="C240">
+        <v>194</v>
+      </c>
+      <c r="D240">
+        <v>232</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>38</v>
+      </c>
+      <c r="C241">
+        <v>194</v>
+      </c>
+      <c r="D241">
+        <v>232</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>32</v>
+      </c>
+      <c r="C242">
+        <v>204</v>
+      </c>
+      <c r="D242">
+        <v>236</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>31</v>
+      </c>
+      <c r="C243">
+        <v>204</v>
+      </c>
+      <c r="D243">
+        <v>235</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>31</v>
+      </c>
+      <c r="C244">
+        <v>204</v>
+      </c>
+      <c r="D244">
+        <v>235</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>34</v>
+      </c>
+      <c r="C245">
+        <v>205</v>
+      </c>
+      <c r="D245">
+        <v>239</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>43</v>
+      </c>
+      <c r="C246">
+        <v>205</v>
+      </c>
+      <c r="D246">
+        <v>248</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>48</v>
+      </c>
+      <c r="C247">
+        <v>204</v>
+      </c>
+      <c r="D247">
+        <v>252</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>49</v>
+      </c>
+      <c r="C248">
+        <v>195</v>
+      </c>
+      <c r="D248">
+        <v>244</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>49</v>
+      </c>
+      <c r="C249">
+        <v>194</v>
+      </c>
+      <c r="D249">
+        <v>243</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>50</v>
+      </c>
+      <c r="C250">
+        <v>188</v>
+      </c>
+      <c r="D250">
+        <v>238</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>51</v>
+      </c>
+      <c r="C251">
+        <v>187</v>
+      </c>
+      <c r="D251">
+        <v>238</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>53</v>
+      </c>
+      <c r="C252">
+        <v>187</v>
+      </c>
+      <c r="D252">
+        <v>240</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>55</v>
+      </c>
+      <c r="C253">
+        <v>187</v>
+      </c>
+      <c r="D253">
+        <v>242</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>129</v>
+      </c>
+      <c r="C254">
+        <v>205</v>
+      </c>
+      <c r="D254">
+        <v>334</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>176</v>
+      </c>
+      <c r="C255">
+        <v>222</v>
+      </c>
+      <c r="D255">
+        <v>398</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>228</v>
+      </c>
+      <c r="C256">
+        <v>221</v>
+      </c>
+      <c r="D256">
+        <v>449</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>225</v>
+      </c>
+      <c r="C257">
+        <v>221</v>
+      </c>
+      <c r="D257">
+        <v>446</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>221</v>
+      </c>
+      <c r="C258">
+        <v>205</v>
+      </c>
+      <c r="D258">
+        <v>426</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>241</v>
+      </c>
+      <c r="C259">
+        <v>207</v>
+      </c>
+      <c r="D259">
+        <v>448</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>148</v>
+      </c>
+      <c r="C260">
+        <v>195</v>
+      </c>
+      <c r="D260">
+        <v>343</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>204</v>
+      </c>
+      <c r="C261">
+        <v>200</v>
+      </c>
+      <c r="D261">
+        <v>404</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>440</v>
+      </c>
+      <c r="C262">
+        <v>506</v>
+      </c>
+      <c r="D262">
+        <v>946</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>447</v>
+      </c>
+      <c r="C263">
+        <v>525</v>
+      </c>
+      <c r="D263">
+        <v>972</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>414</v>
+      </c>
+      <c r="C264">
+        <v>503</v>
+      </c>
+      <c r="D264">
+        <v>917</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>423</v>
+      </c>
+      <c r="C265">
+        <v>517</v>
+      </c>
+      <c r="D265">
+        <v>940</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>638</v>
+      </c>
+      <c r="C266">
+        <v>647</v>
+      </c>
+      <c r="D266">
+        <v>1285</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>639</v>
+      </c>
+      <c r="C267">
+        <v>644</v>
+      </c>
+      <c r="D267">
+        <v>1283</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>639</v>
+      </c>
+      <c r="C268">
+        <v>645</v>
+      </c>
+      <c r="D268">
+        <v>1284</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>648</v>
+      </c>
+      <c r="C269">
+        <v>636</v>
+      </c>
+      <c r="D269">
+        <v>1284</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>671</v>
+      </c>
+      <c r="C270">
+        <v>624</v>
+      </c>
+      <c r="D270">
+        <v>1295</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>667</v>
+      </c>
+      <c r="C271">
+        <v>622</v>
+      </c>
+      <c r="D271">
+        <v>1289</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>667</v>
+      </c>
+      <c r="C272">
+        <v>622</v>
+      </c>
+      <c r="D272">
+        <v>1289</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>662</v>
+      </c>
+      <c r="C273">
+        <v>622</v>
+      </c>
+      <c r="D273">
+        <v>1284</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>646</v>
+      </c>
+      <c r="C274">
+        <v>658</v>
+      </c>
+      <c r="D274">
+        <v>1304</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>647</v>
+      </c>
+      <c r="C275">
+        <v>655</v>
+      </c>
+      <c r="D275">
+        <v>1302</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>655</v>
+      </c>
+      <c r="C276">
+        <v>655</v>
+      </c>
+      <c r="D276">
+        <v>1310</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>658</v>
+      </c>
+      <c r="C277">
+        <v>653</v>
+      </c>
+      <c r="D277">
+        <v>1311</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>620</v>
+      </c>
+      <c r="C278">
+        <v>649</v>
+      </c>
+      <c r="D278">
+        <v>1269</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>622</v>
+      </c>
+      <c r="C279">
+        <v>646</v>
+      </c>
+      <c r="D279">
+        <v>1268</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>625</v>
+      </c>
+      <c r="C280">
+        <v>646</v>
+      </c>
+      <c r="D280">
+        <v>1271</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>613</v>
+      </c>
+      <c r="C281">
+        <v>656</v>
+      </c>
+      <c r="D281">
+        <v>1269</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>615</v>
+      </c>
+      <c r="C282">
+        <v>601</v>
+      </c>
+      <c r="D282">
+        <v>1216</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>614</v>
+      </c>
+      <c r="C283">
+        <v>594</v>
+      </c>
+      <c r="D283">
+        <v>1208</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>614</v>
+      </c>
+      <c r="C284">
+        <v>594</v>
+      </c>
+      <c r="D284">
+        <v>1208</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>610</v>
+      </c>
+      <c r="C285">
+        <v>592</v>
+      </c>
+      <c r="D285">
+        <v>1202</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>556</v>
+      </c>
+      <c r="C286">
+        <v>385</v>
+      </c>
+      <c r="D286">
+        <v>941</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>563</v>
+      </c>
+      <c r="C287">
+        <v>354</v>
+      </c>
+      <c r="D287">
+        <v>917</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>562</v>
+      </c>
+      <c r="C288">
+        <v>355</v>
+      </c>
+      <c r="D288">
+        <v>917</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>550</v>
+      </c>
+      <c r="C289">
+        <v>353</v>
+      </c>
+      <c r="D289">
+        <v>903</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>322</v>
+      </c>
+      <c r="C290">
+        <v>304</v>
+      </c>
+      <c r="D290">
+        <v>626</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>318</v>
+      </c>
+      <c r="C291">
+        <v>307</v>
+      </c>
+      <c r="D291">
+        <v>625</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>318</v>
+      </c>
+      <c r="C292">
+        <v>341</v>
+      </c>
+      <c r="D292">
+        <v>659</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>322</v>
+      </c>
+      <c r="C293">
+        <v>341</v>
+      </c>
+      <c r="D293">
+        <v>663</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>400</v>
+      </c>
+      <c r="C294">
+        <v>339</v>
+      </c>
+      <c r="D294">
+        <v>739</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>390</v>
+      </c>
+      <c r="C295">
+        <v>309</v>
+      </c>
+      <c r="D295">
+        <v>699</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>390</v>
+      </c>
+      <c r="C296">
+        <v>340</v>
+      </c>
+      <c r="D296">
+        <v>730</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>390</v>
+      </c>
+      <c r="C297">
+        <v>323</v>
+      </c>
+      <c r="D297">
+        <v>713</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>405</v>
+      </c>
+      <c r="C298">
+        <v>337</v>
+      </c>
+      <c r="D298">
+        <v>742</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>405</v>
+      </c>
+      <c r="C299">
+        <v>327</v>
+      </c>
+      <c r="D299">
+        <v>732</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>406</v>
+      </c>
+      <c r="C300">
+        <v>329</v>
+      </c>
+      <c r="D300">
+        <v>735</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>357</v>
+      </c>
+      <c r="C301">
+        <v>327</v>
+      </c>
+      <c r="D301">
+        <v>684</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>286</v>
+      </c>
+      <c r="C302">
+        <v>308</v>
+      </c>
+      <c r="D302">
+        <v>594</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>282</v>
+      </c>
+      <c r="C303">
+        <v>303</v>
+      </c>
+      <c r="D303">
+        <v>585</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>255</v>
+      </c>
+      <c r="C304">
+        <v>304</v>
+      </c>
+      <c r="D304">
+        <v>559</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>250</v>
+      </c>
+      <c r="C305">
+        <v>304</v>
+      </c>
+      <c r="D305">
+        <v>554</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>114</v>
+      </c>
+      <c r="C306">
+        <v>258</v>
+      </c>
+      <c r="D306">
+        <v>372</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>81</v>
+      </c>
+      <c r="C307">
+        <v>261</v>
+      </c>
+      <c r="D307">
+        <v>342</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>80</v>
+      </c>
+      <c r="C308">
+        <v>265</v>
+      </c>
+      <c r="D308">
+        <v>345</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>91</v>
+      </c>
+      <c r="C309">
+        <v>266</v>
+      </c>
+      <c r="D309">
+        <v>357</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>336</v>
+      </c>
+      <c r="C310">
+        <v>378</v>
+      </c>
+      <c r="D310">
+        <v>714</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>356</v>
+      </c>
+      <c r="C311">
+        <v>390</v>
+      </c>
+      <c r="D311">
+        <v>746</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>357</v>
+      </c>
+      <c r="C312">
+        <v>403</v>
+      </c>
+      <c r="D312">
+        <v>760</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>386</v>
+      </c>
+      <c r="C313">
+        <v>412</v>
+      </c>
+      <c r="D313">
+        <v>798</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>553</v>
+      </c>
+      <c r="C314">
+        <v>451</v>
+      </c>
+      <c r="D314">
+        <v>1004</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>654</v>
+      </c>
+      <c r="C315">
+        <v>459</v>
+      </c>
+      <c r="D315">
+        <v>1113</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>829</v>
+      </c>
+      <c r="C316">
+        <v>478</v>
+      </c>
+      <c r="D316">
+        <v>1307</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>917</v>
+      </c>
+      <c r="C317">
+        <v>480</v>
+      </c>
+      <c r="D317">
+        <v>1397</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>956</v>
+      </c>
+      <c r="C318">
+        <v>468</v>
+      </c>
+      <c r="D318">
+        <v>1424</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>986</v>
+      </c>
+      <c r="C319">
+        <v>514</v>
+      </c>
+      <c r="D319">
+        <v>1500</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>1100</v>
+      </c>
+      <c r="C320">
+        <v>674</v>
+      </c>
+      <c r="D320">
+        <v>1774</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>1108</v>
+      </c>
+      <c r="C321">
+        <v>678</v>
+      </c>
+      <c r="D321">
+        <v>1786</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1273</v>
+      </c>
+      <c r="C322">
+        <v>646</v>
+      </c>
+      <c r="D322">
+        <v>1919</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>1218</v>
+      </c>
+      <c r="C323">
+        <v>650</v>
+      </c>
+      <c r="D323">
+        <v>1868</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1141</v>
+      </c>
+      <c r="C324">
+        <v>634</v>
+      </c>
+      <c r="D324">
+        <v>1775</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>1122</v>
+      </c>
+      <c r="C325">
+        <v>638</v>
+      </c>
+      <c r="D325">
+        <v>1760</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>1050</v>
+      </c>
+      <c r="C326">
+        <v>462</v>
+      </c>
+      <c r="D326">
+        <v>1512</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>1003</v>
+      </c>
+      <c r="C327">
+        <v>440</v>
+      </c>
+      <c r="D327">
+        <v>1443</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -482,6 +194,306 @@
   </si>
   <si>
     <t>13.10.202654</t>
+  </si>
+  <si>
+    <t>13.10.202655</t>
+  </si>
+  <si>
+    <t>13.10.202656</t>
+  </si>
+  <si>
+    <t>13.10.202657</t>
+  </si>
+  <si>
+    <t>13.10.202658</t>
+  </si>
+  <si>
+    <t>13.10.202659</t>
+  </si>
+  <si>
+    <t>13.10.202660</t>
+  </si>
+  <si>
+    <t>13.10.202661</t>
+  </si>
+  <si>
+    <t>13.10.202662</t>
+  </si>
+  <si>
+    <t>13.10.202663</t>
+  </si>
+  <si>
+    <t>13.10.202664</t>
+  </si>
+  <si>
+    <t>13.10.202665</t>
+  </si>
+  <si>
+    <t>13.10.202666</t>
+  </si>
+  <si>
+    <t>13.10.202667</t>
+  </si>
+  <si>
+    <t>13.10.202668</t>
+  </si>
+  <si>
+    <t>13.10.202669</t>
+  </si>
+  <si>
+    <t>13.10.202670</t>
+  </si>
+  <si>
+    <t>13.10.202671</t>
+  </si>
+  <si>
+    <t>13.10.202672</t>
+  </si>
+  <si>
+    <t>13.10.202673</t>
+  </si>
+  <si>
+    <t>13.10.202674</t>
+  </si>
+  <si>
+    <t>13.10.202675</t>
+  </si>
+  <si>
+    <t>13.10.202676</t>
+  </si>
+  <si>
+    <t>13.10.202677</t>
+  </si>
+  <si>
+    <t>13.10.202678</t>
+  </si>
+  <si>
+    <t>13.10.202679</t>
+  </si>
+  <si>
+    <t>13.10.202680</t>
+  </si>
+  <si>
+    <t>13.10.202681</t>
+  </si>
+  <si>
+    <t>13.10.202682</t>
+  </si>
+  <si>
+    <t>13.10.202683</t>
+  </si>
+  <si>
+    <t>13.10.202684</t>
+  </si>
+  <si>
+    <t>13.10.202685</t>
+  </si>
+  <si>
+    <t>13.10.202686</t>
+  </si>
+  <si>
+    <t>13.10.202687</t>
+  </si>
+  <si>
+    <t>13.10.202688</t>
+  </si>
+  <si>
+    <t>13.10.202689</t>
+  </si>
+  <si>
+    <t>13.10.202690</t>
+  </si>
+  <si>
+    <t>13.10.202691</t>
+  </si>
+  <si>
+    <t>13.10.202692</t>
+  </si>
+  <si>
+    <t>13.10.202693</t>
+  </si>
+  <si>
+    <t>13.10.202694</t>
+  </si>
+  <si>
+    <t>13.10.202695</t>
+  </si>
+  <si>
+    <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
   </si>
 </sst>
 </file>
@@ -843,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -868,16 +880,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="C2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D2">
-        <v>626</v>
+        <v>529</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -888,16 +900,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>318</v>
+        <v>218</v>
       </c>
       <c r="C3">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -908,16 +920,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>318</v>
+        <v>218</v>
       </c>
       <c r="C4">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="D4">
-        <v>659</v>
+        <v>500</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -928,16 +940,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>322</v>
+        <v>218</v>
       </c>
       <c r="C5">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="D5">
-        <v>663</v>
+        <v>499</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -948,16 +960,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>218</v>
       </c>
       <c r="C6">
-        <v>339</v>
+        <v>230</v>
       </c>
       <c r="D6">
-        <v>739</v>
+        <v>448</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -968,16 +980,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>390</v>
+        <v>217</v>
       </c>
       <c r="C7">
-        <v>309</v>
+        <v>225</v>
       </c>
       <c r="D7">
-        <v>699</v>
+        <v>442</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -988,16 +1000,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>390</v>
+        <v>224</v>
       </c>
       <c r="C8">
-        <v>340</v>
+        <v>225</v>
       </c>
       <c r="D8">
-        <v>730</v>
+        <v>449</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1008,16 +1020,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>390</v>
+        <v>224</v>
       </c>
       <c r="C9">
-        <v>323</v>
+        <v>225</v>
       </c>
       <c r="D9">
-        <v>713</v>
+        <v>449</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1028,16 +1040,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="C10">
-        <v>337</v>
+        <v>240</v>
       </c>
       <c r="D10">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1048,16 +1060,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>405</v>
+        <v>503</v>
       </c>
       <c r="C11">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="D11">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1068,16 +1080,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>406</v>
+        <v>503</v>
       </c>
       <c r="C12">
-        <v>329</v>
+        <v>241</v>
       </c>
       <c r="D12">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1088,16 +1100,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>357</v>
+        <v>502</v>
       </c>
       <c r="C13">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="D13">
-        <v>684</v>
+        <v>741</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1108,16 +1120,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="C14">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="D14">
-        <v>594</v>
+        <v>387</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1128,16 +1140,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="C15">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="D15">
-        <v>585</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1148,16 +1160,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="C16">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="D16">
-        <v>559</v>
+        <v>366</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1168,16 +1180,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="C17">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="D17">
-        <v>554</v>
+        <v>365</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1188,16 +1200,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C18">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="D18">
-        <v>372</v>
+        <v>230</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1208,16 +1220,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>261</v>
+        <v>182</v>
       </c>
       <c r="D19">
-        <v>342</v>
+        <v>227</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1228,16 +1240,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="D20">
-        <v>345</v>
+        <v>226</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1248,16 +1260,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C21">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="D21">
-        <v>357</v>
+        <v>229</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1268,16 +1280,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>336</v>
+        <v>57</v>
       </c>
       <c r="C22">
-        <v>378</v>
+        <v>193</v>
       </c>
       <c r="D22">
-        <v>714</v>
+        <v>250</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1288,16 +1300,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>356</v>
+        <v>71</v>
       </c>
       <c r="C23">
-        <v>390</v>
+        <v>193</v>
       </c>
       <c r="D23">
-        <v>746</v>
+        <v>264</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1308,16 +1320,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>357</v>
+        <v>78</v>
       </c>
       <c r="C24">
-        <v>403</v>
+        <v>193</v>
       </c>
       <c r="D24">
-        <v>760</v>
+        <v>271</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1328,16 +1340,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>386</v>
+        <v>109</v>
       </c>
       <c r="C25">
-        <v>412</v>
+        <v>200</v>
       </c>
       <c r="D25">
-        <v>798</v>
+        <v>309</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1348,16 +1360,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>553</v>
+        <v>799</v>
       </c>
       <c r="C26">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="D26">
-        <v>1004</v>
+        <v>1289</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1368,16 +1380,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>654</v>
+        <v>822</v>
       </c>
       <c r="C27">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="D27">
-        <v>1113</v>
+        <v>1336</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1388,16 +1400,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="C28">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="D28">
-        <v>1307</v>
+        <v>1331</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1408,16 +1420,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>917</v>
+        <v>819</v>
       </c>
       <c r="C29">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="D29">
-        <v>1397</v>
+        <v>1335</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1428,16 +1440,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>956</v>
+        <v>892</v>
       </c>
       <c r="C30">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="D30">
-        <v>1424</v>
+        <v>1406</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1448,16 +1460,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>986</v>
+        <v>902</v>
       </c>
       <c r="C31">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="D31">
-        <v>1500</v>
+        <v>1428</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1468,16 +1480,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>1100</v>
+        <v>903</v>
       </c>
       <c r="C32">
-        <v>674</v>
+        <v>527</v>
       </c>
       <c r="D32">
-        <v>1774</v>
+        <v>1430</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1488,16 +1500,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>1108</v>
+        <v>903</v>
       </c>
       <c r="C33">
-        <v>678</v>
+        <v>526</v>
       </c>
       <c r="D33">
-        <v>1786</v>
+        <v>1429</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1508,16 +1520,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>1273</v>
+        <v>863</v>
       </c>
       <c r="C34">
-        <v>646</v>
+        <v>508</v>
       </c>
       <c r="D34">
-        <v>1919</v>
+        <v>1371</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1528,16 +1540,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>1218</v>
+        <v>815</v>
       </c>
       <c r="C35">
-        <v>650</v>
+        <v>498</v>
       </c>
       <c r="D35">
-        <v>1868</v>
+        <v>1313</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1548,16 +1560,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>1141</v>
+        <v>758</v>
       </c>
       <c r="C36">
-        <v>634</v>
+        <v>506</v>
       </c>
       <c r="D36">
-        <v>1775</v>
+        <v>1264</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1568,16 +1580,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>1122</v>
+        <v>743</v>
       </c>
       <c r="C37">
-        <v>638</v>
+        <v>503</v>
       </c>
       <c r="D37">
-        <v>1760</v>
+        <v>1246</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1588,16 +1600,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>1050</v>
+        <v>752</v>
       </c>
       <c r="C38">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D38">
-        <v>1512</v>
+        <v>1223</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1608,16 +1620,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>1003</v>
+        <v>753</v>
       </c>
       <c r="C39">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="D39">
-        <v>1443</v>
+        <v>1221</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1628,16 +1640,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>1076</v>
+        <v>881</v>
       </c>
       <c r="C40">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="D40">
-        <v>1514</v>
+        <v>1352</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1648,16 +1660,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>973</v>
+        <v>865</v>
       </c>
       <c r="C41">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="D41">
-        <v>1398</v>
+        <v>1330</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1668,16 +1680,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>644</v>
+        <v>133</v>
       </c>
       <c r="C42">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="D42">
-        <v>878</v>
+        <v>348</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1688,16 +1700,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>612</v>
+        <v>114</v>
       </c>
       <c r="C43">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="D43">
-        <v>844</v>
+        <v>305</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1708,16 +1720,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>612</v>
+        <v>115</v>
       </c>
       <c r="C44">
-        <v>249</v>
+        <v>195</v>
       </c>
       <c r="D44">
-        <v>861</v>
+        <v>310</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1728,16 +1740,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>672</v>
+        <v>111</v>
       </c>
       <c r="C45">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="D45">
-        <v>878</v>
+        <v>300</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1748,16 +1760,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>637</v>
+        <v>54</v>
       </c>
       <c r="C46">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="D46">
-        <v>912</v>
+        <v>252</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1768,16 +1780,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>641</v>
+        <v>50</v>
       </c>
       <c r="C47">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="D47">
-        <v>927</v>
+        <v>249</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1788,16 +1800,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>643</v>
+        <v>50</v>
       </c>
       <c r="C48">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="D48">
-        <v>929</v>
+        <v>251</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1808,16 +1820,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>642</v>
+        <v>50</v>
       </c>
       <c r="C49">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="D49">
-        <v>928</v>
+        <v>249</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1828,16 +1840,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>523</v>
+        <v>42</v>
       </c>
       <c r="C50">
-        <v>261</v>
+        <v>191</v>
       </c>
       <c r="D50">
-        <v>784</v>
+        <v>233</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1848,16 +1860,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>518</v>
+        <v>44</v>
       </c>
       <c r="C51">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="D51">
-        <v>779</v>
+        <v>238</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1868,16 +1880,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>511</v>
+        <v>44</v>
       </c>
       <c r="C52">
-        <v>265</v>
+        <v>168</v>
       </c>
       <c r="D52">
-        <v>776</v>
+        <v>212</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1888,16 +1900,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>513</v>
+        <v>51</v>
       </c>
       <c r="C53">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="D53">
-        <v>773</v>
+        <v>217</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1908,16 +1920,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>700</v>
+        <v>47</v>
       </c>
       <c r="C54">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="D54">
-        <v>952</v>
+        <v>251</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1928,16 +1940,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>654</v>
+        <v>53</v>
       </c>
       <c r="C55">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D55">
-        <v>868</v>
+        <v>257</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1948,16 +1960,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>657</v>
+        <v>54</v>
       </c>
       <c r="C56">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D56">
-        <v>868</v>
+        <v>258</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1968,16 +1980,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>645</v>
+        <v>53</v>
       </c>
       <c r="C57">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D57">
-        <v>857</v>
+        <v>257</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1988,16 +2000,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>397</v>
+        <v>84</v>
       </c>
       <c r="C58">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="D58">
-        <v>616</v>
+        <v>277</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2008,16 +2020,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>382</v>
+        <v>73</v>
       </c>
       <c r="C59">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="D59">
-        <v>603</v>
+        <v>266</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2028,16 +2040,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>375</v>
+        <v>73</v>
       </c>
       <c r="C60">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="D60">
-        <v>599</v>
+        <v>266</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2048,16 +2060,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>379</v>
+        <v>68</v>
       </c>
       <c r="C61">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="D61">
-        <v>601</v>
+        <v>261</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2068,16 +2080,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>403</v>
+        <v>129</v>
       </c>
       <c r="C62">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D62">
-        <v>619</v>
+        <v>344</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2088,16 +2100,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>399</v>
+        <v>118</v>
       </c>
       <c r="C63">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D63">
-        <v>609</v>
+        <v>345</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2108,16 +2120,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>403</v>
+        <v>102</v>
       </c>
       <c r="C64">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="D64">
-        <v>606</v>
+        <v>329</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2128,16 +2140,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>433</v>
+        <v>145</v>
       </c>
       <c r="C65">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="D65">
-        <v>643</v>
+        <v>388</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2148,16 +2160,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>970</v>
+        <v>722</v>
       </c>
       <c r="C66">
-        <v>440</v>
+        <v>613</v>
       </c>
       <c r="D66">
-        <v>1410</v>
+        <v>1335</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2168,16 +2180,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>1025</v>
+        <v>733</v>
       </c>
       <c r="C67">
-        <v>459</v>
+        <v>638</v>
       </c>
       <c r="D67">
-        <v>1484</v>
+        <v>1371</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2188,16 +2200,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>968</v>
+        <v>732</v>
       </c>
       <c r="C68">
-        <v>464</v>
+        <v>654</v>
       </c>
       <c r="D68">
-        <v>1432</v>
+        <v>1386</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2208,16 +2220,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>970</v>
+        <v>743</v>
       </c>
       <c r="C69">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="D69">
-        <v>1453</v>
+        <v>1401</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2228,16 +2240,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>901</v>
+        <v>788</v>
       </c>
       <c r="C70">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="D70">
-        <v>1509</v>
+        <v>1428</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2248,16 +2260,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="C71">
-        <v>618</v>
+        <v>675</v>
       </c>
       <c r="D71">
-        <v>1518</v>
+        <v>1537</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2268,16 +2280,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="C72">
-        <v>618</v>
+        <v>681</v>
       </c>
       <c r="D72">
-        <v>1519</v>
+        <v>1595</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2288,16 +2300,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>904</v>
+        <v>928</v>
       </c>
       <c r="C73">
-        <v>648</v>
+        <v>684</v>
       </c>
       <c r="D73">
-        <v>1552</v>
+        <v>1612</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2308,16 +2320,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>902</v>
+        <v>1001</v>
       </c>
       <c r="C74">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="D74">
-        <v>1588</v>
+        <v>1678</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2328,16 +2340,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>954</v>
+        <v>978</v>
       </c>
       <c r="C75">
-        <v>698</v>
+        <v>678</v>
       </c>
       <c r="D75">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2348,16 +2360,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>887</v>
+        <v>976</v>
       </c>
       <c r="C76">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="D76">
-        <v>1584</v>
+        <v>1658</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2368,16 +2380,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="C77">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="D77">
-        <v>1642</v>
+        <v>1612</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2388,16 +2400,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>928</v>
+        <v>950</v>
       </c>
       <c r="C78">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D78">
-        <v>1605</v>
+        <v>1635</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2408,16 +2420,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>903</v>
+        <v>975</v>
       </c>
       <c r="C79">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="D79">
-        <v>1578</v>
+        <v>1660</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2428,16 +2440,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>910</v>
+        <v>972</v>
       </c>
       <c r="C80">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D80">
-        <v>1595</v>
+        <v>1659</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2448,16 +2460,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="C81">
-        <v>685</v>
+        <v>649</v>
       </c>
       <c r="D81">
-        <v>1597</v>
+        <v>1576</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2468,16 +2480,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C82">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="D82">
-        <v>1548</v>
+        <v>1526</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2488,16 +2500,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="C83">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="D83">
-        <v>1500</v>
+        <v>1516</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2508,16 +2520,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>897</v>
+        <v>875</v>
       </c>
       <c r="C84">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="D84">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2528,16 +2540,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>915</v>
+        <v>872</v>
       </c>
       <c r="C85">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="D85">
-        <v>1521</v>
+        <v>1509</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2548,16 +2560,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C86">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="D86">
-        <v>1386</v>
+        <v>1436</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2568,16 +2580,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="C87">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="D87">
-        <v>1351</v>
+        <v>1429</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2588,16 +2600,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>729</v>
+        <v>793</v>
       </c>
       <c r="C88">
-        <v>587</v>
+        <v>637</v>
       </c>
       <c r="D88">
-        <v>1316</v>
+        <v>1430</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2608,16 +2620,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="C89">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="D89">
-        <v>1326</v>
+        <v>1427</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2628,16 +2640,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="C90">
-        <v>532</v>
+        <v>624</v>
       </c>
       <c r="D90">
-        <v>1182</v>
+        <v>1299</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2648,16 +2660,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="C91">
-        <v>525</v>
+        <v>636</v>
       </c>
       <c r="D91">
-        <v>1216</v>
+        <v>1300</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2668,16 +2680,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>719</v>
+        <v>658</v>
       </c>
       <c r="C92">
-        <v>527</v>
+        <v>637</v>
       </c>
       <c r="D92">
-        <v>1246</v>
+        <v>1295</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2688,16 +2700,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>716</v>
+        <v>656</v>
       </c>
       <c r="C93">
-        <v>524</v>
+        <v>652</v>
       </c>
       <c r="D93">
-        <v>1240</v>
+        <v>1308</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2708,16 +2720,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>509</v>
+        <v>428</v>
       </c>
       <c r="C94">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="D94">
-        <v>901</v>
+        <v>792</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2728,16 +2740,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>499</v>
+        <v>385</v>
       </c>
       <c r="C95">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="D95">
-        <v>885</v>
+        <v>727</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2748,16 +2760,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>475</v>
+        <v>383</v>
       </c>
       <c r="C96">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="D96">
-        <v>883</v>
+        <v>724</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2768,16 +2780,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C97">
-        <v>434</v>
+        <v>346</v>
       </c>
       <c r="D97">
-        <v>877</v>
+        <v>738</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2788,16 +2800,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>240</v>
+        <v>794</v>
       </c>
       <c r="C98">
-        <v>289</v>
+        <v>417</v>
       </c>
       <c r="D98">
-        <v>529</v>
+        <v>1211</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2808,16 +2820,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>218</v>
+        <v>886</v>
       </c>
       <c r="C99">
-        <v>282</v>
+        <v>418</v>
       </c>
       <c r="D99">
-        <v>500</v>
+        <v>1304</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2828,16 +2840,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>218</v>
+        <v>883</v>
       </c>
       <c r="C100">
-        <v>282</v>
+        <v>417</v>
       </c>
       <c r="D100">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2848,16 +2860,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>218</v>
+        <v>818</v>
       </c>
       <c r="C101">
-        <v>281</v>
+        <v>416</v>
       </c>
       <c r="D101">
-        <v>499</v>
+        <v>1234</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2868,16 +2880,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>218</v>
+        <v>783</v>
       </c>
       <c r="C102">
-        <v>230</v>
+        <v>416</v>
       </c>
       <c r="D102">
-        <v>448</v>
+        <v>1199</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2888,16 +2900,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>217</v>
+        <v>729</v>
       </c>
       <c r="C103">
-        <v>225</v>
+        <v>414</v>
       </c>
       <c r="D103">
-        <v>442</v>
+        <v>1143</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2908,16 +2920,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>224</v>
+        <v>727</v>
       </c>
       <c r="C104">
-        <v>225</v>
+        <v>415</v>
       </c>
       <c r="D104">
-        <v>449</v>
+        <v>1142</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2928,16 +2940,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>224</v>
+        <v>723</v>
       </c>
       <c r="C105">
-        <v>225</v>
+        <v>415</v>
       </c>
       <c r="D105">
-        <v>449</v>
+        <v>1138</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2948,16 +2960,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>484</v>
+        <v>718</v>
       </c>
       <c r="C106">
-        <v>240</v>
+        <v>415</v>
       </c>
       <c r="D106">
-        <v>724</v>
+        <v>1133</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2968,16 +2980,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>503</v>
+        <v>714</v>
       </c>
       <c r="C107">
-        <v>241</v>
+        <v>415</v>
       </c>
       <c r="D107">
-        <v>744</v>
+        <v>1129</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2988,16 +3000,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>503</v>
+        <v>714</v>
       </c>
       <c r="C108">
-        <v>241</v>
+        <v>415</v>
       </c>
       <c r="D108">
-        <v>744</v>
+        <v>1129</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3008,16 +3020,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>502</v>
+        <v>714</v>
       </c>
       <c r="C109">
-        <v>239</v>
+        <v>415</v>
       </c>
       <c r="D109">
-        <v>741</v>
+        <v>1129</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3028,16 +3040,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>221</v>
+        <v>701</v>
       </c>
       <c r="C110">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="D110">
-        <v>387</v>
+        <v>1078</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3048,16 +3060,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>200</v>
+        <v>699</v>
       </c>
       <c r="C111">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="D111">
-        <v>364</v>
+        <v>1073</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3068,16 +3080,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>202</v>
+        <v>701</v>
       </c>
       <c r="C112">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="D112">
-        <v>366</v>
+        <v>1075</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3088,16 +3100,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>201</v>
+        <v>701</v>
       </c>
       <c r="C113">
-        <v>164</v>
+        <v>375</v>
       </c>
       <c r="D113">
-        <v>365</v>
+        <v>1076</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3108,16 +3120,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>49</v>
+        <v>715</v>
       </c>
       <c r="C114">
-        <v>181</v>
+        <v>375</v>
       </c>
       <c r="D114">
-        <v>230</v>
+        <v>1090</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3128,16 +3140,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>45</v>
+        <v>714</v>
       </c>
       <c r="C115">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="D115">
-        <v>227</v>
+        <v>1089</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3148,16 +3160,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>44</v>
+        <v>715</v>
       </c>
       <c r="C116">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="D116">
-        <v>226</v>
+        <v>1090</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3168,16 +3180,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>47</v>
+        <v>747</v>
       </c>
       <c r="C117">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="D117">
-        <v>229</v>
+        <v>1124</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3188,16 +3200,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>57</v>
+        <v>777</v>
       </c>
       <c r="C118">
-        <v>193</v>
+        <v>441</v>
       </c>
       <c r="D118">
-        <v>250</v>
+        <v>1218</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3208,16 +3220,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>71</v>
+        <v>787</v>
       </c>
       <c r="C119">
-        <v>193</v>
+        <v>454</v>
       </c>
       <c r="D119">
-        <v>264</v>
+        <v>1241</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3228,16 +3240,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>78</v>
+        <v>839</v>
       </c>
       <c r="C120">
-        <v>193</v>
+        <v>491</v>
       </c>
       <c r="D120">
-        <v>271</v>
+        <v>1330</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3248,16 +3260,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>109</v>
+        <v>875</v>
       </c>
       <c r="C121">
-        <v>200</v>
+        <v>495</v>
       </c>
       <c r="D121">
-        <v>309</v>
+        <v>1370</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3268,16 +3280,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>799</v>
+        <v>935</v>
       </c>
       <c r="C122">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="D122">
-        <v>1289</v>
+        <v>1457</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3288,16 +3300,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>822</v>
+        <v>944</v>
       </c>
       <c r="C123">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="D123">
-        <v>1336</v>
+        <v>1467</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3308,16 +3320,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>818</v>
+        <v>936</v>
       </c>
       <c r="C124">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D124">
-        <v>1331</v>
+        <v>1461</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3328,16 +3340,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>819</v>
+        <v>938</v>
       </c>
       <c r="C125">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="D125">
-        <v>1335</v>
+        <v>1464</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3348,16 +3360,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>892</v>
+        <v>1010</v>
       </c>
       <c r="C126">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="D126">
-        <v>1406</v>
+        <v>1546</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3368,16 +3380,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>902</v>
+        <v>1024</v>
       </c>
       <c r="C127">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="D127">
-        <v>1428</v>
+        <v>1559</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3388,16 +3400,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>903</v>
+        <v>1016</v>
       </c>
       <c r="C128">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D128">
-        <v>1430</v>
+        <v>1555</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3408,16 +3420,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>903</v>
+        <v>1019</v>
       </c>
       <c r="C129">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="D129">
-        <v>1429</v>
+        <v>1524</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3428,16 +3440,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>863</v>
+        <v>1020</v>
       </c>
       <c r="C130">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="D130">
-        <v>1371</v>
+        <v>1514</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3448,16 +3460,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>815</v>
+        <v>911</v>
       </c>
       <c r="C131">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D131">
-        <v>1313</v>
+        <v>1397</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3468,16 +3480,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>758</v>
+        <v>832</v>
       </c>
       <c r="C132">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="D132">
-        <v>1264</v>
+        <v>1312</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3488,16 +3500,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>743</v>
+        <v>825</v>
       </c>
       <c r="C133">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D133">
-        <v>1246</v>
+        <v>1308</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3508,16 +3520,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>752</v>
+        <v>871</v>
       </c>
       <c r="C134">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D134">
-        <v>1223</v>
+        <v>1341</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3528,16 +3540,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="C135">
         <v>468</v>
       </c>
       <c r="D135">
-        <v>1221</v>
+        <v>1261</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3548,16 +3560,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>881</v>
+        <v>826</v>
       </c>
       <c r="C136">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="D136">
-        <v>1352</v>
+        <v>1312</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3568,16 +3580,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C137">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="D137">
-        <v>1330</v>
+        <v>1342</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3588,16 +3600,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>133</v>
+        <v>782</v>
       </c>
       <c r="C138">
-        <v>215</v>
+        <v>440</v>
       </c>
       <c r="D138">
-        <v>348</v>
+        <v>1222</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3608,16 +3620,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>114</v>
+        <v>785</v>
       </c>
       <c r="C139">
-        <v>191</v>
+        <v>437</v>
       </c>
       <c r="D139">
-        <v>305</v>
+        <v>1222</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3628,16 +3640,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>115</v>
+        <v>785</v>
       </c>
       <c r="C140">
-        <v>195</v>
+        <v>426</v>
       </c>
       <c r="D140">
-        <v>310</v>
+        <v>1211</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3648,16 +3660,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>111</v>
+        <v>781</v>
       </c>
       <c r="C141">
-        <v>189</v>
+        <v>417</v>
       </c>
       <c r="D141">
-        <v>300</v>
+        <v>1198</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3668,16 +3680,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>54</v>
+        <v>719</v>
       </c>
       <c r="C142">
-        <v>198</v>
+        <v>427</v>
       </c>
       <c r="D142">
-        <v>252</v>
+        <v>1146</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3688,16 +3700,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>50</v>
+        <v>716</v>
       </c>
       <c r="C143">
-        <v>199</v>
+        <v>429</v>
       </c>
       <c r="D143">
-        <v>249</v>
+        <v>1145</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3708,16 +3720,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>50</v>
+        <v>714</v>
       </c>
       <c r="C144">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="D144">
-        <v>251</v>
+        <v>1151</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3728,16 +3740,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>50</v>
+        <v>683</v>
       </c>
       <c r="C145">
-        <v>199</v>
+        <v>459</v>
       </c>
       <c r="D145">
-        <v>249</v>
+        <v>1142</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3748,16 +3760,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>42</v>
+        <v>447</v>
       </c>
       <c r="C146">
-        <v>191</v>
+        <v>455</v>
       </c>
       <c r="D146">
-        <v>233</v>
+        <v>902</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3768,16 +3780,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>44</v>
+        <v>432</v>
       </c>
       <c r="C147">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="D147">
-        <v>238</v>
+        <v>885</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3788,16 +3800,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>44</v>
+        <v>415</v>
       </c>
       <c r="C148">
-        <v>168</v>
+        <v>448</v>
       </c>
       <c r="D148">
-        <v>212</v>
+        <v>863</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3808,16 +3820,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="C149">
-        <v>166</v>
+        <v>379</v>
       </c>
       <c r="D149">
-        <v>217</v>
+        <v>603</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3828,16 +3840,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="C150">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="D150">
-        <v>251</v>
+        <v>543</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3848,22 +3860,102 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D151">
-        <v>53</v>
+        <v>443</v>
       </c>
       <c r="E151">
         <v>54</v>
       </c>
       <c r="F151" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="2">
+        <v>46309.5625</v>
+      </c>
+      <c r="B152">
+        <v>164</v>
+      </c>
+      <c r="C152">
+        <v>266</v>
+      </c>
+      <c r="D152">
+        <v>430</v>
+      </c>
+      <c r="E152">
+        <v>55</v>
+      </c>
+      <c r="F152" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>291</v>
+      </c>
+      <c r="C153">
+        <v>278</v>
+      </c>
+      <c r="D153">
+        <v>569</v>
+      </c>
+      <c r="E153">
+        <v>56</v>
+      </c>
+      <c r="F153" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>151</v>
+      </c>
+      <c r="C154">
+        <v>329</v>
+      </c>
+      <c r="D154">
+        <v>480</v>
+      </c>
+      <c r="E154">
+        <v>57</v>
+      </c>
+      <c r="F154" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B155">
+        <v>160</v>
+      </c>
+      <c r="C155">
+        <v>330</v>
+      </c>
+      <c r="D155">
+        <v>490</v>
+      </c>
+      <c r="E155">
+        <v>58</v>
+      </c>
+      <c r="F155" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,466 +34,445 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
   </si>
 </sst>
 </file>
@@ -855,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -880,16 +859,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="C2">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="D2">
-        <v>529</v>
+        <v>333</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -900,16 +879,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="C3">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="D3">
-        <v>500</v>
+        <v>352</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -920,16 +899,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="C4">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="D4">
-        <v>500</v>
+        <v>296</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -940,16 +919,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="D5">
-        <v>499</v>
+        <v>293</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -960,16 +939,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D6">
-        <v>448</v>
+        <v>286</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -980,16 +959,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>217</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D7">
-        <v>442</v>
+        <v>265</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1000,16 +979,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>224</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D8">
-        <v>449</v>
+        <v>263</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1020,16 +999,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D9">
-        <v>449</v>
+        <v>264</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1040,16 +1019,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>484</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D10">
-        <v>724</v>
+        <v>264</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1060,16 +1039,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>503</v>
+        <v>57</v>
       </c>
       <c r="C11">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="D11">
-        <v>744</v>
+        <v>264</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1080,16 +1059,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>503</v>
+        <v>57</v>
       </c>
       <c r="C12">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="D12">
-        <v>744</v>
+        <v>264</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1100,16 +1079,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>502</v>
+        <v>58</v>
       </c>
       <c r="C13">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D13">
-        <v>741</v>
+        <v>265</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1120,16 +1099,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="C14">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="D14">
-        <v>387</v>
+        <v>274</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1140,16 +1119,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>200</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D15">
-        <v>364</v>
+        <v>273</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1160,16 +1139,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C16">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D16">
-        <v>366</v>
+        <v>274</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1180,16 +1159,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="C17">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D17">
-        <v>365</v>
+        <v>273</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1200,16 +1179,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C18">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D18">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1220,16 +1199,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C19">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D19">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1240,16 +1219,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C20">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D20">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1260,16 +1239,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C21">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D21">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1280,16 +1259,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>57</v>
+        <v>315</v>
       </c>
       <c r="C22">
-        <v>193</v>
+        <v>366</v>
       </c>
       <c r="D22">
-        <v>250</v>
+        <v>681</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1300,16 +1279,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>324</v>
       </c>
       <c r="C23">
-        <v>193</v>
+        <v>384</v>
       </c>
       <c r="D23">
-        <v>264</v>
+        <v>708</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1320,16 +1299,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="C24">
-        <v>193</v>
+        <v>385</v>
       </c>
       <c r="D24">
-        <v>271</v>
+        <v>709</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1340,16 +1319,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="C25">
-        <v>200</v>
+        <v>389</v>
       </c>
       <c r="D25">
-        <v>309</v>
+        <v>755</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1360,16 +1339,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>799</v>
+        <v>914</v>
       </c>
       <c r="C26">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="D26">
-        <v>1289</v>
+        <v>1430</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1380,16 +1359,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>822</v>
+        <v>948</v>
       </c>
       <c r="C27">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D27">
-        <v>1336</v>
+        <v>1465</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1400,16 +1379,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>818</v>
+        <v>940</v>
       </c>
       <c r="C28">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="D28">
-        <v>1331</v>
+        <v>1473</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1420,16 +1399,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>819</v>
+        <v>934</v>
       </c>
       <c r="C29">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="D29">
-        <v>1335</v>
+        <v>1523</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1440,16 +1419,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>892</v>
+        <v>989</v>
       </c>
       <c r="C30">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="D30">
-        <v>1406</v>
+        <v>1544</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1460,16 +1439,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>902</v>
+        <v>1002</v>
       </c>
       <c r="C31">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="D31">
-        <v>1428</v>
+        <v>1567</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1480,16 +1459,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>903</v>
+        <v>1028</v>
       </c>
       <c r="C32">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="D32">
-        <v>1430</v>
+        <v>1614</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1500,16 +1479,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>903</v>
+        <v>1090</v>
       </c>
       <c r="C33">
-        <v>526</v>
+        <v>598</v>
       </c>
       <c r="D33">
-        <v>1429</v>
+        <v>1688</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1520,16 +1499,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>863</v>
+        <v>1027</v>
       </c>
       <c r="C34">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="D34">
-        <v>1371</v>
+        <v>1568</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1540,16 +1519,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>815</v>
+        <v>1143</v>
       </c>
       <c r="C35">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="D35">
-        <v>1313</v>
+        <v>1695</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1560,16 +1539,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>758</v>
+        <v>1240</v>
       </c>
       <c r="C36">
-        <v>506</v>
+        <v>710</v>
       </c>
       <c r="D36">
-        <v>1264</v>
+        <v>1950</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1580,16 +1559,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>743</v>
+        <v>1445</v>
       </c>
       <c r="C37">
-        <v>503</v>
+        <v>749</v>
       </c>
       <c r="D37">
-        <v>1246</v>
+        <v>2194</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1600,16 +1579,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>752</v>
+        <v>1240</v>
       </c>
       <c r="C38">
-        <v>471</v>
+        <v>581</v>
       </c>
       <c r="D38">
-        <v>1223</v>
+        <v>1821</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1620,16 +1599,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>753</v>
+        <v>1229</v>
       </c>
       <c r="C39">
-        <v>468</v>
+        <v>561</v>
       </c>
       <c r="D39">
-        <v>1221</v>
+        <v>1790</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1640,16 +1619,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>881</v>
+        <v>1171</v>
       </c>
       <c r="C40">
-        <v>471</v>
+        <v>561</v>
       </c>
       <c r="D40">
-        <v>1352</v>
+        <v>1732</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1660,16 +1639,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>865</v>
+        <v>1028</v>
       </c>
       <c r="C41">
-        <v>465</v>
+        <v>555</v>
       </c>
       <c r="D41">
-        <v>1330</v>
+        <v>1583</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1680,16 +1659,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>133</v>
+        <v>500</v>
       </c>
       <c r="C42">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="D42">
-        <v>348</v>
+        <v>824</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1700,16 +1679,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>114</v>
+        <v>421</v>
       </c>
       <c r="C43">
-        <v>191</v>
+        <v>304</v>
       </c>
       <c r="D43">
-        <v>305</v>
+        <v>725</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1720,16 +1699,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>115</v>
+        <v>559</v>
       </c>
       <c r="C44">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="D44">
-        <v>310</v>
+        <v>864</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1740,16 +1719,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>111</v>
+        <v>591</v>
       </c>
       <c r="C45">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="D45">
-        <v>300</v>
+        <v>894</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1760,16 +1739,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>54</v>
+        <v>749</v>
       </c>
       <c r="C46">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="D46">
-        <v>252</v>
+        <v>1061</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1780,16 +1759,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>50</v>
+        <v>753</v>
       </c>
       <c r="C47">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="D47">
-        <v>249</v>
+        <v>1076</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1800,16 +1779,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>50</v>
+        <v>617</v>
       </c>
       <c r="C48">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D48">
-        <v>251</v>
+        <v>917</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1820,16 +1799,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>50</v>
+        <v>533</v>
       </c>
       <c r="C49">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="D49">
-        <v>249</v>
+        <v>828</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1840,16 +1819,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>42</v>
+        <v>445</v>
       </c>
       <c r="C50">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="D50">
-        <v>233</v>
+        <v>721</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1860,16 +1839,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="C51">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="D51">
-        <v>238</v>
+        <v>433</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1880,16 +1859,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C52">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="D52">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1900,16 +1879,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="D53">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1920,16 +1899,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C54">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="D54">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1940,16 +1919,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C55">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="D55">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1960,16 +1939,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C56">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="D56">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1980,16 +1959,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="D57">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2000,16 +1979,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C58">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="D58">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2020,16 +1999,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C59">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D59">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2040,16 +2019,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C60">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D60">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2060,16 +2039,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C61">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D61">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2080,16 +2059,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C62">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D62">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2100,16 +2079,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C63">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D63">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2120,16 +2099,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C64">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D64">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2140,16 +2119,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="C65">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="D65">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2160,16 +2139,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>722</v>
+        <v>606</v>
       </c>
       <c r="C66">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="D66">
-        <v>1335</v>
+        <v>1209</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2180,16 +2159,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>733</v>
+        <v>632</v>
       </c>
       <c r="C67">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="D67">
-        <v>1371</v>
+        <v>1284</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2200,16 +2179,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>732</v>
+        <v>697</v>
       </c>
       <c r="C68">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="D68">
-        <v>1386</v>
+        <v>1329</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2220,16 +2199,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="C69">
-        <v>658</v>
+        <v>633</v>
       </c>
       <c r="D69">
-        <v>1401</v>
+        <v>1345</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2240,16 +2219,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="C70">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="D70">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2260,16 +2239,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>862</v>
+        <v>845</v>
       </c>
       <c r="C71">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D71">
-        <v>1537</v>
+        <v>1519</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2280,16 +2259,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>914</v>
+        <v>848</v>
       </c>
       <c r="C72">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="D72">
-        <v>1595</v>
+        <v>1520</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2300,16 +2279,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="C73">
-        <v>684</v>
+        <v>710</v>
       </c>
       <c r="D73">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2320,16 +2299,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>1001</v>
+        <v>921</v>
       </c>
       <c r="C74">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="D74">
-        <v>1678</v>
+        <v>1610</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2340,16 +2319,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>978</v>
+        <v>929</v>
       </c>
       <c r="C75">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="D75">
-        <v>1656</v>
+        <v>1621</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2360,16 +2339,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>976</v>
+        <v>930</v>
       </c>
       <c r="C76">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D76">
-        <v>1658</v>
+        <v>1608</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2380,16 +2359,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C77">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D77">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2400,16 +2379,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>950</v>
+        <v>892</v>
       </c>
       <c r="C78">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D78">
-        <v>1635</v>
+        <v>1579</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2420,16 +2399,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>975</v>
+        <v>889</v>
       </c>
       <c r="C79">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D79">
-        <v>1660</v>
+        <v>1576</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2440,16 +2419,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>972</v>
+        <v>895</v>
       </c>
       <c r="C80">
         <v>687</v>
       </c>
       <c r="D80">
-        <v>1659</v>
+        <v>1582</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2460,16 +2439,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>927</v>
+        <v>892</v>
       </c>
       <c r="C81">
-        <v>649</v>
+        <v>688</v>
       </c>
       <c r="D81">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2480,16 +2459,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="C82">
-        <v>642</v>
+        <v>682</v>
       </c>
       <c r="D82">
-        <v>1526</v>
+        <v>1543</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2500,16 +2479,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="C83">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="D83">
-        <v>1516</v>
+        <v>1535</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2520,16 +2499,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>875</v>
+        <v>852</v>
       </c>
       <c r="C84">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="D84">
-        <v>1513</v>
+        <v>1529</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2540,16 +2519,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="C85">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="D85">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2560,16 +2539,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>796</v>
+        <v>755</v>
       </c>
       <c r="C86">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D86">
-        <v>1436</v>
+        <v>1393</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2580,16 +2559,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="C87">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D87">
-        <v>1429</v>
+        <v>1389</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2600,16 +2579,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>793</v>
+        <v>754</v>
       </c>
       <c r="C88">
         <v>637</v>
       </c>
       <c r="D88">
-        <v>1430</v>
+        <v>1391</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2620,16 +2599,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>791</v>
+        <v>737</v>
       </c>
       <c r="C89">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="D89">
-        <v>1427</v>
+        <v>1387</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2640,16 +2619,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>675</v>
+        <v>755</v>
       </c>
       <c r="C90">
-        <v>624</v>
+        <v>550</v>
       </c>
       <c r="D90">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2660,16 +2639,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>664</v>
+        <v>755</v>
       </c>
       <c r="C91">
-        <v>636</v>
+        <v>527</v>
       </c>
       <c r="D91">
-        <v>1300</v>
+        <v>1282</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2680,16 +2659,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>658</v>
+        <v>753</v>
       </c>
       <c r="C92">
-        <v>637</v>
+        <v>527</v>
       </c>
       <c r="D92">
-        <v>1295</v>
+        <v>1280</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2700,16 +2679,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>656</v>
+        <v>755</v>
       </c>
       <c r="C93">
-        <v>652</v>
+        <v>525</v>
       </c>
       <c r="D93">
-        <v>1308</v>
+        <v>1280</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2720,16 +2699,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>428</v>
+        <v>795</v>
       </c>
       <c r="C94">
-        <v>364</v>
+        <v>452</v>
       </c>
       <c r="D94">
-        <v>792</v>
+        <v>1247</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2740,16 +2719,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>385</v>
+        <v>781</v>
       </c>
       <c r="C95">
-        <v>342</v>
+        <v>441</v>
       </c>
       <c r="D95">
-        <v>727</v>
+        <v>1222</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2760,16 +2739,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>383</v>
+        <v>780</v>
       </c>
       <c r="C96">
-        <v>341</v>
+        <v>441</v>
       </c>
       <c r="D96">
-        <v>724</v>
+        <v>1221</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2780,16 +2759,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>392</v>
+        <v>767</v>
       </c>
       <c r="C97">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="D97">
-        <v>738</v>
+        <v>1206</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2800,16 +2779,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>794</v>
+        <v>737</v>
       </c>
       <c r="C98">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D98">
-        <v>1211</v>
+        <v>1157</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2820,16 +2799,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>886</v>
+        <v>733</v>
       </c>
       <c r="C99">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D99">
-        <v>1304</v>
+        <v>1150</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2840,16 +2819,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>883</v>
+        <v>734</v>
       </c>
       <c r="C100">
         <v>417</v>
       </c>
       <c r="D100">
-        <v>1300</v>
+        <v>1151</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2860,16 +2839,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>818</v>
+        <v>730</v>
       </c>
       <c r="C101">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D101">
-        <v>1234</v>
+        <v>1147</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2880,16 +2859,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>783</v>
+        <v>452</v>
       </c>
       <c r="C102">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D102">
-        <v>1199</v>
+        <v>870</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2900,16 +2879,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>729</v>
+        <v>447</v>
       </c>
       <c r="C103">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D103">
-        <v>1143</v>
+        <v>865</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2920,16 +2899,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>727</v>
+        <v>448</v>
       </c>
       <c r="C104">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D104">
-        <v>1142</v>
+        <v>865</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2940,16 +2919,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>723</v>
+        <v>447</v>
       </c>
       <c r="C105">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D105">
-        <v>1138</v>
+        <v>864</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2960,16 +2939,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>718</v>
+        <v>444</v>
       </c>
       <c r="C106">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D106">
-        <v>1133</v>
+        <v>856</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2980,16 +2959,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>714</v>
+        <v>443</v>
       </c>
       <c r="C107">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D107">
-        <v>1129</v>
+        <v>855</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3000,16 +2979,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>714</v>
+        <v>443</v>
       </c>
       <c r="C108">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D108">
-        <v>1129</v>
+        <v>855</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3020,16 +2999,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>714</v>
+        <v>444</v>
       </c>
       <c r="C109">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D109">
-        <v>1129</v>
+        <v>856</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3040,16 +3019,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>701</v>
+        <v>414</v>
       </c>
       <c r="C110">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="D110">
-        <v>1078</v>
+        <v>817</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3060,16 +3039,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>699</v>
+        <v>413</v>
       </c>
       <c r="C111">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="D111">
-        <v>1073</v>
+        <v>816</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3080,16 +3059,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>701</v>
+        <v>412</v>
       </c>
       <c r="C112">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="D112">
-        <v>1075</v>
+        <v>815</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3100,16 +3079,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>701</v>
+        <v>419</v>
       </c>
       <c r="C113">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="D113">
-        <v>1076</v>
+        <v>821</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3120,16 +3099,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>715</v>
+        <v>652</v>
       </c>
       <c r="C114">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D114">
-        <v>1090</v>
+        <v>1055</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3140,16 +3119,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="C115">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D115">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3160,16 +3139,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>715</v>
+        <v>677</v>
       </c>
       <c r="C116">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D116">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3180,16 +3159,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>747</v>
+        <v>685</v>
       </c>
       <c r="C117">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="D117">
-        <v>1124</v>
+        <v>1087</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3200,16 +3179,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="C118">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="D118">
-        <v>1218</v>
+        <v>1239</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3220,16 +3199,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="C119">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="D119">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3240,16 +3219,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="C120">
-        <v>491</v>
+        <v>421</v>
       </c>
       <c r="D120">
-        <v>1330</v>
+        <v>1249</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3260,16 +3239,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>875</v>
+        <v>836</v>
       </c>
       <c r="C121">
-        <v>495</v>
+        <v>421</v>
       </c>
       <c r="D121">
-        <v>1370</v>
+        <v>1257</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3280,16 +3259,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>935</v>
+        <v>1008</v>
       </c>
       <c r="C122">
-        <v>522</v>
+        <v>416</v>
       </c>
       <c r="D122">
-        <v>1457</v>
+        <v>1424</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3300,16 +3279,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>944</v>
+        <v>1026</v>
       </c>
       <c r="C123">
-        <v>523</v>
+        <v>411</v>
       </c>
       <c r="D123">
-        <v>1467</v>
+        <v>1437</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3320,16 +3299,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>936</v>
+        <v>1019</v>
       </c>
       <c r="C124">
-        <v>525</v>
+        <v>414</v>
       </c>
       <c r="D124">
-        <v>1461</v>
+        <v>1433</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3340,16 +3319,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>938</v>
+        <v>1015</v>
       </c>
       <c r="C125">
-        <v>526</v>
+        <v>415</v>
       </c>
       <c r="D125">
-        <v>1464</v>
+        <v>1430</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3360,16 +3339,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="C126">
-        <v>536</v>
+        <v>449</v>
       </c>
       <c r="D126">
-        <v>1546</v>
+        <v>1489</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3380,16 +3359,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C127">
-        <v>535</v>
+        <v>448</v>
       </c>
       <c r="D127">
-        <v>1559</v>
+        <v>1475</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3400,16 +3379,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C128">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="D128">
-        <v>1555</v>
+        <v>1482</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3420,16 +3399,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C129">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="D129">
-        <v>1524</v>
+        <v>1481</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3440,16 +3419,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>1020</v>
+        <v>997</v>
       </c>
       <c r="C130">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="D130">
-        <v>1514</v>
+        <v>1443</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3460,16 +3439,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>911</v>
+        <v>987</v>
       </c>
       <c r="C131">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="D131">
-        <v>1397</v>
+        <v>1430</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3480,16 +3459,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>832</v>
+        <v>995</v>
       </c>
       <c r="C132">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="D132">
-        <v>1312</v>
+        <v>1440</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3500,16 +3479,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>825</v>
+        <v>983</v>
       </c>
       <c r="C133">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="D133">
-        <v>1308</v>
+        <v>1440</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3520,16 +3499,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="C134">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="D134">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3540,16 +3519,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>793</v>
+        <v>896</v>
       </c>
       <c r="C135">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="D135">
-        <v>1261</v>
+        <v>1336</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3560,16 +3539,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>826</v>
+        <v>895</v>
       </c>
       <c r="C136">
-        <v>486</v>
+        <v>438</v>
       </c>
       <c r="D136">
-        <v>1312</v>
+        <v>1333</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3580,16 +3559,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>858</v>
+        <v>736</v>
       </c>
       <c r="C137">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="D137">
-        <v>1342</v>
+        <v>1174</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3600,16 +3579,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>782</v>
+        <v>70</v>
       </c>
       <c r="C138">
-        <v>440</v>
+        <v>184</v>
       </c>
       <c r="D138">
-        <v>1222</v>
+        <v>254</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3620,16 +3599,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>785</v>
+        <v>51</v>
       </c>
       <c r="C139">
-        <v>437</v>
+        <v>208</v>
       </c>
       <c r="D139">
-        <v>1222</v>
+        <v>259</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3640,16 +3619,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>785</v>
+        <v>50</v>
       </c>
       <c r="C140">
-        <v>426</v>
+        <v>207</v>
       </c>
       <c r="D140">
-        <v>1211</v>
+        <v>257</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3660,16 +3639,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>781</v>
+        <v>48</v>
       </c>
       <c r="C141">
-        <v>417</v>
+        <v>207</v>
       </c>
       <c r="D141">
-        <v>1198</v>
+        <v>255</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3680,16 +3659,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>719</v>
+        <v>40</v>
       </c>
       <c r="C142">
-        <v>427</v>
+        <v>214</v>
       </c>
       <c r="D142">
-        <v>1146</v>
+        <v>254</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3700,16 +3679,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>716</v>
+        <v>40</v>
       </c>
       <c r="C143">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="D143">
-        <v>1145</v>
+        <v>256</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3720,16 +3699,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>714</v>
+        <v>40</v>
       </c>
       <c r="C144">
-        <v>437</v>
+        <v>217</v>
       </c>
       <c r="D144">
-        <v>1151</v>
+        <v>257</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3740,16 +3719,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>683</v>
+        <v>39</v>
       </c>
       <c r="C145">
-        <v>459</v>
+        <v>215</v>
       </c>
       <c r="D145">
-        <v>1142</v>
+        <v>254</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3760,16 +3739,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>447</v>
+        <v>42</v>
       </c>
       <c r="C146">
-        <v>455</v>
+        <v>204</v>
       </c>
       <c r="D146">
-        <v>902</v>
+        <v>246</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3780,16 +3759,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>432</v>
+        <v>42</v>
       </c>
       <c r="C147">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>885</v>
+        <v>42</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3800,162 +3779,22 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>415</v>
+        <v>39</v>
       </c>
       <c r="C148">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>863</v>
+        <v>39</v>
       </c>
       <c r="E148">
         <v>51</v>
       </c>
       <c r="F148" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" s="2">
-        <v>46309.53125</v>
-      </c>
-      <c r="B149">
-        <v>224</v>
-      </c>
-      <c r="C149">
-        <v>379</v>
-      </c>
-      <c r="D149">
-        <v>603</v>
-      </c>
-      <c r="E149">
-        <v>52</v>
-      </c>
-      <c r="F149" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>238</v>
-      </c>
-      <c r="C150">
-        <v>305</v>
-      </c>
-      <c r="D150">
-        <v>543</v>
-      </c>
-      <c r="E150">
-        <v>53</v>
-      </c>
-      <c r="F150" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>174</v>
-      </c>
-      <c r="C151">
-        <v>269</v>
-      </c>
-      <c r="D151">
-        <v>443</v>
-      </c>
-      <c r="E151">
-        <v>54</v>
-      </c>
-      <c r="F151" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B152">
-        <v>164</v>
-      </c>
-      <c r="C152">
-        <v>266</v>
-      </c>
-      <c r="D152">
-        <v>430</v>
-      </c>
-      <c r="E152">
-        <v>55</v>
-      </c>
-      <c r="F152" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>291</v>
-      </c>
-      <c r="C153">
-        <v>278</v>
-      </c>
-      <c r="D153">
-        <v>569</v>
-      </c>
-      <c r="E153">
-        <v>56</v>
-      </c>
-      <c r="F153" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>151</v>
-      </c>
-      <c r="C154">
-        <v>329</v>
-      </c>
-      <c r="D154">
-        <v>480</v>
-      </c>
-      <c r="E154">
-        <v>57</v>
-      </c>
-      <c r="F154" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B155">
-        <v>160</v>
-      </c>
-      <c r="C155">
-        <v>330</v>
-      </c>
-      <c r="D155">
-        <v>490</v>
-      </c>
-      <c r="E155">
-        <v>58</v>
-      </c>
-      <c r="F155" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,445 +34,397 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
   </si>
 </sst>
 </file>
@@ -834,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -859,16 +811,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>95</v>
+        <v>967</v>
       </c>
       <c r="C2">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="D2">
-        <v>333</v>
+        <v>1239</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -879,16 +831,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>129</v>
+        <v>965</v>
       </c>
       <c r="C3">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="D3">
-        <v>352</v>
+        <v>1235</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -899,16 +851,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>72</v>
+        <v>967</v>
       </c>
       <c r="C4">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="D4">
-        <v>296</v>
+        <v>1238</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -919,16 +871,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>69</v>
+        <v>965</v>
       </c>
       <c r="C5">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="D5">
-        <v>293</v>
+        <v>1235</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -939,16 +891,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>58</v>
+        <v>954</v>
       </c>
       <c r="C6">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="D6">
-        <v>286</v>
+        <v>1219</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -959,16 +911,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>57</v>
+        <v>1003</v>
       </c>
       <c r="C7">
-        <v>208</v>
+        <v>322</v>
       </c>
       <c r="D7">
-        <v>265</v>
+        <v>1325</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -979,16 +931,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>56</v>
+        <v>1075</v>
       </c>
       <c r="C8">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="D8">
-        <v>263</v>
+        <v>1396</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -999,16 +951,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>57</v>
+        <v>1084</v>
       </c>
       <c r="C9">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="D9">
-        <v>264</v>
+        <v>1405</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1019,16 +971,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>967</v>
       </c>
       <c r="C10">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="D10">
-        <v>264</v>
+        <v>1212</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1039,16 +991,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>966</v>
       </c>
       <c r="C11">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D11">
-        <v>264</v>
+        <v>1204</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1059,16 +1011,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>57</v>
+        <v>966</v>
       </c>
       <c r="C12">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D12">
-        <v>264</v>
+        <v>1204</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1079,16 +1031,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>58</v>
+        <v>967</v>
       </c>
       <c r="C13">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D13">
-        <v>265</v>
+        <v>1205</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1099,16 +1051,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>67</v>
+        <v>968</v>
       </c>
       <c r="C14">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="D14">
-        <v>274</v>
+        <v>1211</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1119,16 +1071,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>66</v>
+        <v>967</v>
       </c>
       <c r="C15">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="D15">
-        <v>273</v>
+        <v>1210</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1139,16 +1091,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>67</v>
+        <v>967</v>
       </c>
       <c r="C16">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="D16">
-        <v>274</v>
+        <v>1210</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1159,16 +1111,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>66</v>
+        <v>967</v>
       </c>
       <c r="C17">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="D17">
-        <v>273</v>
+        <v>1212</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1179,16 +1131,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>55</v>
+        <v>964</v>
       </c>
       <c r="C18">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="D18">
-        <v>262</v>
+        <v>1253</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1199,16 +1151,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>55</v>
+        <v>963</v>
       </c>
       <c r="C19">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="D19">
-        <v>262</v>
+        <v>1252</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1219,16 +1171,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>55</v>
+        <v>965</v>
       </c>
       <c r="C20">
-        <v>207</v>
+        <v>290</v>
       </c>
       <c r="D20">
-        <v>262</v>
+        <v>1255</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1239,16 +1191,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>76</v>
+        <v>976</v>
       </c>
       <c r="C21">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="D21">
-        <v>283</v>
+        <v>1270</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1259,16 +1211,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>315</v>
+        <v>922</v>
       </c>
       <c r="C22">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="D22">
-        <v>681</v>
+        <v>1323</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1279,16 +1231,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>324</v>
+        <v>925</v>
       </c>
       <c r="C23">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="D23">
-        <v>708</v>
+        <v>1336</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1299,16 +1251,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>324</v>
+        <v>931</v>
       </c>
       <c r="C24">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="D24">
-        <v>709</v>
+        <v>1346</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1319,16 +1271,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>366</v>
+        <v>942</v>
       </c>
       <c r="C25">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="D25">
-        <v>755</v>
+        <v>1359</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1339,16 +1291,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>914</v>
+        <v>1015</v>
       </c>
       <c r="C26">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D26">
-        <v>1430</v>
+        <v>1537</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1359,16 +1311,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>948</v>
+        <v>1009</v>
       </c>
       <c r="C27">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D27">
-        <v>1465</v>
+        <v>1531</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1379,16 +1331,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>940</v>
+        <v>1014</v>
       </c>
       <c r="C28">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D28">
-        <v>1473</v>
+        <v>1541</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1399,16 +1351,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>934</v>
+        <v>1015</v>
       </c>
       <c r="C29">
-        <v>589</v>
+        <v>528</v>
       </c>
       <c r="D29">
-        <v>1523</v>
+        <v>1543</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1419,16 +1371,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>989</v>
+        <v>1081</v>
       </c>
       <c r="C30">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="D30">
-        <v>1544</v>
+        <v>1647</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1439,16 +1391,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>1002</v>
+        <v>1068</v>
       </c>
       <c r="C31">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D31">
-        <v>1567</v>
+        <v>1628</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1459,16 +1411,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C32">
-        <v>586</v>
+        <v>560</v>
       </c>
       <c r="D32">
-        <v>1614</v>
+        <v>1589</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1479,16 +1431,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>1090</v>
+        <v>1039</v>
       </c>
       <c r="C33">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="D33">
-        <v>1688</v>
+        <v>1601</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1499,13 +1451,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>1027</v>
+        <v>1059</v>
       </c>
       <c r="C34">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="D34">
         <v>1568</v>
@@ -1519,16 +1471,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>1143</v>
+        <v>1058</v>
       </c>
       <c r="C35">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="D35">
-        <v>1695</v>
+        <v>1562</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1539,16 +1491,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>1240</v>
+        <v>1046</v>
       </c>
       <c r="C36">
-        <v>710</v>
+        <v>515</v>
       </c>
       <c r="D36">
-        <v>1950</v>
+        <v>1561</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1559,16 +1511,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>1445</v>
+        <v>1043</v>
       </c>
       <c r="C37">
-        <v>749</v>
+        <v>517</v>
       </c>
       <c r="D37">
-        <v>2194</v>
+        <v>1560</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1579,16 +1531,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>1240</v>
+        <v>990</v>
       </c>
       <c r="C38">
-        <v>581</v>
+        <v>519</v>
       </c>
       <c r="D38">
-        <v>1821</v>
+        <v>1509</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1599,16 +1551,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>1229</v>
+        <v>980</v>
       </c>
       <c r="C39">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="D39">
-        <v>1790</v>
+        <v>1504</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1619,16 +1571,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>1171</v>
+        <v>974</v>
       </c>
       <c r="C40">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="D40">
-        <v>1732</v>
+        <v>1492</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1639,16 +1591,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>1028</v>
+        <v>956</v>
       </c>
       <c r="C41">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="D41">
-        <v>1583</v>
+        <v>1474</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1659,16 +1611,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="C42">
-        <v>324</v>
+        <v>261</v>
       </c>
       <c r="D42">
-        <v>824</v>
+        <v>631</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1679,16 +1631,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>421</v>
+        <v>333</v>
       </c>
       <c r="C43">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="D43">
-        <v>725</v>
+        <v>582</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1699,16 +1651,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>559</v>
+        <v>262</v>
       </c>
       <c r="C44">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="D44">
-        <v>864</v>
+        <v>512</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1719,16 +1671,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>591</v>
+        <v>258</v>
       </c>
       <c r="C45">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="D45">
-        <v>894</v>
+        <v>507</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1739,16 +1691,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>749</v>
+        <v>71</v>
       </c>
       <c r="C46">
-        <v>312</v>
+        <v>197</v>
       </c>
       <c r="D46">
-        <v>1061</v>
+        <v>268</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1759,16 +1711,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>753</v>
+        <v>62</v>
       </c>
       <c r="C47">
-        <v>323</v>
+        <v>207</v>
       </c>
       <c r="D47">
-        <v>1076</v>
+        <v>269</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1779,16 +1731,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>617</v>
+        <v>79</v>
       </c>
       <c r="C48">
-        <v>300</v>
+        <v>234</v>
       </c>
       <c r="D48">
-        <v>917</v>
+        <v>313</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1799,16 +1751,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="C49">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="D49">
-        <v>828</v>
+        <v>317</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1819,16 +1771,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>445</v>
+        <v>66</v>
       </c>
       <c r="C50">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="D50">
-        <v>721</v>
+        <v>263</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1839,16 +1791,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>184</v>
+        <v>61</v>
       </c>
       <c r="C51">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="D51">
-        <v>433</v>
+        <v>273</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1859,16 +1811,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C52">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="D52">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1879,16 +1831,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C53">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D53">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1899,16 +1851,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C54">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D54">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1919,16 +1871,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C55">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D55">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1939,16 +1891,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C56">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D56">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1959,16 +1911,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C57">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D57">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1979,16 +1931,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C58">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D58">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -1999,13 +1951,13 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C59">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="D59">
         <v>263</v>
@@ -2019,16 +1971,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C60">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="D60">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2039,16 +1991,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C61">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="D61">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2059,16 +2011,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="C62">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D62">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2079,16 +2031,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C63">
         <v>226</v>
       </c>
       <c r="D63">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2099,16 +2051,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C64">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D64">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2119,16 +2071,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C65">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="D65">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2139,16 +2091,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>606</v>
+        <v>922</v>
       </c>
       <c r="C66">
-        <v>603</v>
+        <v>467</v>
       </c>
       <c r="D66">
-        <v>1209</v>
+        <v>1389</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2159,16 +2111,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>632</v>
+        <v>1008</v>
       </c>
       <c r="C67">
-        <v>652</v>
+        <v>471</v>
       </c>
       <c r="D67">
-        <v>1284</v>
+        <v>1479</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2179,16 +2131,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>697</v>
+        <v>1009</v>
       </c>
       <c r="C68">
-        <v>632</v>
+        <v>473</v>
       </c>
       <c r="D68">
-        <v>1329</v>
+        <v>1482</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2199,16 +2151,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>712</v>
+        <v>1012</v>
       </c>
       <c r="C69">
-        <v>633</v>
+        <v>480</v>
       </c>
       <c r="D69">
-        <v>1345</v>
+        <v>1492</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2219,16 +2171,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>773</v>
+        <v>988</v>
       </c>
       <c r="C70">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D70">
-        <v>1436</v>
+        <v>1653</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2239,16 +2191,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>845</v>
+        <v>992</v>
       </c>
       <c r="C71">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D71">
-        <v>1519</v>
+        <v>1664</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2259,16 +2211,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>848</v>
+        <v>1084</v>
       </c>
       <c r="C72">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D72">
-        <v>1520</v>
+        <v>1757</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2279,16 +2231,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>910</v>
+        <v>1089</v>
       </c>
       <c r="C73">
-        <v>710</v>
+        <v>672</v>
       </c>
       <c r="D73">
-        <v>1620</v>
+        <v>1761</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2299,16 +2251,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>921</v>
+        <v>1124</v>
       </c>
       <c r="C74">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="D74">
-        <v>1610</v>
+        <v>1795</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2319,16 +2271,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>929</v>
+        <v>1124</v>
       </c>
       <c r="C75">
-        <v>692</v>
+        <v>669</v>
       </c>
       <c r="D75">
-        <v>1621</v>
+        <v>1793</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2339,16 +2291,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>930</v>
+        <v>1018</v>
       </c>
       <c r="C76">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="D76">
-        <v>1608</v>
+        <v>1678</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2359,16 +2311,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>931</v>
+        <v>1029</v>
       </c>
       <c r="C77">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="D77">
-        <v>1609</v>
+        <v>1689</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2379,16 +2331,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>892</v>
+        <v>1040</v>
       </c>
       <c r="C78">
-        <v>687</v>
+        <v>665</v>
       </c>
       <c r="D78">
-        <v>1579</v>
+        <v>1705</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2399,16 +2351,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>889</v>
+        <v>1041</v>
       </c>
       <c r="C79">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="D79">
-        <v>1576</v>
+        <v>1704</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2419,16 +2371,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>895</v>
+        <v>1133</v>
       </c>
       <c r="C80">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="D80">
-        <v>1582</v>
+        <v>1797</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2439,16 +2391,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>892</v>
+        <v>1046</v>
       </c>
       <c r="C81">
-        <v>688</v>
+        <v>638</v>
       </c>
       <c r="D81">
-        <v>1580</v>
+        <v>1684</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2459,16 +2411,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>861</v>
+        <v>1013</v>
       </c>
       <c r="C82">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D82">
-        <v>1543</v>
+        <v>1690</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2479,16 +2431,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>858</v>
+        <v>1107</v>
       </c>
       <c r="C83">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="D83">
-        <v>1535</v>
+        <v>1824</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2499,16 +2451,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>852</v>
+        <v>1205</v>
       </c>
       <c r="C84">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="D84">
-        <v>1529</v>
+        <v>1922</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2519,16 +2471,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>854</v>
+        <v>1102</v>
       </c>
       <c r="C85">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="D85">
-        <v>1512</v>
+        <v>1782</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2539,16 +2491,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>755</v>
+        <v>1015</v>
       </c>
       <c r="C86">
-        <v>638</v>
+        <v>706</v>
       </c>
       <c r="D86">
-        <v>1393</v>
+        <v>1721</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2559,16 +2511,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>752</v>
+        <v>1006</v>
       </c>
       <c r="C87">
-        <v>637</v>
+        <v>708</v>
       </c>
       <c r="D87">
-        <v>1389</v>
+        <v>1714</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2579,16 +2531,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>754</v>
+        <v>858</v>
       </c>
       <c r="C88">
-        <v>637</v>
+        <v>688</v>
       </c>
       <c r="D88">
-        <v>1391</v>
+        <v>1546</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2599,16 +2551,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>737</v>
+        <v>848</v>
       </c>
       <c r="C89">
-        <v>650</v>
+        <v>686</v>
       </c>
       <c r="D89">
-        <v>1387</v>
+        <v>1534</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2619,16 +2571,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>755</v>
+        <v>863</v>
       </c>
       <c r="C90">
-        <v>550</v>
+        <v>666</v>
       </c>
       <c r="D90">
-        <v>1305</v>
+        <v>1529</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2639,16 +2591,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>755</v>
+        <v>861</v>
       </c>
       <c r="C91">
-        <v>527</v>
+        <v>661</v>
       </c>
       <c r="D91">
-        <v>1282</v>
+        <v>1522</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2659,16 +2611,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>753</v>
+        <v>853</v>
       </c>
       <c r="C92">
-        <v>527</v>
+        <v>662</v>
       </c>
       <c r="D92">
-        <v>1280</v>
+        <v>1515</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2679,16 +2631,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>755</v>
+        <v>848</v>
       </c>
       <c r="C93">
-        <v>525</v>
+        <v>660</v>
       </c>
       <c r="D93">
-        <v>1280</v>
+        <v>1508</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2699,16 +2651,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>795</v>
+        <v>773</v>
       </c>
       <c r="C94">
-        <v>452</v>
+        <v>627</v>
       </c>
       <c r="D94">
-        <v>1247</v>
+        <v>1400</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2719,16 +2671,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>781</v>
+        <v>695</v>
       </c>
       <c r="C95">
-        <v>441</v>
+        <v>558</v>
       </c>
       <c r="D95">
-        <v>1222</v>
+        <v>1253</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2739,16 +2691,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>780</v>
+        <v>691</v>
       </c>
       <c r="C96">
-        <v>441</v>
+        <v>582</v>
       </c>
       <c r="D96">
-        <v>1221</v>
+        <v>1273</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2759,16 +2711,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>767</v>
+        <v>688</v>
       </c>
       <c r="C97">
-        <v>439</v>
+        <v>572</v>
       </c>
       <c r="D97">
-        <v>1206</v>
+        <v>1260</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2779,16 +2731,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>737</v>
+        <v>150</v>
       </c>
       <c r="C98">
-        <v>420</v>
+        <v>246</v>
       </c>
       <c r="D98">
-        <v>1157</v>
+        <v>396</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2799,16 +2751,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>733</v>
+        <v>130</v>
       </c>
       <c r="C99">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D99">
-        <v>1150</v>
+        <v>354</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2819,16 +2771,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>734</v>
+        <v>130</v>
       </c>
       <c r="C100">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D100">
-        <v>1151</v>
+        <v>354</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2839,16 +2791,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>730</v>
+        <v>152</v>
       </c>
       <c r="C101">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D101">
-        <v>1147</v>
+        <v>376</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2859,16 +2811,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C102">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="D102">
-        <v>870</v>
+        <v>687</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2879,16 +2831,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C103">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="D103">
-        <v>865</v>
+        <v>691</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2899,16 +2851,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="C104">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D104">
-        <v>865</v>
+        <v>694</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2919,16 +2871,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="C105">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D105">
-        <v>864</v>
+        <v>697</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2939,16 +2891,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>444</v>
+        <v>799</v>
       </c>
       <c r="C106">
-        <v>412</v>
+        <v>227</v>
       </c>
       <c r="D106">
-        <v>856</v>
+        <v>1026</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2959,16 +2911,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>443</v>
+        <v>896</v>
       </c>
       <c r="C107">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="D107">
-        <v>855</v>
+        <v>1171</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2979,16 +2931,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>443</v>
+        <v>910</v>
       </c>
       <c r="C108">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="D108">
-        <v>855</v>
+        <v>1185</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -2999,16 +2951,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>444</v>
+        <v>903</v>
       </c>
       <c r="C109">
-        <v>412</v>
+        <v>274</v>
       </c>
       <c r="D109">
-        <v>856</v>
+        <v>1177</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3019,16 +2971,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>414</v>
+        <v>806</v>
       </c>
       <c r="C110">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="D110">
-        <v>817</v>
+        <v>1082</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3039,16 +2991,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>413</v>
+        <v>697</v>
       </c>
       <c r="C111">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="D111">
-        <v>816</v>
+        <v>973</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3059,16 +3011,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>412</v>
+        <v>787</v>
       </c>
       <c r="C112">
-        <v>403</v>
+        <v>275</v>
       </c>
       <c r="D112">
-        <v>815</v>
+        <v>1062</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3079,16 +3031,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>419</v>
+        <v>878</v>
       </c>
       <c r="C113">
-        <v>402</v>
+        <v>275</v>
       </c>
       <c r="D113">
-        <v>821</v>
+        <v>1153</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3099,16 +3051,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>652</v>
+        <v>545</v>
       </c>
       <c r="C114">
-        <v>403</v>
+        <v>229</v>
       </c>
       <c r="D114">
-        <v>1055</v>
+        <v>774</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3119,16 +3071,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="C115">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="D115">
-        <v>1069</v>
+        <v>916</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3139,16 +3091,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>677</v>
+        <v>644</v>
       </c>
       <c r="C116">
-        <v>403</v>
+        <v>275</v>
       </c>
       <c r="D116">
-        <v>1080</v>
+        <v>919</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3159,16 +3111,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="C117">
-        <v>402</v>
+        <v>274</v>
       </c>
       <c r="D117">
-        <v>1087</v>
+        <v>914</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3179,16 +3131,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>822</v>
+        <v>741</v>
       </c>
       <c r="C118">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="D118">
-        <v>1239</v>
+        <v>1056</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3199,16 +3151,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>828</v>
+        <v>753</v>
       </c>
       <c r="C119">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="D119">
-        <v>1248</v>
+        <v>1079</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3219,16 +3171,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>828</v>
+        <v>657</v>
       </c>
       <c r="C120">
-        <v>421</v>
+        <v>231</v>
       </c>
       <c r="D120">
-        <v>1249</v>
+        <v>888</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3239,16 +3191,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>836</v>
+        <v>669</v>
       </c>
       <c r="C121">
-        <v>421</v>
+        <v>229</v>
       </c>
       <c r="D121">
-        <v>1257</v>
+        <v>898</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3259,16 +3211,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>1008</v>
+        <v>923</v>
       </c>
       <c r="C122">
-        <v>416</v>
+        <v>559</v>
       </c>
       <c r="D122">
-        <v>1424</v>
+        <v>1482</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3279,16 +3231,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>1026</v>
+        <v>976</v>
       </c>
       <c r="C123">
-        <v>411</v>
+        <v>570</v>
       </c>
       <c r="D123">
-        <v>1437</v>
+        <v>1546</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3299,16 +3251,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>1019</v>
+        <v>947</v>
       </c>
       <c r="C124">
-        <v>414</v>
+        <v>570</v>
       </c>
       <c r="D124">
-        <v>1433</v>
+        <v>1517</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3319,16 +3271,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="C125">
-        <v>415</v>
+        <v>570</v>
       </c>
       <c r="D125">
-        <v>1430</v>
+        <v>1567</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3339,16 +3291,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>1040</v>
+        <v>1006</v>
       </c>
       <c r="C126">
-        <v>449</v>
+        <v>560</v>
       </c>
       <c r="D126">
-        <v>1489</v>
+        <v>1566</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3359,16 +3311,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>1027</v>
+        <v>1002</v>
       </c>
       <c r="C127">
-        <v>448</v>
+        <v>561</v>
       </c>
       <c r="D127">
-        <v>1475</v>
+        <v>1563</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3379,16 +3331,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>1024</v>
+        <v>1007</v>
       </c>
       <c r="C128">
-        <v>458</v>
+        <v>562</v>
       </c>
       <c r="D128">
-        <v>1482</v>
+        <v>1569</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3399,16 +3351,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="C129">
-        <v>459</v>
+        <v>561</v>
       </c>
       <c r="D129">
-        <v>1481</v>
+        <v>1569</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3419,16 +3371,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="C130">
-        <v>446</v>
+        <v>539</v>
       </c>
       <c r="D130">
-        <v>1443</v>
+        <v>1551</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3439,16 +3391,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>987</v>
+        <v>1022</v>
       </c>
       <c r="C131">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="D131">
-        <v>1430</v>
+        <v>1560</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3459,342 +3411,22 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>995</v>
+        <v>1042</v>
       </c>
       <c r="C132">
-        <v>445</v>
+        <v>582</v>
       </c>
       <c r="D132">
-        <v>1440</v>
+        <v>1624</v>
       </c>
       <c r="E132">
         <v>35</v>
       </c>
       <c r="F132" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>983</v>
-      </c>
-      <c r="C133">
-        <v>457</v>
-      </c>
-      <c r="D133">
-        <v>1440</v>
-      </c>
-      <c r="E133">
-        <v>36</v>
-      </c>
-      <c r="F133" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B134">
-        <v>898</v>
-      </c>
-      <c r="C134">
-        <v>440</v>
-      </c>
-      <c r="D134">
-        <v>1338</v>
-      </c>
-      <c r="E134">
-        <v>37</v>
-      </c>
-      <c r="F134" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>896</v>
-      </c>
-      <c r="C135">
-        <v>440</v>
-      </c>
-      <c r="D135">
-        <v>1336</v>
-      </c>
-      <c r="E135">
-        <v>38</v>
-      </c>
-      <c r="F135" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>895</v>
-      </c>
-      <c r="C136">
-        <v>438</v>
-      </c>
-      <c r="D136">
-        <v>1333</v>
-      </c>
-      <c r="E136">
-        <v>39</v>
-      </c>
-      <c r="F136" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B137">
-        <v>736</v>
-      </c>
-      <c r="C137">
-        <v>438</v>
-      </c>
-      <c r="D137">
-        <v>1174</v>
-      </c>
-      <c r="E137">
-        <v>40</v>
-      </c>
-      <c r="F137" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>70</v>
-      </c>
-      <c r="C138">
-        <v>184</v>
-      </c>
-      <c r="D138">
-        <v>254</v>
-      </c>
-      <c r="E138">
-        <v>41</v>
-      </c>
-      <c r="F138" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>51</v>
-      </c>
-      <c r="C139">
-        <v>208</v>
-      </c>
-      <c r="D139">
-        <v>259</v>
-      </c>
-      <c r="E139">
-        <v>42</v>
-      </c>
-      <c r="F139" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B140">
-        <v>50</v>
-      </c>
-      <c r="C140">
-        <v>207</v>
-      </c>
-      <c r="D140">
-        <v>257</v>
-      </c>
-      <c r="E140">
-        <v>43</v>
-      </c>
-      <c r="F140" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>48</v>
-      </c>
-      <c r="C141">
-        <v>207</v>
-      </c>
-      <c r="D141">
-        <v>255</v>
-      </c>
-      <c r="E141">
-        <v>44</v>
-      </c>
-      <c r="F141" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>40</v>
-      </c>
-      <c r="C142">
-        <v>214</v>
-      </c>
-      <c r="D142">
-        <v>254</v>
-      </c>
-      <c r="E142">
-        <v>45</v>
-      </c>
-      <c r="F142" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B143">
-        <v>40</v>
-      </c>
-      <c r="C143">
-        <v>216</v>
-      </c>
-      <c r="D143">
-        <v>256</v>
-      </c>
-      <c r="E143">
-        <v>46</v>
-      </c>
-      <c r="F143" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>40</v>
-      </c>
-      <c r="C144">
-        <v>217</v>
-      </c>
-      <c r="D144">
-        <v>257</v>
-      </c>
-      <c r="E144">
-        <v>47</v>
-      </c>
-      <c r="F144" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>39</v>
-      </c>
-      <c r="C145">
-        <v>215</v>
-      </c>
-      <c r="D145">
-        <v>254</v>
-      </c>
-      <c r="E145">
-        <v>48</v>
-      </c>
-      <c r="F145" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B146">
-        <v>42</v>
-      </c>
-      <c r="C146">
-        <v>204</v>
-      </c>
-      <c r="D146">
-        <v>246</v>
-      </c>
-      <c r="E146">
-        <v>49</v>
-      </c>
-      <c r="F146" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>42</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>42</v>
-      </c>
-      <c r="E147">
-        <v>50</v>
-      </c>
-      <c r="F147" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>39</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>39</v>
-      </c>
-      <c r="E148">
-        <v>51</v>
-      </c>
-      <c r="F148" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,397 +34,403 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -811,16 +817,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>967</v>
+        <v>459</v>
       </c>
       <c r="C2">
-        <v>272</v>
+        <v>349</v>
       </c>
       <c r="D2">
-        <v>1239</v>
+        <v>808</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -831,16 +837,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>965</v>
+        <v>457</v>
       </c>
       <c r="C3">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="D3">
-        <v>1235</v>
+        <v>804</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -851,16 +857,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>967</v>
+        <v>379</v>
       </c>
       <c r="C4">
-        <v>271</v>
+        <v>346</v>
       </c>
       <c r="D4">
-        <v>1238</v>
+        <v>725</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -871,16 +877,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>965</v>
+        <v>282</v>
       </c>
       <c r="C5">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="D5">
-        <v>1235</v>
+        <v>629</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -891,16 +897,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>954</v>
+        <v>36</v>
       </c>
       <c r="C6">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="D6">
-        <v>1219</v>
+        <v>272</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -911,16 +917,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>1003</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="D7">
-        <v>1325</v>
+        <v>266</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -931,16 +937,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>1075</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>321</v>
+        <v>218</v>
       </c>
       <c r="D8">
-        <v>1396</v>
+        <v>252</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -951,16 +957,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>1084</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="D9">
-        <v>1405</v>
+        <v>250</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -971,16 +977,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>967</v>
+        <v>31</v>
       </c>
       <c r="C10">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="D10">
-        <v>1212</v>
+        <v>254</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -991,16 +997,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>966</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D11">
-        <v>1204</v>
+        <v>267</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1011,16 +1017,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>966</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D12">
-        <v>1204</v>
+        <v>268</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1031,16 +1037,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>967</v>
+        <v>30</v>
       </c>
       <c r="C13">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13">
-        <v>1205</v>
+        <v>267</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1051,16 +1057,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>968</v>
+        <v>32</v>
       </c>
       <c r="C14">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D14">
-        <v>1211</v>
+        <v>269</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1071,16 +1077,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>967</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D15">
-        <v>1210</v>
+        <v>269</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1091,16 +1097,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>967</v>
+        <v>32</v>
       </c>
       <c r="C16">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D16">
-        <v>1210</v>
+        <v>269</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1111,16 +1117,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>967</v>
+        <v>42</v>
       </c>
       <c r="C17">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D17">
-        <v>1212</v>
+        <v>282</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1131,16 +1137,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>964</v>
+        <v>256</v>
       </c>
       <c r="C18">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="D18">
-        <v>1253</v>
+        <v>598</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1151,16 +1157,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>963</v>
+        <v>263</v>
       </c>
       <c r="C19">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="D19">
-        <v>1252</v>
+        <v>608</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1171,16 +1177,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>965</v>
+        <v>266</v>
       </c>
       <c r="C20">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="D20">
-        <v>1255</v>
+        <v>611</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1191,16 +1197,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>976</v>
+        <v>273</v>
       </c>
       <c r="C21">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="D21">
-        <v>1270</v>
+        <v>625</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1211,16 +1217,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>922</v>
+        <v>483</v>
       </c>
       <c r="C22">
-        <v>401</v>
+        <v>510</v>
       </c>
       <c r="D22">
-        <v>1323</v>
+        <v>993</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1231,16 +1237,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>925</v>
+        <v>638</v>
       </c>
       <c r="C23">
-        <v>411</v>
+        <v>522</v>
       </c>
       <c r="D23">
-        <v>1336</v>
+        <v>1160</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1251,16 +1257,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>931</v>
+        <v>661</v>
       </c>
       <c r="C24">
-        <v>415</v>
+        <v>514</v>
       </c>
       <c r="D24">
-        <v>1346</v>
+        <v>1175</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1271,16 +1277,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>942</v>
+        <v>659</v>
       </c>
       <c r="C25">
-        <v>417</v>
+        <v>522</v>
       </c>
       <c r="D25">
-        <v>1359</v>
+        <v>1181</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1291,16 +1297,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>1015</v>
+        <v>711</v>
       </c>
       <c r="C26">
-        <v>522</v>
+        <v>566</v>
       </c>
       <c r="D26">
-        <v>1537</v>
+        <v>1277</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1311,16 +1317,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>1009</v>
+        <v>712</v>
       </c>
       <c r="C27">
-        <v>522</v>
+        <v>571</v>
       </c>
       <c r="D27">
-        <v>1531</v>
+        <v>1283</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1331,16 +1337,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>1014</v>
+        <v>710</v>
       </c>
       <c r="C28">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="D28">
-        <v>1541</v>
+        <v>1283</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1351,16 +1357,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>1015</v>
+        <v>709</v>
       </c>
       <c r="C29">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="D29">
-        <v>1543</v>
+        <v>1280</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1371,16 +1377,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>1081</v>
+        <v>720</v>
       </c>
       <c r="C30">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="D30">
-        <v>1647</v>
+        <v>1305</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1391,16 +1397,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>1068</v>
+        <v>719</v>
       </c>
       <c r="C31">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="D31">
-        <v>1628</v>
+        <v>1304</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1411,16 +1417,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>1029</v>
+        <v>719</v>
       </c>
       <c r="C32">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="D32">
-        <v>1589</v>
+        <v>1304</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1431,16 +1437,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>1039</v>
+        <v>721</v>
       </c>
       <c r="C33">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="D33">
-        <v>1601</v>
+        <v>1305</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1451,16 +1457,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>1059</v>
+        <v>679</v>
       </c>
       <c r="C34">
-        <v>509</v>
+        <v>566</v>
       </c>
       <c r="D34">
-        <v>1568</v>
+        <v>1245</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1471,16 +1477,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>1058</v>
+        <v>678</v>
       </c>
       <c r="C35">
-        <v>504</v>
+        <v>563</v>
       </c>
       <c r="D35">
-        <v>1562</v>
+        <v>1241</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1491,16 +1497,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>1046</v>
+        <v>643</v>
       </c>
       <c r="C36">
-        <v>515</v>
+        <v>573</v>
       </c>
       <c r="D36">
-        <v>1561</v>
+        <v>1216</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1511,16 +1517,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>1043</v>
+        <v>635</v>
       </c>
       <c r="C37">
-        <v>517</v>
+        <v>574</v>
       </c>
       <c r="D37">
-        <v>1560</v>
+        <v>1209</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1531,16 +1537,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>990</v>
+        <v>94</v>
       </c>
       <c r="C38">
-        <v>519</v>
+        <v>318</v>
       </c>
       <c r="D38">
-        <v>1509</v>
+        <v>412</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1551,16 +1557,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>980</v>
+        <v>84</v>
       </c>
       <c r="C39">
-        <v>524</v>
+        <v>293</v>
       </c>
       <c r="D39">
-        <v>1504</v>
+        <v>377</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1571,16 +1577,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>974</v>
+        <v>88</v>
       </c>
       <c r="C40">
-        <v>518</v>
+        <v>293</v>
       </c>
       <c r="D40">
-        <v>1492</v>
+        <v>381</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1591,16 +1597,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>956</v>
+        <v>204</v>
       </c>
       <c r="C41">
-        <v>518</v>
+        <v>333</v>
       </c>
       <c r="D41">
-        <v>1474</v>
+        <v>537</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1611,16 +1617,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>370</v>
+        <v>219</v>
       </c>
       <c r="C42">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D42">
-        <v>631</v>
+        <v>473</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1631,16 +1637,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>333</v>
+        <v>268</v>
       </c>
       <c r="C43">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D43">
-        <v>582</v>
+        <v>514</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1651,16 +1657,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C44">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D44">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1671,16 +1677,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="C45">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D45">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1691,16 +1697,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>71</v>
+        <v>221</v>
       </c>
       <c r="C46">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="D46">
-        <v>268</v>
+        <v>482</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1711,16 +1717,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="C47">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D47">
-        <v>269</v>
+        <v>457</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1731,16 +1737,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
         <v>79</v>
       </c>
       <c r="C48">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D48">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1751,16 +1757,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C49">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D49">
-        <v>317</v>
+        <v>272</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1771,16 +1777,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C50">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D50">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1791,16 +1797,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C51">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D51">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1811,16 +1817,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C52">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D52">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -1831,16 +1837,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C53">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D53">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -1851,16 +1857,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C54">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="D54">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -1871,16 +1877,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C55">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D55">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -1891,16 +1897,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C56">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D56">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -1911,16 +1917,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C57">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D57">
-        <v>305</v>
+        <v>258</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -1931,16 +1937,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C58">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D58">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -1951,16 +1957,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="C59">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D59">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -1971,16 +1977,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C60">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="D60">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -1991,16 +1997,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="C61">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D61">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2011,16 +2017,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="C62">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D62">
-        <v>348</v>
+        <v>268</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2031,16 +2037,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="C63">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D63">
-        <v>351</v>
+        <v>270</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2051,16 +2057,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="C64">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D64">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2071,16 +2077,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="C65">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D65">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2091,16 +2097,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>922</v>
+        <v>612</v>
       </c>
       <c r="C66">
-        <v>467</v>
+        <v>625</v>
       </c>
       <c r="D66">
-        <v>1389</v>
+        <v>1237</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2111,16 +2117,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>1008</v>
+        <v>619</v>
       </c>
       <c r="C67">
-        <v>471</v>
+        <v>652</v>
       </c>
       <c r="D67">
-        <v>1479</v>
+        <v>1271</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2131,16 +2137,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>1009</v>
+        <v>687</v>
       </c>
       <c r="C68">
-        <v>473</v>
+        <v>697</v>
       </c>
       <c r="D68">
-        <v>1482</v>
+        <v>1384</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2151,16 +2157,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>1012</v>
+        <v>697</v>
       </c>
       <c r="C69">
-        <v>480</v>
+        <v>693</v>
       </c>
       <c r="D69">
-        <v>1492</v>
+        <v>1390</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2171,16 +2177,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>988</v>
+        <v>809</v>
       </c>
       <c r="C70">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="D70">
-        <v>1653</v>
+        <v>1522</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2191,16 +2197,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>992</v>
+        <v>752</v>
       </c>
       <c r="C71">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="D71">
-        <v>1664</v>
+        <v>1452</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2211,16 +2217,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>1084</v>
+        <v>750</v>
       </c>
       <c r="C72">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="D72">
-        <v>1757</v>
+        <v>1446</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2231,16 +2237,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>1089</v>
+        <v>751</v>
       </c>
       <c r="C73">
-        <v>672</v>
+        <v>696</v>
       </c>
       <c r="D73">
-        <v>1761</v>
+        <v>1447</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2251,16 +2257,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>1124</v>
+        <v>864</v>
       </c>
       <c r="C74">
-        <v>671</v>
+        <v>695</v>
       </c>
       <c r="D74">
-        <v>1795</v>
+        <v>1559</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2271,16 +2277,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>1124</v>
+        <v>872</v>
       </c>
       <c r="C75">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="D75">
-        <v>1793</v>
+        <v>1569</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2291,16 +2297,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>1018</v>
+        <v>867</v>
       </c>
       <c r="C76">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="D76">
-        <v>1678</v>
+        <v>1574</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2311,16 +2317,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>1029</v>
+        <v>867</v>
       </c>
       <c r="C77">
-        <v>660</v>
+        <v>703</v>
       </c>
       <c r="D77">
-        <v>1689</v>
+        <v>1570</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2331,16 +2337,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>1040</v>
+        <v>853</v>
       </c>
       <c r="C78">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D78">
-        <v>1705</v>
+        <v>1516</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2351,16 +2357,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>1041</v>
+        <v>846</v>
       </c>
       <c r="C79">
         <v>663</v>
       </c>
       <c r="D79">
-        <v>1704</v>
+        <v>1509</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2371,16 +2377,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>1133</v>
+        <v>845</v>
       </c>
       <c r="C80">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D80">
-        <v>1797</v>
+        <v>1506</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2391,16 +2397,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>1046</v>
+        <v>845</v>
       </c>
       <c r="C81">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="D81">
-        <v>1684</v>
+        <v>1508</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2411,16 +2417,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>1013</v>
+        <v>814</v>
       </c>
       <c r="C82">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="D82">
-        <v>1690</v>
+        <v>1477</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2431,16 +2437,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>1107</v>
+        <v>811</v>
       </c>
       <c r="C83">
-        <v>717</v>
+        <v>663</v>
       </c>
       <c r="D83">
-        <v>1824</v>
+        <v>1474</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2451,16 +2457,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>1205</v>
+        <v>811</v>
       </c>
       <c r="C84">
-        <v>717</v>
+        <v>660</v>
       </c>
       <c r="D84">
-        <v>1922</v>
+        <v>1471</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2471,16 +2477,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>1102</v>
+        <v>815</v>
       </c>
       <c r="C85">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="D85">
-        <v>1782</v>
+        <v>1477</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2491,16 +2497,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>1015</v>
+        <v>741</v>
       </c>
       <c r="C86">
-        <v>706</v>
+        <v>660</v>
       </c>
       <c r="D86">
-        <v>1721</v>
+        <v>1401</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2511,16 +2517,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>1006</v>
+        <v>739</v>
       </c>
       <c r="C87">
-        <v>708</v>
+        <v>660</v>
       </c>
       <c r="D87">
-        <v>1714</v>
+        <v>1399</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2531,16 +2537,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>858</v>
+        <v>723</v>
       </c>
       <c r="C88">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="D88">
-        <v>1546</v>
+        <v>1400</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2551,16 +2557,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>848</v>
+        <v>716</v>
       </c>
       <c r="C89">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D89">
-        <v>1534</v>
+        <v>1397</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2571,16 +2577,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>863</v>
+        <v>609</v>
       </c>
       <c r="C90">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="D90">
-        <v>1529</v>
+        <v>1290</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2591,16 +2597,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>861</v>
+        <v>603</v>
       </c>
       <c r="C91">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="D91">
-        <v>1522</v>
+        <v>1282</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2611,16 +2617,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>853</v>
+        <v>604</v>
       </c>
       <c r="C92">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="D92">
-        <v>1515</v>
+        <v>1280</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2631,16 +2637,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>848</v>
+        <v>599</v>
       </c>
       <c r="C93">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="D93">
-        <v>1508</v>
+        <v>1274</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2651,16 +2657,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>773</v>
+        <v>649</v>
       </c>
       <c r="C94">
-        <v>627</v>
+        <v>571</v>
       </c>
       <c r="D94">
-        <v>1400</v>
+        <v>1220</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2671,16 +2677,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="C95">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D95">
-        <v>1253</v>
+        <v>1208</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2691,16 +2697,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>691</v>
+        <v>643</v>
       </c>
       <c r="C96">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="D96">
-        <v>1273</v>
+        <v>1210</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2711,16 +2717,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>688</v>
+        <v>642</v>
       </c>
       <c r="C97">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D97">
-        <v>1260</v>
+        <v>1205</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2731,16 +2737,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>150</v>
+        <v>644</v>
       </c>
       <c r="C98">
-        <v>246</v>
+        <v>516</v>
       </c>
       <c r="D98">
-        <v>396</v>
+        <v>1160</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2751,16 +2757,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>130</v>
+        <v>643</v>
       </c>
       <c r="C99">
-        <v>224</v>
+        <v>512</v>
       </c>
       <c r="D99">
-        <v>354</v>
+        <v>1155</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2771,16 +2777,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>130</v>
+        <v>643</v>
       </c>
       <c r="C100">
-        <v>224</v>
+        <v>512</v>
       </c>
       <c r="D100">
-        <v>354</v>
+        <v>1155</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2791,16 +2797,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>152</v>
+        <v>628</v>
       </c>
       <c r="C101">
-        <v>224</v>
+        <v>511</v>
       </c>
       <c r="D101">
-        <v>376</v>
+        <v>1139</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2811,16 +2817,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>463</v>
+        <v>49</v>
       </c>
       <c r="C102">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D102">
-        <v>687</v>
+        <v>288</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -2831,16 +2837,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>467</v>
+        <v>35</v>
       </c>
       <c r="C103">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D103">
-        <v>691</v>
+        <v>258</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -2851,16 +2857,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>470</v>
+        <v>36</v>
       </c>
       <c r="C104">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D104">
-        <v>694</v>
+        <v>259</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -2871,16 +2877,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="C105">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D105">
-        <v>697</v>
+        <v>358</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -2891,16 +2897,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>799</v>
+        <v>131</v>
       </c>
       <c r="C106">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D106">
-        <v>1026</v>
+        <v>359</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -2911,16 +2917,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
-        <v>896</v>
+        <v>131</v>
       </c>
       <c r="C107">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D107">
-        <v>1171</v>
+        <v>359</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -2931,16 +2937,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
-        <v>910</v>
+        <v>131</v>
       </c>
       <c r="C108">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D108">
-        <v>1185</v>
+        <v>359</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -2951,16 +2957,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
-        <v>903</v>
+        <v>131</v>
       </c>
       <c r="C109">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="D109">
-        <v>1177</v>
+        <v>359</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -2971,16 +2977,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>806</v>
+        <v>131</v>
       </c>
       <c r="C110">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D110">
-        <v>1082</v>
+        <v>359</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -2991,16 +2997,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>697</v>
+        <v>131</v>
       </c>
       <c r="C111">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D111">
-        <v>973</v>
+        <v>359</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3011,16 +3017,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>787</v>
+        <v>131</v>
       </c>
       <c r="C112">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D112">
-        <v>1062</v>
+        <v>359</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3031,16 +3037,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>878</v>
+        <v>131</v>
       </c>
       <c r="C113">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D113">
-        <v>1153</v>
+        <v>359</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3051,16 +3057,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>545</v>
+        <v>131</v>
       </c>
       <c r="C114">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D114">
-        <v>774</v>
+        <v>359</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3071,16 +3077,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>644</v>
+        <v>32</v>
       </c>
       <c r="C115">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="D115">
-        <v>916</v>
+        <v>259</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3091,16 +3097,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>644</v>
+        <v>32</v>
       </c>
       <c r="C116">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="D116">
-        <v>919</v>
+        <v>259</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3111,16 +3117,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>640</v>
+        <v>31</v>
       </c>
       <c r="C117">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="D117">
-        <v>914</v>
+        <v>258</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3131,16 +3137,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>741</v>
+        <v>52</v>
       </c>
       <c r="C118">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="D118">
-        <v>1056</v>
+        <v>281</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3151,16 +3157,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>753</v>
+        <v>51</v>
       </c>
       <c r="C119">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="D119">
-        <v>1079</v>
+        <v>280</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3171,16 +3177,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>657</v>
+        <v>54</v>
       </c>
       <c r="C120">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D120">
-        <v>888</v>
+        <v>283</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3191,16 +3197,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>669</v>
+        <v>100</v>
       </c>
       <c r="C121">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D121">
-        <v>898</v>
+        <v>334</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3211,16 +3217,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>923</v>
+        <v>579</v>
       </c>
       <c r="C122">
-        <v>559</v>
+        <v>490</v>
       </c>
       <c r="D122">
-        <v>1482</v>
+        <v>1069</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3231,16 +3237,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>976</v>
+        <v>638</v>
       </c>
       <c r="C123">
-        <v>570</v>
+        <v>519</v>
       </c>
       <c r="D123">
-        <v>1546</v>
+        <v>1157</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3251,16 +3257,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>947</v>
+        <v>644</v>
       </c>
       <c r="C124">
-        <v>570</v>
+        <v>521</v>
       </c>
       <c r="D124">
-        <v>1517</v>
+        <v>1165</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3271,16 +3277,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>997</v>
+        <v>636</v>
       </c>
       <c r="C125">
-        <v>570</v>
+        <v>521</v>
       </c>
       <c r="D125">
-        <v>1567</v>
+        <v>1157</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3291,16 +3297,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>1006</v>
+        <v>646</v>
       </c>
       <c r="C126">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="D126">
-        <v>1566</v>
+        <v>1179</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3311,16 +3317,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>1002</v>
+        <v>647</v>
       </c>
       <c r="C127">
-        <v>561</v>
+        <v>532</v>
       </c>
       <c r="D127">
-        <v>1563</v>
+        <v>1179</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3331,16 +3337,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>1007</v>
+        <v>648</v>
       </c>
       <c r="C128">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D128">
-        <v>1569</v>
+        <v>1207</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3351,16 +3357,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>1008</v>
+        <v>645</v>
       </c>
       <c r="C129">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D129">
-        <v>1569</v>
+        <v>1213</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3371,16 +3377,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>1012</v>
+        <v>153</v>
       </c>
       <c r="C130">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D130">
-        <v>1551</v>
+        <v>618</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3391,16 +3397,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>1022</v>
+        <v>120</v>
       </c>
       <c r="C131">
-        <v>538</v>
+        <v>460</v>
       </c>
       <c r="D131">
-        <v>1560</v>
+        <v>580</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3411,22 +3417,62 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>1042</v>
+        <v>117</v>
       </c>
       <c r="C132">
+        <v>465</v>
+      </c>
+      <c r="D132">
         <v>582</v>
-      </c>
-      <c r="D132">
-        <v>1624</v>
       </c>
       <c r="E132">
         <v>35</v>
       </c>
       <c r="F132" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="2">
+        <v>46320.32291666666</v>
+      </c>
+      <c r="B133">
+        <v>115</v>
+      </c>
+      <c r="C133">
+        <v>465</v>
+      </c>
+      <c r="D133">
+        <v>580</v>
+      </c>
+      <c r="E133">
+        <v>36</v>
+      </c>
+      <c r="F133" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="2">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="B134">
+        <v>126</v>
+      </c>
+      <c r="C134">
+        <v>455</v>
+      </c>
+      <c r="D134">
+        <v>581</v>
+      </c>
+      <c r="E134">
+        <v>37</v>
+      </c>
+      <c r="F134" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
